--- a/plan/2026-2027/APEX-Yearly-Plan.xlsx
+++ b/plan/2026-2027/APEX-Yearly-Plan.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H2" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I2" s="28" t="inlineStr">
@@ -1587,8 +1587,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J2" s="26" t="inlineStr"/>
-      <c r="K2" s="26" t="inlineStr"/>
+      <c r="J2" s="26" t="inlineStr">
+        <is>
+          <t>+972544319991</t>
+        </is>
+      </c>
+      <c r="K2" s="26" t="inlineStr">
+        <is>
+          <t>assafmonsa@gmail.com</t>
+        </is>
+      </c>
       <c r="L2" s="29" t="n"/>
       <c r="M2" s="29" t="n"/>
     </row>
@@ -1626,7 +1634,7 @@
       </c>
       <c r="H3" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I3" s="28" t="inlineStr">
@@ -1634,8 +1642,16 @@
           <t>Node candidate — founded Snyk. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr"/>
-      <c r="K3" s="26" t="inlineStr"/>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>+972507616594</t>
+        </is>
+      </c>
+      <c r="K3" s="26" t="inlineStr">
+        <is>
+          <t>danny.grander@gmail.com</t>
+        </is>
+      </c>
       <c r="L3" s="29" t="n"/>
       <c r="M3" s="29" t="n"/>
     </row>
@@ -1720,16 +1736,24 @@
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J5" s="26" t="inlineStr"/>
-      <c r="K5" s="26" t="inlineStr"/>
+          <t>Stay current — what are they working on now, and what would help?</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>+972549954666</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t>avieladler@gmail.com</t>
+        </is>
+      </c>
       <c r="L5" s="29" t="n"/>
       <c r="M5" s="29" t="n"/>
     </row>
@@ -1814,7 +1838,7 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
@@ -1822,8 +1846,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr"/>
-      <c r="K7" s="26" t="inlineStr"/>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>+972545424895</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>eran.hertzmann@gmail.com</t>
+        </is>
+      </c>
       <c r="L7" s="29" t="n"/>
       <c r="M7" s="29" t="n"/>
     </row>
@@ -1908,7 +1940,7 @@
       </c>
       <c r="H9" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
@@ -1916,7 +1948,11 @@
           <t>Stay current — what are they working on in research now, and what would help?</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr"/>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>+972524056440</t>
+        </is>
+      </c>
       <c r="K9" s="26" t="inlineStr"/>
       <c r="L9" s="29" t="n"/>
       <c r="M9" s="29" t="n"/>
@@ -2049,7 +2085,7 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I12" s="28" t="inlineStr">
@@ -2057,8 +2093,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr"/>
-      <c r="K12" s="26" t="inlineStr"/>
+      <c r="J12" s="26" t="inlineStr">
+        <is>
+          <t>+972524598022</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>michalshilo6@gmail.com</t>
+        </is>
+      </c>
       <c r="L12" s="29" t="n"/>
       <c r="M12" s="29" t="n"/>
     </row>
@@ -2096,7 +2140,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I13" s="28" t="inlineStr">
@@ -2104,8 +2148,16 @@
           <t>Node candidate — founded SendBlocks. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr"/>
-      <c r="K13" s="26" t="inlineStr"/>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>+972545311213</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>mike53il@gmail.com</t>
+        </is>
+      </c>
       <c r="L13" s="29" t="n"/>
       <c r="M13" s="29" t="n"/>
     </row>
@@ -2331,7 +2383,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>email</t>
         </is>
       </c>
       <c r="I18" s="28" t="inlineStr">
@@ -2340,7 +2392,11 @@
         </is>
       </c>
       <c r="J18" s="26" t="inlineStr"/>
-      <c r="K18" s="26" t="inlineStr"/>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t>zviwex@gmail.com</t>
+        </is>
+      </c>
       <c r="L18" s="29" t="n"/>
       <c r="M18" s="29" t="n"/>
     </row>
@@ -2519,7 +2575,7 @@
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I22" s="28" t="inlineStr">
@@ -2527,8 +2583,16 @@
           <t>Stay current — what are they working on in infra-systems now, and what would help?</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr"/>
-      <c r="K22" s="26" t="inlineStr"/>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t>+972548303525</t>
+        </is>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
+        <is>
+          <t>eranhirsch@gmail.com</t>
+        </is>
+      </c>
       <c r="L22" s="29" t="n"/>
       <c r="M22" s="29" t="n"/>
     </row>
@@ -2566,7 +2630,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
@@ -2574,8 +2638,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr"/>
-      <c r="K23" s="26" t="inlineStr"/>
+      <c r="J23" s="26" t="inlineStr">
+        <is>
+          <t>+972507363131</t>
+        </is>
+      </c>
+      <c r="K23" s="26" t="inlineStr">
+        <is>
+          <t>almogx3@gmail.com</t>
+        </is>
+      </c>
       <c r="L23" s="29" t="n"/>
       <c r="M23" s="29" t="n"/>
     </row>
@@ -2707,7 +2779,7 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I26" s="28" t="inlineStr">
@@ -2715,8 +2787,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J26" s="26" t="inlineStr"/>
-      <c r="K26" s="26" t="inlineStr"/>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>+972525892000</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>barmatit@gmail.com</t>
+        </is>
+      </c>
       <c r="L26" s="29" t="n"/>
       <c r="M26" s="29" t="n"/>
     </row>
@@ -2754,7 +2834,7 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I27" s="28" t="inlineStr">
@@ -2762,8 +2842,16 @@
           <t>Node candidate — founded Xcardia. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J27" s="26" t="inlineStr"/>
-      <c r="K27" s="26" t="inlineStr"/>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>+972544345653</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>rousso.benny@gmail.com</t>
+        </is>
+      </c>
       <c r="L27" s="29" t="n"/>
       <c r="M27" s="29" t="n"/>
     </row>
@@ -2895,7 +2983,7 @@
       </c>
       <c r="H30" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I30" s="28" t="inlineStr">
@@ -2903,8 +2991,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr"/>
-      <c r="K30" s="26" t="inlineStr"/>
+      <c r="J30" s="26" t="inlineStr">
+        <is>
+          <t>+972502338655</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>galwiernik@gmail.com</t>
+        </is>
+      </c>
       <c r="L30" s="29" t="n"/>
       <c r="M30" s="29" t="n"/>
     </row>
@@ -2942,7 +3038,7 @@
       </c>
       <c r="H31" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
@@ -2950,8 +3046,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J31" s="26" t="inlineStr"/>
-      <c r="K31" s="26" t="inlineStr"/>
+      <c r="J31" s="26" t="inlineStr">
+        <is>
+          <t>+972508717313</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="inlineStr">
+        <is>
+          <t>yoshpe@gmail.com</t>
+        </is>
+      </c>
       <c r="L31" s="29" t="n"/>
       <c r="M31" s="29" t="n"/>
     </row>
@@ -3036,7 +3140,7 @@
       </c>
       <c r="H33" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
@@ -3044,8 +3148,16 @@
           <t>Node candidate — founded Cabinet (AI workspace). What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J33" s="26" t="inlineStr"/>
-      <c r="K33" s="26" t="inlineStr"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>+972508871171</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>hila4321@gmail.com</t>
+        </is>
+      </c>
       <c r="L33" s="29" t="n"/>
       <c r="M33" s="29" t="n"/>
     </row>
@@ -3083,7 +3195,7 @@
       </c>
       <c r="H34" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I34" s="28" t="inlineStr">
@@ -3091,8 +3203,16 @@
           <t>What can they give — office hours, referrals into Palo Alto Networks, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J34" s="26" t="inlineStr"/>
-      <c r="K34" s="26" t="inlineStr"/>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>+972547260058</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>avielz1199@gmail.com</t>
+        </is>
+      </c>
       <c r="L34" s="29" t="n"/>
       <c r="M34" s="29" t="n"/>
     </row>
@@ -3130,7 +3250,7 @@
       </c>
       <c r="H35" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I35" s="28" t="inlineStr">
@@ -3138,8 +3258,16 @@
           <t>Stay current — what are they working on now, and what would help?</t>
         </is>
       </c>
-      <c r="J35" s="26" t="inlineStr"/>
-      <c r="K35" s="26" t="inlineStr"/>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>+972543315821</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>benzionkossowsky@gmail.com</t>
+        </is>
+      </c>
       <c r="L35" s="29" t="n"/>
       <c r="M35" s="29" t="n"/>
     </row>
@@ -3177,7 +3305,7 @@
       </c>
       <c r="H36" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I36" s="28" t="inlineStr">
@@ -3185,8 +3313,16 @@
           <t>Node candidate — founded Sayata. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr"/>
-      <c r="K36" s="26" t="inlineStr"/>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>+972542421974</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>igolomb@gmail.com</t>
+        </is>
+      </c>
       <c r="L36" s="29" t="n"/>
       <c r="M36" s="29" t="n"/>
     </row>
@@ -3224,7 +3360,7 @@
       </c>
       <c r="H37" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I37" s="28" t="inlineStr">
@@ -3232,8 +3368,16 @@
           <t>Node candidate — founded Medida AI. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr"/>
-      <c r="K37" s="26" t="inlineStr"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>+972528198278</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>jonathan@medida.ai</t>
+        </is>
+      </c>
       <c r="L37" s="29" t="n"/>
       <c r="M37" s="29" t="n"/>
     </row>
@@ -3271,7 +3415,7 @@
       </c>
       <c r="H38" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -3279,8 +3423,16 @@
           <t>What can they give — office hours, referrals into Claroty (DS Team Leader per roster), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr"/>
-      <c r="K38" s="26" t="inlineStr"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>+972506228892</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>eyalhoro6@gmail.com</t>
+        </is>
+      </c>
       <c r="L38" s="29" t="n"/>
       <c r="M38" s="29" t="n"/>
     </row>
@@ -3365,7 +3517,7 @@
       </c>
       <c r="H40" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I40" s="28" t="inlineStr">
@@ -3373,8 +3525,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J40" s="26" t="inlineStr"/>
-      <c r="K40" s="26" t="inlineStr"/>
+      <c r="J40" s="26" t="inlineStr">
+        <is>
+          <t>+972544911254</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>liran.markin@gmail.com</t>
+        </is>
+      </c>
       <c r="L40" s="29" t="n"/>
       <c r="M40" s="29" t="n"/>
     </row>
@@ -3412,7 +3572,7 @@
       </c>
       <c r="H41" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I41" s="28" t="inlineStr">
@@ -3420,8 +3580,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J41" s="26" t="inlineStr"/>
-      <c r="K41" s="26" t="inlineStr"/>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>+972544319975</t>
+        </is>
+      </c>
+      <c r="K41" s="26" t="inlineStr">
+        <is>
+          <t>mikomraz@gmail.com</t>
+        </is>
+      </c>
       <c r="L41" s="29" t="n"/>
       <c r="M41" s="29" t="n"/>
     </row>
@@ -3459,7 +3627,7 @@
       </c>
       <c r="H42" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I42" s="28" t="inlineStr">
@@ -3467,8 +3635,16 @@
           <t>What can they give — office hours, referrals into Remitly (AI/ML), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr"/>
-      <c r="K42" s="26" t="inlineStr"/>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>+972544322242</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>gil.raytan@gmail.com</t>
+        </is>
+      </c>
       <c r="L42" s="29" t="n"/>
       <c r="M42" s="29" t="n"/>
     </row>
@@ -3506,7 +3682,7 @@
       </c>
       <c r="H43" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I43" s="28" t="inlineStr">
@@ -3514,8 +3690,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J43" s="26" t="inlineStr"/>
-      <c r="K43" s="26" t="inlineStr"/>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>+972507711998</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>mor.m.shemesh@gmail.com</t>
+        </is>
+      </c>
       <c r="L43" s="29" t="n"/>
       <c r="M43" s="29" t="n"/>
     </row>
@@ -3553,7 +3737,7 @@
       </c>
       <c r="H44" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -3561,8 +3745,16 @@
           <t>What can they give — office hours, referrals into Q.ai, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J44" s="26" t="inlineStr"/>
-      <c r="K44" s="26" t="inlineStr"/>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>+972528584131</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>idokazma@gmail.com</t>
+        </is>
+      </c>
       <c r="L44" s="29" t="n"/>
       <c r="M44" s="29" t="n"/>
     </row>
@@ -3600,7 +3792,7 @@
       </c>
       <c r="H45" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I45" s="28" t="inlineStr">
@@ -3608,8 +3800,16 @@
           <t>What can they give — office hours, referrals into Glassbox, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J45" s="26" t="inlineStr"/>
-      <c r="K45" s="26" t="inlineStr"/>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>+972547397052</t>
+        </is>
+      </c>
+      <c r="K45" s="26" t="inlineStr">
+        <is>
+          <t>ilan.voronel@gmail.com</t>
+        </is>
+      </c>
       <c r="L45" s="29" t="n"/>
       <c r="M45" s="29" t="n"/>
     </row>
@@ -3647,7 +3847,7 @@
       </c>
       <c r="H46" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I46" s="28" t="inlineStr">
@@ -3655,8 +3855,16 @@
           <t>Stay current — still at Eon.io? What are they working on in infra-systems, and what would help?</t>
         </is>
       </c>
-      <c r="J46" s="26" t="inlineStr"/>
-      <c r="K46" s="26" t="inlineStr"/>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>+972542267010</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
+        <is>
+          <t>liorlevtov@gmail.com</t>
+        </is>
+      </c>
       <c r="L46" s="29" t="n"/>
       <c r="M46" s="29" t="n"/>
     </row>
@@ -3694,7 +3902,7 @@
       </c>
       <c r="H47" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I47" s="28" t="inlineStr">
@@ -3702,8 +3910,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J47" s="26" t="inlineStr"/>
-      <c r="K47" s="26" t="inlineStr"/>
+      <c r="J47" s="26" t="inlineStr">
+        <is>
+          <t>+972546777815</t>
+        </is>
+      </c>
+      <c r="K47" s="26" t="inlineStr">
+        <is>
+          <t>roymoshe23@gmail.com</t>
+        </is>
+      </c>
       <c r="L47" s="29" t="n"/>
       <c r="M47" s="29" t="n"/>
     </row>
@@ -3741,7 +3957,7 @@
       </c>
       <c r="H48" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -3749,8 +3965,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr"/>
-      <c r="K48" s="26" t="inlineStr"/>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>+972544744575</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>tomergoren99@gmail.com</t>
+        </is>
+      </c>
       <c r="L48" s="29" t="n"/>
       <c r="M48" s="29" t="n"/>
     </row>
@@ -3788,7 +4012,7 @@
       </c>
       <c r="H49" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I49" s="28" t="inlineStr">
@@ -3796,8 +4020,16 @@
           <t>What can they give — office hours, referrals into TAU (ex-Amazon), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J49" s="26" t="inlineStr"/>
-      <c r="K49" s="26" t="inlineStr"/>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>+972527564010</t>
+        </is>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t>giga123@gmail.com</t>
+        </is>
+      </c>
       <c r="L49" s="29" t="n"/>
       <c r="M49" s="29" t="n"/>
     </row>
@@ -3835,7 +4067,7 @@
       </c>
       <c r="H50" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I50" s="28" t="inlineStr">
@@ -3843,8 +4075,16 @@
           <t>Stay current — still at Protai? What are they working on in ai-ml, and what would help?</t>
         </is>
       </c>
-      <c r="J50" s="26" t="inlineStr"/>
-      <c r="K50" s="26" t="inlineStr"/>
+      <c r="J50" s="26" t="inlineStr">
+        <is>
+          <t>+972544443440</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="inlineStr">
+        <is>
+          <t>michalran95@gmail.com</t>
+        </is>
+      </c>
       <c r="L50" s="29" t="n"/>
       <c r="M50" s="29" t="n"/>
     </row>
@@ -3882,7 +4122,7 @@
       </c>
       <c r="H51" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I51" s="28" t="inlineStr">
@@ -3890,8 +4130,16 @@
           <t>What can they give — office hours, referrals into Akeyless (ex-System Architect, DriveNets), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J51" s="26" t="inlineStr"/>
-      <c r="K51" s="26" t="inlineStr"/>
+      <c r="J51" s="26" t="inlineStr">
+        <is>
+          <t>+972508112332</t>
+        </is>
+      </c>
+      <c r="K51" s="26" t="inlineStr">
+        <is>
+          <t>omeronn@gmail.com</t>
+        </is>
+      </c>
       <c r="L51" s="29" t="n"/>
       <c r="M51" s="29" t="n"/>
     </row>
@@ -3929,7 +4177,7 @@
       </c>
       <c r="H52" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -3937,8 +4185,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J52" s="26" t="inlineStr"/>
-      <c r="K52" s="26" t="inlineStr"/>
+      <c r="J52" s="26" t="inlineStr">
+        <is>
+          <t>+972528225572</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="inlineStr">
+        <is>
+          <t>gotlib.omri@gmail.com</t>
+        </is>
+      </c>
       <c r="L52" s="29" t="n"/>
       <c r="M52" s="29" t="n"/>
     </row>
@@ -3976,7 +4232,7 @@
       </c>
       <c r="H53" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I53" s="28" t="inlineStr">
@@ -3984,8 +4240,16 @@
           <t>Node candidate — founded Predicta Med. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J53" s="26" t="inlineStr"/>
-      <c r="K53" s="26" t="inlineStr"/>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>+972545551000</t>
+        </is>
+      </c>
+      <c r="K53" s="26" t="inlineStr">
+        <is>
+          <t>benny.getz@gmail.com</t>
+        </is>
+      </c>
       <c r="L53" s="29" t="n"/>
       <c r="M53" s="29" t="n"/>
     </row>
@@ -4023,7 +4287,7 @@
       </c>
       <c r="H54" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -4031,8 +4295,16 @@
           <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr"/>
-      <c r="K54" s="26" t="inlineStr"/>
+      <c r="J54" s="26" t="inlineStr">
+        <is>
+          <t>+972525677675</t>
+        </is>
+      </c>
+      <c r="K54" s="26" t="inlineStr">
+        <is>
+          <t>dolevelb@gmail.com</t>
+        </is>
+      </c>
       <c r="L54" s="29" t="n"/>
       <c r="M54" s="29" t="n"/>
     </row>
@@ -4070,7 +4342,7 @@
       </c>
       <c r="H55" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I55" s="28" t="inlineStr">
@@ -4078,8 +4350,16 @@
           <t>What can they give — office hours, referrals into Datadog, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J55" s="26" t="inlineStr"/>
-      <c r="K55" s="26" t="inlineStr"/>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>+972503039885</t>
+        </is>
+      </c>
+      <c r="K55" s="26" t="inlineStr">
+        <is>
+          <t>rongalay@gmail.com</t>
+        </is>
+      </c>
       <c r="L55" s="29" t="n"/>
       <c r="M55" s="29" t="n"/>
     </row>
@@ -4117,7 +4397,7 @@
       </c>
       <c r="H56" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -4125,8 +4405,16 @@
           <t>Stay current — still at Cyera? What are they working on in security, and what would help?</t>
         </is>
       </c>
-      <c r="J56" s="26" t="inlineStr"/>
-      <c r="K56" s="26" t="inlineStr"/>
+      <c r="J56" s="26" t="inlineStr">
+        <is>
+          <t>+972524447878</t>
+        </is>
+      </c>
+      <c r="K56" s="26" t="inlineStr">
+        <is>
+          <t>peleg87@gmail.com</t>
+        </is>
+      </c>
       <c r="L56" s="29" t="n"/>
       <c r="M56" s="29" t="n"/>
     </row>
@@ -4164,7 +4452,7 @@
       </c>
       <c r="H57" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I57" s="28" t="inlineStr">
@@ -4172,8 +4460,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J57" s="26" t="inlineStr"/>
-      <c r="K57" s="26" t="inlineStr"/>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>+972543134989</t>
+        </is>
+      </c>
+      <c r="K57" s="26" t="inlineStr">
+        <is>
+          <t>nadav.claude.cohen@gmail.com</t>
+        </is>
+      </c>
       <c r="L57" s="29" t="n"/>
       <c r="M57" s="29" t="n"/>
     </row>
@@ -4258,7 +4554,7 @@
       </c>
       <c r="H59" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I59" s="28" t="inlineStr">
@@ -4266,8 +4562,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J59" s="26" t="inlineStr"/>
-      <c r="K59" s="26" t="inlineStr"/>
+      <c r="J59" s="26" t="inlineStr">
+        <is>
+          <t>+972544702148</t>
+        </is>
+      </c>
+      <c r="K59" s="26" t="inlineStr">
+        <is>
+          <t>sharon.brizinov@gmail.com</t>
+        </is>
+      </c>
       <c r="L59" s="29" t="n"/>
       <c r="M59" s="29" t="n"/>
     </row>
@@ -4305,7 +4609,7 @@
       </c>
       <c r="H60" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I60" s="28" t="inlineStr">
@@ -4313,8 +4617,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J60" s="26" t="inlineStr"/>
-      <c r="K60" s="26" t="inlineStr"/>
+      <c r="J60" s="26" t="inlineStr">
+        <is>
+          <t>+972586392129</t>
+        </is>
+      </c>
+      <c r="K60" s="26" t="inlineStr">
+        <is>
+          <t>orenfine@gmail.com</t>
+        </is>
+      </c>
       <c r="L60" s="29" t="n"/>
       <c r="M60" s="29" t="n"/>
     </row>
@@ -4352,7 +4664,7 @@
       </c>
       <c r="H61" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I61" s="28" t="inlineStr">
@@ -4360,8 +4672,16 @@
           <t>Node candidate — founded TrueNorth Systems. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J61" s="26" t="inlineStr"/>
-      <c r="K61" s="26" t="inlineStr"/>
+      <c r="J61" s="26" t="inlineStr">
+        <is>
+          <t>+972545330111</t>
+        </is>
+      </c>
+      <c r="K61" s="26" t="inlineStr">
+        <is>
+          <t>shlomo@lahavs.com</t>
+        </is>
+      </c>
       <c r="L61" s="29" t="n"/>
       <c r="M61" s="29" t="n"/>
     </row>
@@ -4399,7 +4719,7 @@
       </c>
       <c r="H62" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -4407,8 +4727,16 @@
           <t>What can they give — office hours, referrals into Orca Security, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J62" s="26" t="inlineStr"/>
-      <c r="K62" s="26" t="inlineStr"/>
+      <c r="J62" s="26" t="inlineStr">
+        <is>
+          <t>+972538271198</t>
+        </is>
+      </c>
+      <c r="K62" s="26" t="inlineStr">
+        <is>
+          <t>tzahpahima123@gmail.com</t>
+        </is>
+      </c>
       <c r="L62" s="29" t="n"/>
       <c r="M62" s="29" t="n"/>
     </row>
@@ -4446,7 +4774,7 @@
       </c>
       <c r="H63" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I63" s="28" t="inlineStr">
@@ -4454,8 +4782,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J63" s="26" t="inlineStr"/>
-      <c r="K63" s="26" t="inlineStr"/>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>+972529508555</t>
+        </is>
+      </c>
+      <c r="K63" s="26" t="inlineStr">
+        <is>
+          <t>yakov.kosoburd@gmail.com</t>
+        </is>
+      </c>
       <c r="L63" s="29" t="n"/>
       <c r="M63" s="29" t="n"/>
     </row>
@@ -4493,7 +4829,7 @@
       </c>
       <c r="H64" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -4501,8 +4837,16 @@
           <t>Stay current — still at Vayyar Imaging? What are they working on in ai-ml, and what would help?</t>
         </is>
       </c>
-      <c r="J64" s="26" t="inlineStr"/>
-      <c r="K64" s="26" t="inlineStr"/>
+      <c r="J64" s="26" t="inlineStr">
+        <is>
+          <t>+972542566787</t>
+        </is>
+      </c>
+      <c r="K64" s="26" t="inlineStr">
+        <is>
+          <t>shachar.resisi@gmail.com</t>
+        </is>
+      </c>
       <c r="L64" s="29" t="n"/>
       <c r="M64" s="29" t="n"/>
     </row>
@@ -4540,7 +4884,7 @@
       </c>
       <c r="H65" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I65" s="28" t="inlineStr">
@@ -4548,8 +4892,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J65" s="26" t="inlineStr"/>
-      <c r="K65" s="26" t="inlineStr"/>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>+972525621097</t>
+        </is>
+      </c>
+      <c r="K65" s="26" t="inlineStr">
+        <is>
+          <t>yanivsh002@gmail.com</t>
+        </is>
+      </c>
       <c r="L65" s="29" t="n"/>
       <c r="M65" s="29" t="n"/>
     </row>
@@ -4587,7 +4939,7 @@
       </c>
       <c r="H66" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -4595,8 +4947,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J66" s="26" t="inlineStr"/>
-      <c r="K66" s="26" t="inlineStr"/>
+      <c r="J66" s="26" t="inlineStr">
+        <is>
+          <t>+972544319991</t>
+        </is>
+      </c>
+      <c r="K66" s="26" t="inlineStr">
+        <is>
+          <t>assafmonsa@gmail.com</t>
+        </is>
+      </c>
       <c r="L66" s="29" t="n"/>
       <c r="M66" s="29" t="n"/>
     </row>
@@ -4634,7 +4994,7 @@
       </c>
       <c r="H67" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I67" s="28" t="inlineStr">
@@ -4642,8 +5002,16 @@
           <t>Node candidate — founded Snyk. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J67" s="26" t="inlineStr"/>
-      <c r="K67" s="26" t="inlineStr"/>
+      <c r="J67" s="26" t="inlineStr">
+        <is>
+          <t>+972507616594</t>
+        </is>
+      </c>
+      <c r="K67" s="26" t="inlineStr">
+        <is>
+          <t>danny.grander@gmail.com</t>
+        </is>
+      </c>
       <c r="L67" s="29" t="n"/>
       <c r="M67" s="29" t="n"/>
     </row>
@@ -4681,7 +5049,7 @@
       </c>
       <c r="H68" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -4689,8 +5057,16 @@
           <t>What can they give — office hours, referrals into PureSec (Architect @ PAN per roster), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J68" s="26" t="inlineStr"/>
-      <c r="K68" s="26" t="inlineStr"/>
+      <c r="J68" s="26" t="inlineStr">
+        <is>
+          <t>+972547225688</t>
+        </is>
+      </c>
+      <c r="K68" s="26" t="inlineStr">
+        <is>
+          <t>yurishapira@gmail.com</t>
+        </is>
+      </c>
       <c r="L68" s="29" t="n"/>
       <c r="M68" s="29" t="n"/>
     </row>
@@ -4728,7 +5104,7 @@
       </c>
       <c r="H69" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I69" s="28" t="inlineStr">
@@ -4736,8 +5112,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J69" s="26" t="inlineStr"/>
-      <c r="K69" s="26" t="inlineStr"/>
+      <c r="J69" s="26" t="inlineStr">
+        <is>
+          <t>+972543990302</t>
+        </is>
+      </c>
+      <c r="K69" s="26" t="inlineStr">
+        <is>
+          <t>cohenadi02@gmail.com</t>
+        </is>
+      </c>
       <c r="L69" s="29" t="n"/>
       <c r="M69" s="29" t="n"/>
     </row>
@@ -4869,7 +5253,7 @@
       </c>
       <c r="H72" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I72" s="28" t="inlineStr">
@@ -4877,8 +5261,16 @@
           <t>What can they give — office hours, referrals into Cyera, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J72" s="26" t="inlineStr"/>
-      <c r="K72" s="26" t="inlineStr"/>
+      <c r="J72" s="26" t="inlineStr">
+        <is>
+          <t>+972546611903</t>
+        </is>
+      </c>
+      <c r="K72" s="26" t="inlineStr">
+        <is>
+          <t>alonwolfy@gmail.com</t>
+        </is>
+      </c>
       <c r="L72" s="29" t="n"/>
       <c r="M72" s="29" t="n"/>
     </row>
@@ -4916,7 +5308,7 @@
       </c>
       <c r="H73" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I73" s="28" t="inlineStr">
@@ -4924,8 +5316,16 @@
           <t>What can they give — office hours, referrals into Zafran, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J73" s="26" t="inlineStr"/>
-      <c r="K73" s="26" t="inlineStr"/>
+      <c r="J73" s="26" t="inlineStr">
+        <is>
+          <t>+972545301526</t>
+        </is>
+      </c>
+      <c r="K73" s="26" t="inlineStr">
+        <is>
+          <t>relrelbachar@gmail.com</t>
+        </is>
+      </c>
       <c r="L73" s="29" t="n"/>
       <c r="M73" s="29" t="n"/>
     </row>
@@ -5010,7 +5410,7 @@
       </c>
       <c r="H75" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I75" s="28" t="inlineStr">
@@ -5018,8 +5418,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J75" s="26" t="inlineStr"/>
-      <c r="K75" s="26" t="inlineStr"/>
+      <c r="J75" s="26" t="inlineStr">
+        <is>
+          <t>+972526207606</t>
+        </is>
+      </c>
+      <c r="K75" s="26" t="inlineStr">
+        <is>
+          <t>avraham.berr@gmail.com</t>
+        </is>
+      </c>
       <c r="L75" s="29" t="n"/>
       <c r="M75" s="29" t="n"/>
     </row>
@@ -5104,7 +5512,7 @@
       </c>
       <c r="H77" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I77" s="28" t="inlineStr">
@@ -5112,8 +5520,16 @@
           <t>Node candidate — founded SendBlocks. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J77" s="26" t="inlineStr"/>
-      <c r="K77" s="26" t="inlineStr"/>
+      <c r="J77" s="26" t="inlineStr">
+        <is>
+          <t>+972545311213</t>
+        </is>
+      </c>
+      <c r="K77" s="26" t="inlineStr">
+        <is>
+          <t>mike53il@gmail.com</t>
+        </is>
+      </c>
       <c r="L77" s="29" t="n"/>
       <c r="M77" s="29" t="n"/>
     </row>
@@ -5198,7 +5614,7 @@
       </c>
       <c r="H79" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I79" s="28" t="inlineStr">
@@ -5206,8 +5622,16 @@
           <t>What can they give — office hours, referrals into Walmart Global Tech, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J79" s="26" t="inlineStr"/>
-      <c r="K79" s="26" t="inlineStr"/>
+      <c r="J79" s="26" t="inlineStr">
+        <is>
+          <t>+972523872832</t>
+        </is>
+      </c>
+      <c r="K79" s="26" t="inlineStr">
+        <is>
+          <t>gmelamed@gmail.com</t>
+        </is>
+      </c>
       <c r="L79" s="29" t="n"/>
       <c r="M79" s="29" t="n"/>
     </row>
@@ -5245,7 +5669,7 @@
       </c>
       <c r="H80" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I80" s="28" t="inlineStr">
@@ -5253,8 +5677,16 @@
           <t>Stay current — still at Technion (coding/information theory, DNA storage lab)? What are they working on in research, and what would help?</t>
         </is>
       </c>
-      <c r="J80" s="26" t="inlineStr"/>
-      <c r="K80" s="26" t="inlineStr"/>
+      <c r="J80" s="26" t="inlineStr">
+        <is>
+          <t>+972546540789</t>
+        </is>
+      </c>
+      <c r="K80" s="26" t="inlineStr">
+        <is>
+          <t>adir.kob@gmail.com</t>
+        </is>
+      </c>
       <c r="L80" s="29" t="n"/>
       <c r="M80" s="29" t="n"/>
     </row>
@@ -5292,7 +5724,7 @@
       </c>
       <c r="H81" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>email</t>
         </is>
       </c>
       <c r="I81" s="28" t="inlineStr">
@@ -5301,7 +5733,11 @@
         </is>
       </c>
       <c r="J81" s="26" t="inlineStr"/>
-      <c r="K81" s="26" t="inlineStr"/>
+      <c r="K81" s="26" t="inlineStr">
+        <is>
+          <t>zviwex@gmail.com</t>
+        </is>
+      </c>
       <c r="L81" s="29" t="n"/>
       <c r="M81" s="29" t="n"/>
     </row>
@@ -5339,7 +5775,7 @@
       </c>
       <c r="H82" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I82" s="28" t="inlineStr">
@@ -5347,8 +5783,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J82" s="26" t="inlineStr"/>
-      <c r="K82" s="26" t="inlineStr"/>
+      <c r="J82" s="26" t="inlineStr">
+        <is>
+          <t>+972507363131</t>
+        </is>
+      </c>
+      <c r="K82" s="26" t="inlineStr">
+        <is>
+          <t>almogx3@gmail.com</t>
+        </is>
+      </c>
       <c r="L82" s="29" t="n"/>
       <c r="M82" s="29" t="n"/>
     </row>
@@ -5386,7 +5830,7 @@
       </c>
       <c r="H83" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I83" s="28" t="inlineStr">
@@ -5394,8 +5838,16 @@
           <t>What can they give — office hours, referrals into Wiz, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J83" s="26" t="inlineStr"/>
-      <c r="K83" s="26" t="inlineStr"/>
+      <c r="J83" s="26" t="inlineStr">
+        <is>
+          <t>+972542172153</t>
+        </is>
+      </c>
+      <c r="K83" s="26" t="inlineStr">
+        <is>
+          <t>guy.goldenberg@gmail.com</t>
+        </is>
+      </c>
       <c r="L83" s="29" t="n"/>
       <c r="M83" s="29" t="n"/>
     </row>
@@ -5433,7 +5885,7 @@
       </c>
       <c r="H84" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -5441,8 +5893,16 @@
           <t>What can they give — office hours, referrals into Technion Autonomous Systems (POMDP planning), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J84" s="26" t="inlineStr"/>
-      <c r="K84" s="26" t="inlineStr"/>
+      <c r="J84" s="26" t="inlineStr">
+        <is>
+          <t>+972523059999</t>
+        </is>
+      </c>
+      <c r="K84" s="26" t="inlineStr">
+        <is>
+          <t>idanly98@gmail.com</t>
+        </is>
+      </c>
       <c r="L84" s="29" t="n"/>
       <c r="M84" s="29" t="n"/>
     </row>
@@ -5480,7 +5940,7 @@
       </c>
       <c r="H85" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I85" s="28" t="inlineStr">
@@ -5488,8 +5948,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J85" s="26" t="inlineStr"/>
-      <c r="K85" s="26" t="inlineStr"/>
+      <c r="J85" s="26" t="inlineStr">
+        <is>
+          <t>+972525892000</t>
+        </is>
+      </c>
+      <c r="K85" s="26" t="inlineStr">
+        <is>
+          <t>barmatit@gmail.com</t>
+        </is>
+      </c>
       <c r="L85" s="29" t="n"/>
       <c r="M85" s="29" t="n"/>
     </row>
@@ -5527,7 +5995,7 @@
       </c>
       <c r="H86" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I86" s="28" t="inlineStr">
@@ -5535,8 +6003,16 @@
           <t>What can they give — office hours, referrals into Wiz, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J86" s="26" t="inlineStr"/>
-      <c r="K86" s="26" t="inlineStr"/>
+      <c r="J86" s="26" t="inlineStr">
+        <is>
+          <t>+972504787314</t>
+        </is>
+      </c>
+      <c r="K86" s="26" t="inlineStr">
+        <is>
+          <t>itamar.gilad@wiz.io</t>
+        </is>
+      </c>
       <c r="L86" s="29" t="n"/>
       <c r="M86" s="29" t="n"/>
     </row>
@@ -5574,7 +6050,7 @@
       </c>
       <c r="H87" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I87" s="28" t="inlineStr">
@@ -5582,8 +6058,16 @@
           <t>What can they give — office hours, referrals into nT-Tao (compact fusion), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J87" s="26" t="inlineStr"/>
-      <c r="K87" s="26" t="inlineStr"/>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>+972504039870</t>
+        </is>
+      </c>
+      <c r="K87" s="26" t="inlineStr">
+        <is>
+          <t>itaigiss@gmail.com</t>
+        </is>
+      </c>
       <c r="L87" s="29" t="n"/>
       <c r="M87" s="29" t="n"/>
     </row>
@@ -5621,16 +6105,24 @@
       </c>
       <c r="H88" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I88" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J88" s="26" t="inlineStr"/>
-      <c r="K88" s="26" t="inlineStr"/>
+          <t>Stay current — what are they working on now, and what would help?</t>
+        </is>
+      </c>
+      <c r="J88" s="26" t="inlineStr">
+        <is>
+          <t>+972525591311</t>
+        </is>
+      </c>
+      <c r="K88" s="26" t="inlineStr">
+        <is>
+          <t>amirbalva@gmail.com</t>
+        </is>
+      </c>
       <c r="L88" s="29" t="n"/>
       <c r="M88" s="29" t="n"/>
     </row>
@@ -5668,7 +6160,7 @@
       </c>
       <c r="H89" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I89" s="28" t="inlineStr">
@@ -5676,8 +6168,16 @@
           <t>Node candidate — founded Xcardia. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J89" s="26" t="inlineStr"/>
-      <c r="K89" s="26" t="inlineStr"/>
+      <c r="J89" s="26" t="inlineStr">
+        <is>
+          <t>+972544345653</t>
+        </is>
+      </c>
+      <c r="K89" s="26" t="inlineStr">
+        <is>
+          <t>rousso.benny@gmail.com</t>
+        </is>
+      </c>
       <c r="L89" s="29" t="n"/>
       <c r="M89" s="29" t="n"/>
     </row>
@@ -5715,7 +6215,7 @@
       </c>
       <c r="H90" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I90" s="28" t="inlineStr">
@@ -5723,8 +6223,16 @@
           <t>What can they give — office hours, referrals into Weizmann (Milo lab, Nature co-author), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J90" s="26" t="inlineStr"/>
-      <c r="K90" s="26" t="inlineStr"/>
+      <c r="J90" s="26" t="inlineStr">
+        <is>
+          <t>+972546326372</t>
+        </is>
+      </c>
+      <c r="K90" s="26" t="inlineStr">
+        <is>
+          <t>liadgo2@gmail.com</t>
+        </is>
+      </c>
       <c r="L90" s="29" t="n"/>
       <c r="M90" s="29" t="n"/>
     </row>
@@ -5762,16 +6270,24 @@
       </c>
       <c r="H91" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I91" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J91" s="26" t="inlineStr"/>
-      <c r="K91" s="26" t="inlineStr"/>
+          <t>Stay current — still at Franklin by QIAGEN? What are they working on, and what would help?</t>
+        </is>
+      </c>
+      <c r="J91" s="26" t="inlineStr">
+        <is>
+          <t>+972522344098</t>
+        </is>
+      </c>
+      <c r="K91" s="26" t="inlineStr">
+        <is>
+          <t>amitai.nevo2@gmail.com</t>
+        </is>
+      </c>
       <c r="L91" s="29" t="n"/>
       <c r="M91" s="29" t="n"/>
     </row>
@@ -5809,7 +6325,7 @@
       </c>
       <c r="H92" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I92" s="28" t="inlineStr">
@@ -5817,8 +6333,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J92" s="26" t="inlineStr"/>
-      <c r="K92" s="26" t="inlineStr"/>
+      <c r="J92" s="26" t="inlineStr">
+        <is>
+          <t>+972502338655</t>
+        </is>
+      </c>
+      <c r="K92" s="26" t="inlineStr">
+        <is>
+          <t>galwiernik@gmail.com</t>
+        </is>
+      </c>
       <c r="L92" s="29" t="n"/>
       <c r="M92" s="29" t="n"/>
     </row>
@@ -5856,7 +6380,7 @@
       </c>
       <c r="H93" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I93" s="28" t="inlineStr">
@@ -5864,8 +6388,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J93" s="26" t="inlineStr"/>
-      <c r="K93" s="26" t="inlineStr"/>
+      <c r="J93" s="26" t="inlineStr">
+        <is>
+          <t>+972508717313</t>
+        </is>
+      </c>
+      <c r="K93" s="26" t="inlineStr">
+        <is>
+          <t>yoshpe@gmail.com</t>
+        </is>
+      </c>
       <c r="L93" s="29" t="n"/>
       <c r="M93" s="29" t="n"/>
     </row>
@@ -5903,7 +6435,7 @@
       </c>
       <c r="H94" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -5911,8 +6443,16 @@
           <t>What can they give — office hours, referrals into Vayyar Imaging, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J94" s="26" t="inlineStr"/>
-      <c r="K94" s="26" t="inlineStr"/>
+      <c r="J94" s="26" t="inlineStr">
+        <is>
+          <t>+972544321050</t>
+        </is>
+      </c>
+      <c r="K94" s="26" t="inlineStr">
+        <is>
+          <t>mark.popov@gmail.com</t>
+        </is>
+      </c>
       <c r="L94" s="29" t="n"/>
       <c r="M94" s="29" t="n"/>
     </row>
@@ -5950,7 +6490,7 @@
       </c>
       <c r="H95" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I95" s="28" t="inlineStr">
@@ -5958,8 +6498,16 @@
           <t>What can they give — office hours, referrals into OpenEyes, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J95" s="26" t="inlineStr"/>
-      <c r="K95" s="26" t="inlineStr"/>
+      <c r="J95" s="26" t="inlineStr">
+        <is>
+          <t>+972545221060</t>
+        </is>
+      </c>
+      <c r="K95" s="26" t="inlineStr">
+        <is>
+          <t>matan.shoef@gmail.com</t>
+        </is>
+      </c>
       <c r="L95" s="29" t="n"/>
       <c r="M95" s="29" t="n"/>
     </row>
@@ -6044,7 +6592,7 @@
       </c>
       <c r="H97" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I97" s="28" t="inlineStr">
@@ -6052,8 +6600,16 @@
           <t>Node candidate — founded Cabinet (AI workspace). What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J97" s="26" t="inlineStr"/>
-      <c r="K97" s="26" t="inlineStr"/>
+      <c r="J97" s="26" t="inlineStr">
+        <is>
+          <t>+972508871171</t>
+        </is>
+      </c>
+      <c r="K97" s="26" t="inlineStr">
+        <is>
+          <t>hila4321@gmail.com</t>
+        </is>
+      </c>
       <c r="L97" s="29" t="n"/>
       <c r="M97" s="29" t="n"/>
     </row>
@@ -6091,7 +6647,7 @@
       </c>
       <c r="H98" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I98" s="28" t="inlineStr">
@@ -6099,8 +6655,16 @@
           <t>Node candidate — founded Sayata. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J98" s="26" t="inlineStr"/>
-      <c r="K98" s="26" t="inlineStr"/>
+      <c r="J98" s="26" t="inlineStr">
+        <is>
+          <t>+972542421974</t>
+        </is>
+      </c>
+      <c r="K98" s="26" t="inlineStr">
+        <is>
+          <t>igolomb@gmail.com</t>
+        </is>
+      </c>
       <c r="L98" s="29" t="n"/>
       <c r="M98" s="29" t="n"/>
     </row>
@@ -6138,7 +6702,7 @@
       </c>
       <c r="H99" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I99" s="28" t="inlineStr">
@@ -6146,8 +6710,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J99" s="26" t="inlineStr"/>
-      <c r="K99" s="26" t="inlineStr"/>
+      <c r="J99" s="26" t="inlineStr">
+        <is>
+          <t>+972526351833</t>
+        </is>
+      </c>
+      <c r="K99" s="26" t="inlineStr">
+        <is>
+          <t>avichayr@gmail.com</t>
+        </is>
+      </c>
       <c r="L99" s="29" t="n"/>
       <c r="M99" s="29" t="n"/>
     </row>
@@ -6185,7 +6757,7 @@
       </c>
       <c r="H100" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I100" s="28" t="inlineStr">
@@ -6193,8 +6765,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J100" s="26" t="inlineStr"/>
-      <c r="K100" s="26" t="inlineStr"/>
+      <c r="J100" s="26" t="inlineStr">
+        <is>
+          <t>+972545424895</t>
+        </is>
+      </c>
+      <c r="K100" s="26" t="inlineStr">
+        <is>
+          <t>eran.hertzmann@gmail.com</t>
+        </is>
+      </c>
       <c r="L100" s="29" t="n"/>
       <c r="M100" s="29" t="n"/>
     </row>
@@ -6279,7 +6859,7 @@
       </c>
       <c r="H102" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I102" s="28" t="inlineStr">
@@ -6287,8 +6867,16 @@
           <t>Node candidate — founded Medida AI. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J102" s="26" t="inlineStr"/>
-      <c r="K102" s="26" t="inlineStr"/>
+      <c r="J102" s="26" t="inlineStr">
+        <is>
+          <t>+972528198278</t>
+        </is>
+      </c>
+      <c r="K102" s="26" t="inlineStr">
+        <is>
+          <t>jonathan@medida.ai</t>
+        </is>
+      </c>
       <c r="L102" s="29" t="n"/>
       <c r="M102" s="29" t="n"/>
     </row>
@@ -6326,7 +6914,7 @@
       </c>
       <c r="H103" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I103" s="28" t="inlineStr">
@@ -6334,8 +6922,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J103" s="26" t="inlineStr"/>
-      <c r="K103" s="26" t="inlineStr"/>
+      <c r="J103" s="26" t="inlineStr">
+        <is>
+          <t>+972544911254</t>
+        </is>
+      </c>
+      <c r="K103" s="26" t="inlineStr">
+        <is>
+          <t>liran.markin@gmail.com</t>
+        </is>
+      </c>
       <c r="L103" s="29" t="n"/>
       <c r="M103" s="29" t="n"/>
     </row>
@@ -6373,7 +6969,7 @@
       </c>
       <c r="H104" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I104" s="28" t="inlineStr">
@@ -6381,8 +6977,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J104" s="26" t="inlineStr"/>
-      <c r="K104" s="26" t="inlineStr"/>
+      <c r="J104" s="26" t="inlineStr">
+        <is>
+          <t>+972524598022</t>
+        </is>
+      </c>
+      <c r="K104" s="26" t="inlineStr">
+        <is>
+          <t>michalshilo6@gmail.com</t>
+        </is>
+      </c>
       <c r="L104" s="29" t="n"/>
       <c r="M104" s="29" t="n"/>
     </row>
@@ -6467,7 +7071,7 @@
       </c>
       <c r="H106" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I106" s="28" t="inlineStr">
@@ -6475,8 +7079,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J106" s="26" t="inlineStr"/>
-      <c r="K106" s="26" t="inlineStr"/>
+      <c r="J106" s="26" t="inlineStr">
+        <is>
+          <t>+972544319975</t>
+        </is>
+      </c>
+      <c r="K106" s="26" t="inlineStr">
+        <is>
+          <t>mikomraz@gmail.com</t>
+        </is>
+      </c>
       <c r="L106" s="29" t="n"/>
       <c r="M106" s="29" t="n"/>
     </row>
@@ -6514,16 +7126,24 @@
       </c>
       <c r="H107" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I107" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J107" s="26" t="inlineStr"/>
-      <c r="K107" s="26" t="inlineStr"/>
+          <t>Stay current — still at Stealth? What are they working on, and what would help?</t>
+        </is>
+      </c>
+      <c r="J107" s="26" t="inlineStr">
+        <is>
+          <t>+972544961009</t>
+        </is>
+      </c>
+      <c r="K107" s="26" t="inlineStr">
+        <is>
+          <t>davidroyshasha@gmail.com</t>
+        </is>
+      </c>
       <c r="L107" s="29" t="n"/>
       <c r="M107" s="29" t="n"/>
     </row>
@@ -6608,7 +7228,7 @@
       </c>
       <c r="H109" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I109" s="28" t="inlineStr">
@@ -6616,8 +7236,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J109" s="26" t="inlineStr"/>
-      <c r="K109" s="26" t="inlineStr"/>
+      <c r="J109" s="26" t="inlineStr">
+        <is>
+          <t>+972507711998</t>
+        </is>
+      </c>
+      <c r="K109" s="26" t="inlineStr">
+        <is>
+          <t>mor.m.shemesh@gmail.com</t>
+        </is>
+      </c>
       <c r="L109" s="29" t="n"/>
       <c r="M109" s="29" t="n"/>
     </row>
@@ -6655,7 +7283,7 @@
       </c>
       <c r="H110" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I110" s="28" t="inlineStr">
@@ -6663,8 +7291,16 @@
           <t>Stay current — still at Carefam (AI healthcare hiring, $10.5M raised)? What are they working on in ai-ml, and what would help?</t>
         </is>
       </c>
-      <c r="J110" s="26" t="inlineStr"/>
-      <c r="K110" s="26" t="inlineStr"/>
+      <c r="J110" s="26" t="inlineStr">
+        <is>
+          <t>+972545258759</t>
+        </is>
+      </c>
+      <c r="K110" s="26" t="inlineStr">
+        <is>
+          <t>hilleltwersky@gmail.com</t>
+        </is>
+      </c>
       <c r="L110" s="29" t="n"/>
       <c r="M110" s="29" t="n"/>
     </row>
@@ -6796,7 +7432,7 @@
       </c>
       <c r="H113" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I113" s="28" t="inlineStr">
@@ -6804,8 +7440,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J113" s="26" t="inlineStr"/>
-      <c r="K113" s="26" t="inlineStr"/>
+      <c r="J113" s="26" t="inlineStr">
+        <is>
+          <t>+972546777815</t>
+        </is>
+      </c>
+      <c r="K113" s="26" t="inlineStr">
+        <is>
+          <t>roymoshe23@gmail.com</t>
+        </is>
+      </c>
       <c r="L113" s="29" t="n"/>
       <c r="M113" s="29" t="n"/>
     </row>
@@ -6843,7 +7487,7 @@
       </c>
       <c r="H114" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I114" s="28" t="inlineStr">
@@ -6851,8 +7495,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J114" s="26" t="inlineStr"/>
-      <c r="K114" s="26" t="inlineStr"/>
+      <c r="J114" s="26" t="inlineStr">
+        <is>
+          <t>+972544744575</t>
+        </is>
+      </c>
+      <c r="K114" s="26" t="inlineStr">
+        <is>
+          <t>tomergoren99@gmail.com</t>
+        </is>
+      </c>
       <c r="L114" s="29" t="n"/>
       <c r="M114" s="29" t="n"/>
     </row>
@@ -6937,7 +7589,7 @@
       </c>
       <c r="H116" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I116" s="28" t="inlineStr">
@@ -6945,8 +7597,16 @@
           <t>Node candidate — founded Predicta Med. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J116" s="26" t="inlineStr"/>
-      <c r="K116" s="26" t="inlineStr"/>
+      <c r="J116" s="26" t="inlineStr">
+        <is>
+          <t>+972545551000</t>
+        </is>
+      </c>
+      <c r="K116" s="26" t="inlineStr">
+        <is>
+          <t>benny.getz@gmail.com</t>
+        </is>
+      </c>
       <c r="L116" s="29" t="n"/>
       <c r="M116" s="29" t="n"/>
     </row>
@@ -6984,7 +7644,7 @@
       </c>
       <c r="H117" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I117" s="28" t="inlineStr">
@@ -6992,8 +7652,16 @@
           <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J117" s="26" t="inlineStr"/>
-      <c r="K117" s="26" t="inlineStr"/>
+      <c r="J117" s="26" t="inlineStr">
+        <is>
+          <t>+972525677675</t>
+        </is>
+      </c>
+      <c r="K117" s="26" t="inlineStr">
+        <is>
+          <t>dolevelb@gmail.com</t>
+        </is>
+      </c>
       <c r="L117" s="29" t="n"/>
       <c r="M117" s="29" t="n"/>
     </row>
@@ -7031,16 +7699,24 @@
       </c>
       <c r="H118" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I118" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J118" s="26" t="inlineStr"/>
-      <c r="K118" s="26" t="inlineStr"/>
+          <t>Stay current — still at Toga Networks-a Huawei Company? What are they working on, and what would help?</t>
+        </is>
+      </c>
+      <c r="J118" s="26" t="inlineStr">
+        <is>
+          <t>+972523322722</t>
+        </is>
+      </c>
+      <c r="K118" s="26" t="inlineStr">
+        <is>
+          <t>ibentsion@gmail.com</t>
+        </is>
+      </c>
       <c r="L118" s="29" t="n"/>
       <c r="M118" s="29" t="n"/>
     </row>
@@ -7125,7 +7801,7 @@
       </c>
       <c r="H120" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I120" s="28" t="inlineStr">
@@ -7133,8 +7809,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J120" s="26" t="inlineStr"/>
-      <c r="K120" s="26" t="inlineStr"/>
+      <c r="J120" s="26" t="inlineStr">
+        <is>
+          <t>+972543134989</t>
+        </is>
+      </c>
+      <c r="K120" s="26" t="inlineStr">
+        <is>
+          <t>nadav.claude.cohen@gmail.com</t>
+        </is>
+      </c>
       <c r="L120" s="29" t="n"/>
       <c r="M120" s="29" t="n"/>
     </row>
@@ -7172,7 +7856,7 @@
       </c>
       <c r="H121" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I121" s="28" t="inlineStr">
@@ -7180,8 +7864,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J121" s="26" t="inlineStr"/>
-      <c r="K121" s="26" t="inlineStr"/>
+      <c r="J121" s="26" t="inlineStr">
+        <is>
+          <t>+972586392129</t>
+        </is>
+      </c>
+      <c r="K121" s="26" t="inlineStr">
+        <is>
+          <t>orenfine@gmail.com</t>
+        </is>
+      </c>
       <c r="L121" s="29" t="n"/>
       <c r="M121" s="29" t="n"/>
     </row>
@@ -7219,16 +7911,24 @@
       </c>
       <c r="H122" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I122" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J122" s="26" t="inlineStr"/>
-      <c r="K122" s="26" t="inlineStr"/>
+          <t>Stay current — what are they working on now, and what would help?</t>
+        </is>
+      </c>
+      <c r="J122" s="26" t="inlineStr">
+        <is>
+          <t>+972503028929</t>
+        </is>
+      </c>
+      <c r="K122" s="26" t="inlineStr">
+        <is>
+          <t>ilan3580@gmail.com</t>
+        </is>
+      </c>
       <c r="L122" s="29" t="n"/>
       <c r="M122" s="29" t="n"/>
     </row>
@@ -7360,7 +8060,7 @@
       </c>
       <c r="H125" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I125" s="28" t="inlineStr">
@@ -7368,8 +8068,16 @@
           <t>Node candidate — founded TrueNorth Systems. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J125" s="26" t="inlineStr"/>
-      <c r="K125" s="26" t="inlineStr"/>
+      <c r="J125" s="26" t="inlineStr">
+        <is>
+          <t>+972545330111</t>
+        </is>
+      </c>
+      <c r="K125" s="26" t="inlineStr">
+        <is>
+          <t>shlomo@lahavs.com</t>
+        </is>
+      </c>
       <c r="L125" s="29" t="n"/>
       <c r="M125" s="29" t="n"/>
     </row>
@@ -7407,7 +8115,7 @@
       </c>
       <c r="H126" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I126" s="28" t="inlineStr">
@@ -7415,8 +8123,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J126" s="26" t="inlineStr"/>
-      <c r="K126" s="26" t="inlineStr"/>
+      <c r="J126" s="26" t="inlineStr">
+        <is>
+          <t>+972544319991</t>
+        </is>
+      </c>
+      <c r="K126" s="26" t="inlineStr">
+        <is>
+          <t>assafmonsa@gmail.com</t>
+        </is>
+      </c>
       <c r="L126" s="29" t="n"/>
       <c r="M126" s="29" t="n"/>
     </row>
@@ -7501,7 +8217,7 @@
       </c>
       <c r="H128" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I128" s="28" t="inlineStr">
@@ -7509,8 +8225,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J128" s="26" t="inlineStr"/>
-      <c r="K128" s="26" t="inlineStr"/>
+      <c r="J128" s="26" t="inlineStr">
+        <is>
+          <t>+972525621097</t>
+        </is>
+      </c>
+      <c r="K128" s="26" t="inlineStr">
+        <is>
+          <t>yanivsh002@gmail.com</t>
+        </is>
+      </c>
       <c r="L128" s="29" t="n"/>
       <c r="M128" s="29" t="n"/>
     </row>
@@ -7548,16 +8272,24 @@
       </c>
       <c r="H129" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I129" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J129" s="26" t="inlineStr"/>
-      <c r="K129" s="26" t="inlineStr"/>
+          <t>Stay current — what are they working on now, and what would help?</t>
+        </is>
+      </c>
+      <c r="J129" s="26" t="inlineStr">
+        <is>
+          <t>+972529280436</t>
+        </is>
+      </c>
+      <c r="K129" s="26" t="inlineStr">
+        <is>
+          <t>yitzhokt2@gmail.com</t>
+        </is>
+      </c>
       <c r="L129" s="29" t="n"/>
       <c r="M129" s="29" t="n"/>
     </row>
@@ -7595,7 +8327,7 @@
       </c>
       <c r="H130" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I130" s="28" t="inlineStr">
@@ -7603,8 +8335,16 @@
           <t>Node candidate — founded Snyk. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J130" s="26" t="inlineStr"/>
-      <c r="K130" s="26" t="inlineStr"/>
+      <c r="J130" s="26" t="inlineStr">
+        <is>
+          <t>+972507616594</t>
+        </is>
+      </c>
+      <c r="K130" s="26" t="inlineStr">
+        <is>
+          <t>danny.grander@gmail.com</t>
+        </is>
+      </c>
       <c r="L130" s="29" t="n"/>
       <c r="M130" s="29" t="n"/>
     </row>
@@ -7642,7 +8382,7 @@
       </c>
       <c r="H131" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I131" s="28" t="inlineStr">
@@ -7650,8 +8390,16 @@
           <t>What can they give — office hours, referrals into Palo Alto Networks, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J131" s="26" t="inlineStr"/>
-      <c r="K131" s="26" t="inlineStr"/>
+      <c r="J131" s="26" t="inlineStr">
+        <is>
+          <t>+972547260058</t>
+        </is>
+      </c>
+      <c r="K131" s="26" t="inlineStr">
+        <is>
+          <t>avielz1199@gmail.com</t>
+        </is>
+      </c>
       <c r="L131" s="29" t="n"/>
       <c r="M131" s="29" t="n"/>
     </row>
@@ -7689,7 +8437,7 @@
       </c>
       <c r="H132" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I132" s="28" t="inlineStr">
@@ -7697,8 +8445,16 @@
           <t>What can they give — office hours, referrals into Claroty (DS Team Leader per roster), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J132" s="26" t="inlineStr"/>
-      <c r="K132" s="26" t="inlineStr"/>
+      <c r="J132" s="26" t="inlineStr">
+        <is>
+          <t>+972506228892</t>
+        </is>
+      </c>
+      <c r="K132" s="26" t="inlineStr">
+        <is>
+          <t>eyalhoro6@gmail.com</t>
+        </is>
+      </c>
       <c r="L132" s="29" t="n"/>
       <c r="M132" s="29" t="n"/>
     </row>
@@ -7736,7 +8492,7 @@
       </c>
       <c r="H133" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I133" s="28" t="inlineStr">
@@ -7744,8 +8500,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J133" s="26" t="inlineStr"/>
-      <c r="K133" s="26" t="inlineStr"/>
+      <c r="J133" s="26" t="inlineStr">
+        <is>
+          <t>+972552242152</t>
+        </is>
+      </c>
+      <c r="K133" s="26" t="inlineStr">
+        <is>
+          <t>mayak144@gmail.com</t>
+        </is>
+      </c>
       <c r="L133" s="29" t="n"/>
       <c r="M133" s="29" t="n"/>
     </row>
@@ -7877,7 +8641,7 @@
       </c>
       <c r="H136" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I136" s="28" t="inlineStr">
@@ -7885,8 +8649,16 @@
           <t>What can they give — office hours, referrals into Remitly (AI/ML), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J136" s="26" t="inlineStr"/>
-      <c r="K136" s="26" t="inlineStr"/>
+      <c r="J136" s="26" t="inlineStr">
+        <is>
+          <t>+972544322242</t>
+        </is>
+      </c>
+      <c r="K136" s="26" t="inlineStr">
+        <is>
+          <t>gil.raytan@gmail.com</t>
+        </is>
+      </c>
       <c r="L136" s="29" t="n"/>
       <c r="M136" s="29" t="n"/>
     </row>
@@ -7924,7 +8696,7 @@
       </c>
       <c r="H137" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I137" s="28" t="inlineStr">
@@ -7932,8 +8704,16 @@
           <t>What can they give — office hours, referrals into Q.ai, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J137" s="26" t="inlineStr"/>
-      <c r="K137" s="26" t="inlineStr"/>
+      <c r="J137" s="26" t="inlineStr">
+        <is>
+          <t>+972528584131</t>
+        </is>
+      </c>
+      <c r="K137" s="26" t="inlineStr">
+        <is>
+          <t>idokazma@gmail.com</t>
+        </is>
+      </c>
       <c r="L137" s="29" t="n"/>
       <c r="M137" s="29" t="n"/>
     </row>
@@ -8018,7 +8798,7 @@
       </c>
       <c r="H139" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I139" s="28" t="inlineStr">
@@ -8026,8 +8806,16 @@
           <t>Node candidate — founded SendBlocks. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J139" s="26" t="inlineStr"/>
-      <c r="K139" s="26" t="inlineStr"/>
+      <c r="J139" s="26" t="inlineStr">
+        <is>
+          <t>+972545311213</t>
+        </is>
+      </c>
+      <c r="K139" s="26" t="inlineStr">
+        <is>
+          <t>mike53il@gmail.com</t>
+        </is>
+      </c>
       <c r="L139" s="29" t="n"/>
       <c r="M139" s="29" t="n"/>
     </row>
@@ -8065,7 +8853,7 @@
       </c>
       <c r="H140" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I140" s="28" t="inlineStr">
@@ -8073,8 +8861,16 @@
           <t>What can they give — office hours, referrals into Glassbox, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J140" s="26" t="inlineStr"/>
-      <c r="K140" s="26" t="inlineStr"/>
+      <c r="J140" s="26" t="inlineStr">
+        <is>
+          <t>+972547397052</t>
+        </is>
+      </c>
+      <c r="K140" s="26" t="inlineStr">
+        <is>
+          <t>ilan.voronel@gmail.com</t>
+        </is>
+      </c>
       <c r="L140" s="29" t="n"/>
       <c r="M140" s="29" t="n"/>
     </row>
@@ -8112,7 +8908,7 @@
       </c>
       <c r="H141" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I141" s="28" t="inlineStr">
@@ -8120,8 +8916,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J141" s="26" t="inlineStr"/>
-      <c r="K141" s="26" t="inlineStr"/>
+      <c r="J141" s="26" t="inlineStr">
+        <is>
+          <t>+972504291882</t>
+        </is>
+      </c>
+      <c r="K141" s="26" t="inlineStr">
+        <is>
+          <t>maya.naveh.40@gmail.com</t>
+        </is>
+      </c>
       <c r="L141" s="29" t="n"/>
       <c r="M141" s="29" t="n"/>
     </row>
@@ -8206,7 +9010,7 @@
       </c>
       <c r="H143" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I143" s="28" t="inlineStr">
@@ -8214,8 +9018,16 @@
           <t>What can they give — office hours, referrals into TAU (ex-Amazon), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J143" s="26" t="inlineStr"/>
-      <c r="K143" s="26" t="inlineStr"/>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t>+972527564010</t>
+        </is>
+      </c>
+      <c r="K143" s="26" t="inlineStr">
+        <is>
+          <t>giga123@gmail.com</t>
+        </is>
+      </c>
       <c r="L143" s="29" t="n"/>
       <c r="M143" s="29" t="n"/>
     </row>
@@ -8253,7 +9065,7 @@
       </c>
       <c r="H144" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I144" s="28" t="inlineStr">
@@ -8261,8 +9073,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J144" s="26" t="inlineStr"/>
-      <c r="K144" s="26" t="inlineStr"/>
+      <c r="J144" s="26" t="inlineStr">
+        <is>
+          <t>+972542338686</t>
+        </is>
+      </c>
+      <c r="K144" s="26" t="inlineStr">
+        <is>
+          <t>meny1237@gmail.com</t>
+        </is>
+      </c>
       <c r="L144" s="29" t="n"/>
       <c r="M144" s="29" t="n"/>
     </row>
@@ -8300,7 +9120,7 @@
       </c>
       <c r="H145" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>email</t>
         </is>
       </c>
       <c r="I145" s="28" t="inlineStr">
@@ -8309,7 +9129,11 @@
         </is>
       </c>
       <c r="J145" s="26" t="inlineStr"/>
-      <c r="K145" s="26" t="inlineStr"/>
+      <c r="K145" s="26" t="inlineStr">
+        <is>
+          <t>zviwex@gmail.com</t>
+        </is>
+      </c>
       <c r="L145" s="29" t="n"/>
       <c r="M145" s="29" t="n"/>
     </row>
@@ -8347,7 +9171,7 @@
       </c>
       <c r="H146" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I146" s="28" t="inlineStr">
@@ -8355,8 +9179,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J146" s="26" t="inlineStr"/>
-      <c r="K146" s="26" t="inlineStr"/>
+      <c r="J146" s="26" t="inlineStr">
+        <is>
+          <t>+972507363131</t>
+        </is>
+      </c>
+      <c r="K146" s="26" t="inlineStr">
+        <is>
+          <t>almogx3@gmail.com</t>
+        </is>
+      </c>
       <c r="L146" s="29" t="n"/>
       <c r="M146" s="29" t="n"/>
     </row>
@@ -8394,7 +9226,7 @@
       </c>
       <c r="H147" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I147" s="28" t="inlineStr">
@@ -8402,8 +9234,16 @@
           <t>What can they give — office hours, referrals into Akeyless (ex-System Architect, DriveNets), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J147" s="26" t="inlineStr"/>
-      <c r="K147" s="26" t="inlineStr"/>
+      <c r="J147" s="26" t="inlineStr">
+        <is>
+          <t>+972508112332</t>
+        </is>
+      </c>
+      <c r="K147" s="26" t="inlineStr">
+        <is>
+          <t>omeronn@gmail.com</t>
+        </is>
+      </c>
       <c r="L147" s="29" t="n"/>
       <c r="M147" s="29" t="n"/>
     </row>
@@ -8441,7 +9281,7 @@
       </c>
       <c r="H148" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I148" s="28" t="inlineStr">
@@ -8449,8 +9289,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J148" s="26" t="inlineStr"/>
-      <c r="K148" s="26" t="inlineStr"/>
+      <c r="J148" s="26" t="inlineStr">
+        <is>
+          <t>+972528225572</t>
+        </is>
+      </c>
+      <c r="K148" s="26" t="inlineStr">
+        <is>
+          <t>gotlib.omri@gmail.com</t>
+        </is>
+      </c>
       <c r="L148" s="29" t="n"/>
       <c r="M148" s="29" t="n"/>
     </row>
@@ -8488,7 +9336,7 @@
       </c>
       <c r="H149" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I149" s="28" t="inlineStr">
@@ -8496,8 +9344,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J149" s="26" t="inlineStr"/>
-      <c r="K149" s="26" t="inlineStr"/>
+      <c r="J149" s="26" t="inlineStr">
+        <is>
+          <t>+972525892000</t>
+        </is>
+      </c>
+      <c r="K149" s="26" t="inlineStr">
+        <is>
+          <t>barmatit@gmail.com</t>
+        </is>
+      </c>
       <c r="L149" s="29" t="n"/>
       <c r="M149" s="29" t="n"/>
     </row>
@@ -8535,7 +9391,7 @@
       </c>
       <c r="H150" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I150" s="28" t="inlineStr">
@@ -8543,8 +9399,16 @@
           <t>What can they give — office hours, referrals into Datadog, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J150" s="26" t="inlineStr"/>
-      <c r="K150" s="26" t="inlineStr"/>
+      <c r="J150" s="26" t="inlineStr">
+        <is>
+          <t>+972503039885</t>
+        </is>
+      </c>
+      <c r="K150" s="26" t="inlineStr">
+        <is>
+          <t>rongalay@gmail.com</t>
+        </is>
+      </c>
       <c r="L150" s="29" t="n"/>
       <c r="M150" s="29" t="n"/>
     </row>
@@ -8629,16 +9493,20 @@
       </c>
       <c r="H152" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>email</t>
         </is>
       </c>
       <c r="I152" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
+          <t>Stay current — still at Tel Aviv University? What are they working on in research, and what would help?</t>
         </is>
       </c>
       <c r="J152" s="26" t="inlineStr"/>
-      <c r="K152" s="26" t="inlineStr"/>
+      <c r="K152" s="26" t="inlineStr">
+        <is>
+          <t>nadav@deepinsight.co.il</t>
+        </is>
+      </c>
       <c r="L152" s="29" t="n"/>
       <c r="M152" s="29" t="n"/>
     </row>
@@ -8676,7 +9544,7 @@
       </c>
       <c r="H153" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I153" s="28" t="inlineStr">
@@ -8684,8 +9552,16 @@
           <t>Node candidate — founded Xcardia. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J153" s="26" t="inlineStr"/>
-      <c r="K153" s="26" t="inlineStr"/>
+      <c r="J153" s="26" t="inlineStr">
+        <is>
+          <t>+972544345653</t>
+        </is>
+      </c>
+      <c r="K153" s="26" t="inlineStr">
+        <is>
+          <t>rousso.benny@gmail.com</t>
+        </is>
+      </c>
       <c r="L153" s="29" t="n"/>
       <c r="M153" s="29" t="n"/>
     </row>
@@ -8723,7 +9599,7 @@
       </c>
       <c r="H154" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I154" s="28" t="inlineStr">
@@ -8731,8 +9607,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J154" s="26" t="inlineStr"/>
-      <c r="K154" s="26" t="inlineStr"/>
+      <c r="J154" s="26" t="inlineStr">
+        <is>
+          <t>+972502338655</t>
+        </is>
+      </c>
+      <c r="K154" s="26" t="inlineStr">
+        <is>
+          <t>galwiernik@gmail.com</t>
+        </is>
+      </c>
       <c r="L154" s="29" t="n"/>
       <c r="M154" s="29" t="n"/>
     </row>
@@ -8770,7 +9654,7 @@
       </c>
       <c r="H155" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I155" s="28" t="inlineStr">
@@ -8778,8 +9662,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J155" s="26" t="inlineStr"/>
-      <c r="K155" s="26" t="inlineStr"/>
+      <c r="J155" s="26" t="inlineStr">
+        <is>
+          <t>+972544702148</t>
+        </is>
+      </c>
+      <c r="K155" s="26" t="inlineStr">
+        <is>
+          <t>sharon.brizinov@gmail.com</t>
+        </is>
+      </c>
       <c r="L155" s="29" t="n"/>
       <c r="M155" s="29" t="n"/>
     </row>
@@ -8817,7 +9709,7 @@
       </c>
       <c r="H156" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I156" s="28" t="inlineStr">
@@ -8825,8 +9717,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J156" s="26" t="inlineStr"/>
-      <c r="K156" s="26" t="inlineStr"/>
+      <c r="J156" s="26" t="inlineStr">
+        <is>
+          <t>+972586110398</t>
+        </is>
+      </c>
+      <c r="K156" s="26" t="inlineStr">
+        <is>
+          <t>noga.keren@gmail.com</t>
+        </is>
+      </c>
       <c r="L156" s="29" t="n"/>
       <c r="M156" s="29" t="n"/>
     </row>
@@ -8864,7 +9764,7 @@
       </c>
       <c r="H157" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I157" s="28" t="inlineStr">
@@ -8872,8 +9772,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J157" s="26" t="inlineStr"/>
-      <c r="K157" s="26" t="inlineStr"/>
+      <c r="J157" s="26" t="inlineStr">
+        <is>
+          <t>+972508717313</t>
+        </is>
+      </c>
+      <c r="K157" s="26" t="inlineStr">
+        <is>
+          <t>yoshpe@gmail.com</t>
+        </is>
+      </c>
       <c r="L157" s="29" t="n"/>
       <c r="M157" s="29" t="n"/>
     </row>
@@ -8911,7 +9819,7 @@
       </c>
       <c r="H158" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I158" s="28" t="inlineStr">
@@ -8919,8 +9827,16 @@
           <t>Node candidate — founded Cabinet (AI workspace). What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J158" s="26" t="inlineStr"/>
-      <c r="K158" s="26" t="inlineStr"/>
+      <c r="J158" s="26" t="inlineStr">
+        <is>
+          <t>+972508871171</t>
+        </is>
+      </c>
+      <c r="K158" s="26" t="inlineStr">
+        <is>
+          <t>hila4321@gmail.com</t>
+        </is>
+      </c>
       <c r="L158" s="29" t="n"/>
       <c r="M158" s="29" t="n"/>
     </row>
@@ -8958,7 +9874,7 @@
       </c>
       <c r="H159" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I159" s="28" t="inlineStr">
@@ -8966,8 +9882,16 @@
           <t>What can they give — office hours, referrals into Orca Security, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J159" s="26" t="inlineStr"/>
-      <c r="K159" s="26" t="inlineStr"/>
+      <c r="J159" s="26" t="inlineStr">
+        <is>
+          <t>+972538271198</t>
+        </is>
+      </c>
+      <c r="K159" s="26" t="inlineStr">
+        <is>
+          <t>tzahpahima123@gmail.com</t>
+        </is>
+      </c>
       <c r="L159" s="29" t="n"/>
       <c r="M159" s="29" t="n"/>
     </row>
@@ -9005,7 +9929,7 @@
       </c>
       <c r="H160" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I160" s="28" t="inlineStr">
@@ -9013,8 +9937,16 @@
           <t>Node candidate — founded Sayata. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J160" s="26" t="inlineStr"/>
-      <c r="K160" s="26" t="inlineStr"/>
+      <c r="J160" s="26" t="inlineStr">
+        <is>
+          <t>+972542421974</t>
+        </is>
+      </c>
+      <c r="K160" s="26" t="inlineStr">
+        <is>
+          <t>igolomb@gmail.com</t>
+        </is>
+      </c>
       <c r="L160" s="29" t="n"/>
       <c r="M160" s="29" t="n"/>
     </row>
@@ -9052,7 +9984,7 @@
       </c>
       <c r="H161" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I161" s="28" t="inlineStr">
@@ -9060,8 +9992,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J161" s="26" t="inlineStr"/>
-      <c r="K161" s="26" t="inlineStr"/>
+      <c r="J161" s="26" t="inlineStr">
+        <is>
+          <t>+972529508555</t>
+        </is>
+      </c>
+      <c r="K161" s="26" t="inlineStr">
+        <is>
+          <t>yakov.kosoburd@gmail.com</t>
+        </is>
+      </c>
       <c r="L161" s="29" t="n"/>
       <c r="M161" s="29" t="n"/>
     </row>
@@ -9099,7 +10039,7 @@
       </c>
       <c r="H162" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I162" s="28" t="inlineStr">
@@ -9107,8 +10047,16 @@
           <t>What can they give — office hours, referrals into PureSec (Architect @ PAN per roster), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J162" s="26" t="inlineStr"/>
-      <c r="K162" s="26" t="inlineStr"/>
+      <c r="J162" s="26" t="inlineStr">
+        <is>
+          <t>+972547225688</t>
+        </is>
+      </c>
+      <c r="K162" s="26" t="inlineStr">
+        <is>
+          <t>yurishapira@gmail.com</t>
+        </is>
+      </c>
       <c r="L162" s="29" t="n"/>
       <c r="M162" s="29" t="n"/>
     </row>
@@ -9146,7 +10094,7 @@
       </c>
       <c r="H163" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I163" s="28" t="inlineStr">
@@ -9154,8 +10102,16 @@
           <t>Stay current — still at Breeze Security? What are they working on in security, and what would help?</t>
         </is>
       </c>
-      <c r="J163" s="26" t="inlineStr"/>
-      <c r="K163" s="26" t="inlineStr"/>
+      <c r="J163" s="26" t="inlineStr">
+        <is>
+          <t>+972544826333</t>
+        </is>
+      </c>
+      <c r="K163" s="26" t="inlineStr">
+        <is>
+          <t>noyhadar95@gmail.com</t>
+        </is>
+      </c>
       <c r="L163" s="29" t="n"/>
       <c r="M163" s="29" t="n"/>
     </row>
@@ -9193,7 +10149,7 @@
       </c>
       <c r="H164" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I164" s="28" t="inlineStr">
@@ -9201,8 +10157,16 @@
           <t>Node candidate — founded Medida AI. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J164" s="26" t="inlineStr"/>
-      <c r="K164" s="26" t="inlineStr"/>
+      <c r="J164" s="26" t="inlineStr">
+        <is>
+          <t>+972528198278</t>
+        </is>
+      </c>
+      <c r="K164" s="26" t="inlineStr">
+        <is>
+          <t>jonathan@medida.ai</t>
+        </is>
+      </c>
       <c r="L164" s="29" t="n"/>
       <c r="M164" s="29" t="n"/>
     </row>
@@ -9240,7 +10204,7 @@
       </c>
       <c r="H165" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I165" s="28" t="inlineStr">
@@ -9248,8 +10212,16 @@
           <t>Node candidate — founded Edwin. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J165" s="26" t="inlineStr"/>
-      <c r="K165" s="26" t="inlineStr"/>
+      <c r="J165" s="26" t="inlineStr">
+        <is>
+          <t>+972544911254</t>
+        </is>
+      </c>
+      <c r="K165" s="26" t="inlineStr">
+        <is>
+          <t>liran.markin@gmail.com</t>
+        </is>
+      </c>
       <c r="L165" s="29" t="n"/>
       <c r="M165" s="29" t="n"/>
     </row>
@@ -9287,7 +10259,7 @@
       </c>
       <c r="H166" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I166" s="28" t="inlineStr">
@@ -9295,8 +10267,16 @@
           <t>What can they give — office hours, referrals into Cyera, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J166" s="26" t="inlineStr"/>
-      <c r="K166" s="26" t="inlineStr"/>
+      <c r="J166" s="26" t="inlineStr">
+        <is>
+          <t>+972546611903</t>
+        </is>
+      </c>
+      <c r="K166" s="26" t="inlineStr">
+        <is>
+          <t>alonwolfy@gmail.com</t>
+        </is>
+      </c>
       <c r="L166" s="29" t="n"/>
       <c r="M166" s="29" t="n"/>
     </row>
@@ -9334,7 +10314,7 @@
       </c>
       <c r="H167" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I167" s="28" t="inlineStr">
@@ -9342,8 +10322,16 @@
           <t>What can they give — office hours, referrals into Zafran, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J167" s="26" t="inlineStr"/>
-      <c r="K167" s="26" t="inlineStr"/>
+      <c r="J167" s="26" t="inlineStr">
+        <is>
+          <t>+972545301526</t>
+        </is>
+      </c>
+      <c r="K167" s="26" t="inlineStr">
+        <is>
+          <t>relrelbachar@gmail.com</t>
+        </is>
+      </c>
       <c r="L167" s="29" t="n"/>
       <c r="M167" s="29" t="n"/>
     </row>
@@ -9381,7 +10369,7 @@
       </c>
       <c r="H168" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I168" s="28" t="inlineStr">
@@ -9389,8 +10377,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J168" s="26" t="inlineStr"/>
-      <c r="K168" s="26" t="inlineStr"/>
+      <c r="J168" s="26" t="inlineStr">
+        <is>
+          <t>+972544319975</t>
+        </is>
+      </c>
+      <c r="K168" s="26" t="inlineStr">
+        <is>
+          <t>mikomraz@gmail.com</t>
+        </is>
+      </c>
       <c r="L168" s="29" t="n"/>
       <c r="M168" s="29" t="n"/>
     </row>
@@ -9428,7 +10424,7 @@
       </c>
       <c r="H169" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I169" s="28" t="inlineStr">
@@ -9436,8 +10432,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J169" s="26" t="inlineStr"/>
-      <c r="K169" s="26" t="inlineStr"/>
+      <c r="J169" s="26" t="inlineStr">
+        <is>
+          <t>+972507711998</t>
+        </is>
+      </c>
+      <c r="K169" s="26" t="inlineStr">
+        <is>
+          <t>mor.m.shemesh@gmail.com</t>
+        </is>
+      </c>
       <c r="L169" s="29" t="n"/>
       <c r="M169" s="29" t="n"/>
     </row>
@@ -9475,7 +10479,7 @@
       </c>
       <c r="H170" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I170" s="28" t="inlineStr">
@@ -9483,8 +10487,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J170" s="26" t="inlineStr"/>
-      <c r="K170" s="26" t="inlineStr"/>
+      <c r="J170" s="26" t="inlineStr">
+        <is>
+          <t>+972526207606</t>
+        </is>
+      </c>
+      <c r="K170" s="26" t="inlineStr">
+        <is>
+          <t>avraham.berr@gmail.com</t>
+        </is>
+      </c>
       <c r="L170" s="29" t="n"/>
       <c r="M170" s="29" t="n"/>
     </row>
@@ -9522,7 +10534,7 @@
       </c>
       <c r="H171" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I171" s="28" t="inlineStr">
@@ -9530,8 +10542,16 @@
           <t>Stay current — what are they working on in ai-ml now, and what would help?</t>
         </is>
       </c>
-      <c r="J171" s="26" t="inlineStr"/>
-      <c r="K171" s="26" t="inlineStr"/>
+      <c r="J171" s="26" t="inlineStr">
+        <is>
+          <t>+972528645340</t>
+        </is>
+      </c>
+      <c r="K171" s="26" t="inlineStr">
+        <is>
+          <t>oz@tamir.fun</t>
+        </is>
+      </c>
       <c r="L171" s="29" t="n"/>
       <c r="M171" s="29" t="n"/>
     </row>
@@ -9569,7 +10589,7 @@
       </c>
       <c r="H172" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I172" s="28" t="inlineStr">
@@ -9577,8 +10597,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J172" s="26" t="inlineStr"/>
-      <c r="K172" s="26" t="inlineStr"/>
+      <c r="J172" s="26" t="inlineStr">
+        <is>
+          <t>+972546777815</t>
+        </is>
+      </c>
+      <c r="K172" s="26" t="inlineStr">
+        <is>
+          <t>roymoshe23@gmail.com</t>
+        </is>
+      </c>
       <c r="L172" s="29" t="n"/>
       <c r="M172" s="29" t="n"/>
     </row>
@@ -9616,7 +10644,7 @@
       </c>
       <c r="H173" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I173" s="28" t="inlineStr">
@@ -9624,8 +10652,16 @@
           <t>What can they give — office hours, referrals into Walmart Global Tech, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J173" s="26" t="inlineStr"/>
-      <c r="K173" s="26" t="inlineStr"/>
+      <c r="J173" s="26" t="inlineStr">
+        <is>
+          <t>+972523872832</t>
+        </is>
+      </c>
+      <c r="K173" s="26" t="inlineStr">
+        <is>
+          <t>gmelamed@gmail.com</t>
+        </is>
+      </c>
       <c r="L173" s="29" t="n"/>
       <c r="M173" s="29" t="n"/>
     </row>
@@ -9663,7 +10699,7 @@
       </c>
       <c r="H174" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I174" s="28" t="inlineStr">
@@ -9671,8 +10707,16 @@
           <t>What can they give — office hours, referrals into Wiz, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J174" s="26" t="inlineStr"/>
-      <c r="K174" s="26" t="inlineStr"/>
+      <c r="J174" s="26" t="inlineStr">
+        <is>
+          <t>+972542172153</t>
+        </is>
+      </c>
+      <c r="K174" s="26" t="inlineStr">
+        <is>
+          <t>guy.goldenberg@gmail.com</t>
+        </is>
+      </c>
       <c r="L174" s="29" t="n"/>
       <c r="M174" s="29" t="n"/>
     </row>
@@ -9710,7 +10754,7 @@
       </c>
       <c r="H175" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I175" s="28" t="inlineStr">
@@ -9718,8 +10762,16 @@
           <t>Stay current — what are they working on in infra-systems now, and what would help?</t>
         </is>
       </c>
-      <c r="J175" s="26" t="inlineStr"/>
-      <c r="K175" s="26" t="inlineStr"/>
+      <c r="J175" s="26" t="inlineStr">
+        <is>
+          <t>+972549703632</t>
+        </is>
+      </c>
+      <c r="K175" s="26" t="inlineStr">
+        <is>
+          <t>uriariel10@gmail.com</t>
+        </is>
+      </c>
       <c r="L175" s="29" t="n"/>
       <c r="M175" s="29" t="n"/>
     </row>
@@ -9757,7 +10809,7 @@
       </c>
       <c r="H176" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I176" s="28" t="inlineStr">
@@ -9765,8 +10817,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J176" s="26" t="inlineStr"/>
-      <c r="K176" s="26" t="inlineStr"/>
+      <c r="J176" s="26" t="inlineStr">
+        <is>
+          <t>+972544744575</t>
+        </is>
+      </c>
+      <c r="K176" s="26" t="inlineStr">
+        <is>
+          <t>tomergoren99@gmail.com</t>
+        </is>
+      </c>
       <c r="L176" s="29" t="n"/>
       <c r="M176" s="29" t="n"/>
     </row>
@@ -9804,7 +10864,7 @@
       </c>
       <c r="H177" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I177" s="28" t="inlineStr">
@@ -9812,8 +10872,16 @@
           <t>Node candidate — founded Predicta Med. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J177" s="26" t="inlineStr"/>
-      <c r="K177" s="26" t="inlineStr"/>
+      <c r="J177" s="26" t="inlineStr">
+        <is>
+          <t>+972545551000</t>
+        </is>
+      </c>
+      <c r="K177" s="26" t="inlineStr">
+        <is>
+          <t>benny.getz@gmail.com</t>
+        </is>
+      </c>
       <c r="L177" s="29" t="n"/>
       <c r="M177" s="29" t="n"/>
     </row>
@@ -9851,7 +10919,7 @@
       </c>
       <c r="H178" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I178" s="28" t="inlineStr">
@@ -9859,8 +10927,16 @@
           <t>What can they give — office hours, referrals into Technion Autonomous Systems (POMDP planning), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J178" s="26" t="inlineStr"/>
-      <c r="K178" s="26" t="inlineStr"/>
+      <c r="J178" s="26" t="inlineStr">
+        <is>
+          <t>+972523059999</t>
+        </is>
+      </c>
+      <c r="K178" s="26" t="inlineStr">
+        <is>
+          <t>idanly98@gmail.com</t>
+        </is>
+      </c>
       <c r="L178" s="29" t="n"/>
       <c r="M178" s="29" t="n"/>
     </row>
@@ -9898,7 +10974,7 @@
       </c>
       <c r="H179" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I179" s="28" t="inlineStr">
@@ -9906,8 +10982,16 @@
           <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J179" s="26" t="inlineStr"/>
-      <c r="K179" s="26" t="inlineStr"/>
+      <c r="J179" s="26" t="inlineStr">
+        <is>
+          <t>+972525677675</t>
+        </is>
+      </c>
+      <c r="K179" s="26" t="inlineStr">
+        <is>
+          <t>dolevelb@gmail.com</t>
+        </is>
+      </c>
       <c r="L179" s="29" t="n"/>
       <c r="M179" s="29" t="n"/>
     </row>
@@ -9945,7 +11029,7 @@
       </c>
       <c r="H180" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I180" s="28" t="inlineStr">
@@ -9953,8 +11037,16 @@
           <t>What can they give — office hours, referrals into Wiz, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J180" s="26" t="inlineStr"/>
-      <c r="K180" s="26" t="inlineStr"/>
+      <c r="J180" s="26" t="inlineStr">
+        <is>
+          <t>+972504787314</t>
+        </is>
+      </c>
+      <c r="K180" s="26" t="inlineStr">
+        <is>
+          <t>itamar.gilad@wiz.io</t>
+        </is>
+      </c>
       <c r="L180" s="29" t="n"/>
       <c r="M180" s="29" t="n"/>
     </row>
@@ -9992,7 +11084,7 @@
       </c>
       <c r="H181" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I181" s="28" t="inlineStr">
@@ -10000,8 +11092,16 @@
           <t>What can they give — office hours, referrals into nT-Tao (compact fusion), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J181" s="26" t="inlineStr"/>
-      <c r="K181" s="26" t="inlineStr"/>
+      <c r="J181" s="26" t="inlineStr">
+        <is>
+          <t>+972504039870</t>
+        </is>
+      </c>
+      <c r="K181" s="26" t="inlineStr">
+        <is>
+          <t>itaigiss@gmail.com</t>
+        </is>
+      </c>
       <c r="L181" s="29" t="n"/>
       <c r="M181" s="29" t="n"/>
     </row>
@@ -10039,7 +11139,7 @@
       </c>
       <c r="H182" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I182" s="28" t="inlineStr">
@@ -10047,8 +11147,16 @@
           <t>Stay current — still at Wiz? What are they working on in security, and what would help?</t>
         </is>
       </c>
-      <c r="J182" s="26" t="inlineStr"/>
-      <c r="K182" s="26" t="inlineStr"/>
+      <c r="J182" s="26" t="inlineStr">
+        <is>
+          <t>+972502758710</t>
+        </is>
+      </c>
+      <c r="K182" s="26" t="inlineStr">
+        <is>
+          <t>yoni.horn@gmail.com</t>
+        </is>
+      </c>
       <c r="L182" s="29" t="n"/>
       <c r="M182" s="29" t="n"/>
     </row>
@@ -10086,7 +11194,7 @@
       </c>
       <c r="H183" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I183" s="28" t="inlineStr">
@@ -10094,8 +11202,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J183" s="26" t="inlineStr"/>
-      <c r="K183" s="26" t="inlineStr"/>
+      <c r="J183" s="26" t="inlineStr">
+        <is>
+          <t>+972543134989</t>
+        </is>
+      </c>
+      <c r="K183" s="26" t="inlineStr">
+        <is>
+          <t>nadav.claude.cohen@gmail.com</t>
+        </is>
+      </c>
       <c r="L183" s="29" t="n"/>
       <c r="M183" s="29" t="n"/>
     </row>
@@ -10133,7 +11249,7 @@
       </c>
       <c r="H184" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I184" s="28" t="inlineStr">
@@ -10141,8 +11257,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J184" s="26" t="inlineStr"/>
-      <c r="K184" s="26" t="inlineStr"/>
+      <c r="J184" s="26" t="inlineStr">
+        <is>
+          <t>+972586392129</t>
+        </is>
+      </c>
+      <c r="K184" s="26" t="inlineStr">
+        <is>
+          <t>orenfine@gmail.com</t>
+        </is>
+      </c>
       <c r="L184" s="29" t="n"/>
       <c r="M184" s="29" t="n"/>
     </row>
@@ -10180,7 +11304,7 @@
       </c>
       <c r="H185" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I185" s="28" t="inlineStr">
@@ -10188,8 +11312,16 @@
           <t>What can they give — office hours, referrals into Weizmann (Milo lab, Nature co-author), mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J185" s="26" t="inlineStr"/>
-      <c r="K185" s="26" t="inlineStr"/>
+      <c r="J185" s="26" t="inlineStr">
+        <is>
+          <t>+972546326372</t>
+        </is>
+      </c>
+      <c r="K185" s="26" t="inlineStr">
+        <is>
+          <t>liadgo2@gmail.com</t>
+        </is>
+      </c>
       <c r="L185" s="29" t="n"/>
       <c r="M185" s="29" t="n"/>
     </row>
@@ -10227,16 +11359,24 @@
       </c>
       <c r="H186" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I186" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
-        </is>
-      </c>
-      <c r="J186" s="26" t="inlineStr"/>
-      <c r="K186" s="26" t="inlineStr"/>
+          <t>Stay current — still at Government of Israel? What are they working on, and what would help?</t>
+        </is>
+      </c>
+      <c r="J186" s="26" t="inlineStr">
+        <is>
+          <t>+972547260186</t>
+        </is>
+      </c>
+      <c r="K186" s="26" t="inlineStr">
+        <is>
+          <t>yuval.genossar@gmail.com</t>
+        </is>
+      </c>
       <c r="L186" s="29" t="n"/>
       <c r="M186" s="29" t="n"/>
     </row>
@@ -10274,7 +11414,7 @@
       </c>
       <c r="H187" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I187" s="28" t="inlineStr">
@@ -10282,8 +11422,16 @@
           <t>Node candidate — founded TrueNorth Systems. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J187" s="26" t="inlineStr"/>
-      <c r="K187" s="26" t="inlineStr"/>
+      <c r="J187" s="26" t="inlineStr">
+        <is>
+          <t>+972545330111</t>
+        </is>
+      </c>
+      <c r="K187" s="26" t="inlineStr">
+        <is>
+          <t>shlomo@lahavs.com</t>
+        </is>
+      </c>
       <c r="L187" s="29" t="n"/>
       <c r="M187" s="29" t="n"/>
     </row>
@@ -10321,7 +11469,7 @@
       </c>
       <c r="H188" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I188" s="28" t="inlineStr">
@@ -10329,8 +11477,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J188" s="26" t="inlineStr"/>
-      <c r="K188" s="26" t="inlineStr"/>
+      <c r="J188" s="26" t="inlineStr">
+        <is>
+          <t>+972525621097</t>
+        </is>
+      </c>
+      <c r="K188" s="26" t="inlineStr">
+        <is>
+          <t>yanivsh002@gmail.com</t>
+        </is>
+      </c>
       <c r="L188" s="29" t="n"/>
       <c r="M188" s="29" t="n"/>
     </row>
@@ -10368,7 +11524,7 @@
       </c>
       <c r="H189" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I189" s="28" t="inlineStr">
@@ -10376,8 +11532,16 @@
           <t>What can they give — office hours, referrals into Vayyar Imaging, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J189" s="26" t="inlineStr"/>
-      <c r="K189" s="26" t="inlineStr"/>
+      <c r="J189" s="26" t="inlineStr">
+        <is>
+          <t>+972544321050</t>
+        </is>
+      </c>
+      <c r="K189" s="26" t="inlineStr">
+        <is>
+          <t>mark.popov@gmail.com</t>
+        </is>
+      </c>
       <c r="L189" s="29" t="n"/>
       <c r="M189" s="29" t="n"/>
     </row>
@@ -10415,7 +11579,7 @@
       </c>
       <c r="H190" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I190" s="28" t="inlineStr">
@@ -10423,8 +11587,16 @@
           <t>What can they give — office hours, referrals into OpenEyes, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J190" s="26" t="inlineStr"/>
-      <c r="K190" s="26" t="inlineStr"/>
+      <c r="J190" s="26" t="inlineStr">
+        <is>
+          <t>+972545221060</t>
+        </is>
+      </c>
+      <c r="K190" s="26" t="inlineStr">
+        <is>
+          <t>matan.shoef@gmail.com</t>
+        </is>
+      </c>
       <c r="L190" s="29" t="n"/>
       <c r="M190" s="29" t="n"/>
     </row>
@@ -10629,7 +11801,11 @@
           <t>Co-Founder, CTO &amp; VP R&amp;D, D-Fend Solutions</t>
         </is>
       </c>
-      <c r="I2" s="29" t="n"/>
+      <c r="I2" s="29" t="inlineStr">
+        <is>
+          <t>Netanya, Israel</t>
+        </is>
+      </c>
       <c r="J2" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -10653,14 +11829,26 @@
           <t>https://www.linkedin.com/in/assaf-monsa-72a84/</t>
         </is>
       </c>
-      <c r="U2" s="29" t="n"/>
-      <c r="V2" s="29" t="n"/>
+      <c r="U2" s="29" t="inlineStr">
+        <is>
+          <t>assafmonsa@gmail.com</t>
+        </is>
+      </c>
+      <c r="V2" s="29" t="inlineStr">
+        <is>
+          <t>+972544319991</t>
+        </is>
+      </c>
       <c r="W2" s="28" t="inlineStr">
         <is>
           <t>Founded and scaled a real-time RF/hardware company (counter-drone) as CTO/VP R&amp;D - proven physical-systems founder. Domain gap (RF, not GPU/power) and committed to D-Fend.</t>
         </is>
       </c>
-      <c r="X2" s="33" t="n"/>
+      <c r="X2" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: תלפיות · tags: Apex Newsletter,Signed To Apex,Fireside Chat,19/10/25 Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="26" t="n">
@@ -10682,10 +11870,14 @@
       <c r="G3" s="26" t="n"/>
       <c r="H3" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="n"/>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="I3" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J3" s="26" t="n"/>
       <c r="K3" s="35" t="inlineStr">
         <is>
@@ -10705,14 +11897,26 @@
           <t>https://www.linkedin.com/in/aviel-a-a87b2612/</t>
         </is>
       </c>
-      <c r="U3" s="29" t="n"/>
-      <c r="V3" s="29" t="n"/>
+      <c r="U3" s="29" t="inlineStr">
+        <is>
+          <t>avieladler@gmail.com</t>
+        </is>
+      </c>
+      <c r="V3" s="29" t="inlineStr">
+        <is>
+          <t>+972549954666</t>
+        </is>
+      </c>
       <c r="W3" s="28" t="inlineStr">
         <is>
           <t>No company/role data in roster and no reliable public technical record found against the criteria (GPU systems, power, real-time control).</t>
         </is>
       </c>
-      <c r="X3" s="33" t="n"/>
+      <c r="X3" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: תלפיות · tags: Apex Newsletter,Signed To Apex,Fireside Chat,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="n">
@@ -10741,7 +11945,11 @@
           <t>MSc student, Technion</t>
         </is>
       </c>
-      <c r="I4" s="29" t="n"/>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Jerusalem District, Israel</t>
+        </is>
+      </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -10766,7 +11974,11 @@
         </is>
       </c>
       <c r="U4" s="29" t="n"/>
-      <c r="V4" s="29" t="n"/>
+      <c r="V4" s="29" t="inlineStr">
+        <is>
+          <t>+972524056440</t>
+        </is>
+      </c>
       <c r="W4" s="28" t="inlineStr">
         <is>
           <t>Graduate student, Psagot. Insufficient production record to score above the average band.</t>
@@ -10805,7 +12017,11 @@
           <t>Co-Founder</t>
         </is>
       </c>
-      <c r="I5" s="29" t="n"/>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J5" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -10829,14 +12045,26 @@
           <t>https://www.linkedin.com/in/grander</t>
         </is>
       </c>
-      <c r="U5" s="29" t="n"/>
-      <c r="V5" s="29" t="n"/>
+      <c r="U5" s="29" t="inlineStr">
+        <is>
+          <t>danny.grander@gmail.com</t>
+        </is>
+      </c>
+      <c r="V5" s="29" t="inlineStr">
+        <is>
+          <t>+972507616594</t>
+        </is>
+      </c>
       <c r="W5" s="28" t="inlineStr">
         <is>
           <t>World-class 0-to-1 founder signal (Snyk) and now angel - but zero domain overlap with GPU/power. Not an operator fit; top-tier angel/advisor target for Joulix's next round.</t>
         </is>
       </c>
-      <c r="X5" s="33" t="n"/>
+      <c r="X5" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] met with: Can help Apex · education: ארם · tags: Apex Donor,PEF,Apex Newsletter,Mega Connector,Signed To Apex,Fireside Chat,Coffee Avishag,19/10/25 Closing Event,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="26" t="n">
@@ -10985,7 +12213,11 @@
           <t>Product Executive, AI digital health</t>
         </is>
       </c>
-      <c r="I8" s="29" t="n"/>
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J8" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -11009,14 +12241,26 @@
           <t>https://www.linkedin.com/in/eran-hertzmann-24a400</t>
         </is>
       </c>
-      <c r="U8" s="29" t="n"/>
-      <c r="V8" s="29" t="n"/>
+      <c r="U8" s="29" t="inlineStr">
+        <is>
+          <t>eran.hertzmann@gmail.com</t>
+        </is>
+      </c>
+      <c r="V8" s="29" t="inlineStr">
+        <is>
+          <t>+972545424895</t>
+        </is>
+      </c>
       <c r="W8" s="28" t="inlineStr">
         <is>
           <t>Product executive, health tech. Not a technical founding fit for this domain.</t>
         </is>
       </c>
-      <c r="X8" s="33" t="n"/>
+      <c r="X8" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: תלפיות · tags: Apex Newsletter,Signed To Apex,Fireside Chat,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="26" t="n">
@@ -11045,7 +12289,11 @@
           <t>Freelance Full-Stack, ex-Meta</t>
         </is>
       </c>
-      <c r="I9" s="29" t="n"/>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>Givatayim, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J9" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -11069,14 +12317,26 @@
           <t>https://www.linkedin.com/in/eranhirsch</t>
         </is>
       </c>
-      <c r="U9" s="29" t="n"/>
-      <c r="V9" s="29" t="n"/>
+      <c r="U9" s="29" t="inlineStr">
+        <is>
+          <t>eranhirsch@gmail.com</t>
+        </is>
+      </c>
+      <c r="V9" s="29" t="inlineStr">
+        <is>
+          <t>+972548303525</t>
+        </is>
+      </c>
       <c r="W9" s="28" t="inlineStr">
         <is>
           <t>Ex-Meta full-stack freelancer. Application layer; no systems/power depth in public record.</t>
         </is>
       </c>
-      <c r="X9" s="33" t="n"/>
+      <c r="X9" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: אר"ם · tags: Apex Newsletter,Signed To Apex,Fireside Chat,19/10/25 Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="26" t="n">
@@ -11373,14 +12633,26 @@
           <t>https://www.linkedin.com/in/michael-kellner-689258206</t>
         </is>
       </c>
-      <c r="U14" s="29" t="n"/>
-      <c r="V14" s="29" t="n"/>
+      <c r="U14" s="29" t="inlineStr">
+        <is>
+          <t>mike53il@gmail.com</t>
+        </is>
+      </c>
+      <c r="V14" s="29" t="inlineStr">
+        <is>
+          <t>+972545311213</t>
+        </is>
+      </c>
       <c r="W14" s="28" t="inlineStr">
         <is>
           <t>Infra founder-CTO (blockchain data infrastructure). Real infra chops, committed elsewhere, no power/GPU record.</t>
         </is>
       </c>
-      <c r="X14" s="33" t="n"/>
+      <c r="X14" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: תלפיות · tags: Apex Newsletter,Signed To Apex,Fireside Chat,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="26" t="n">
@@ -11409,7 +12681,11 @@
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="I15" s="29" t="n"/>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J15" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -11433,14 +12709,26 @@
           <t>https://www.linkedin.com/in/michal-shilo-ba3002190/</t>
         </is>
       </c>
-      <c r="U15" s="29" t="n"/>
-      <c r="V15" s="29" t="n"/>
+      <c r="U15" s="29" t="inlineStr">
+        <is>
+          <t>michalshilo6@gmail.com</t>
+        </is>
+      </c>
+      <c r="V15" s="29" t="inlineStr">
+        <is>
+          <t>+972524598022</t>
+        </is>
+      </c>
       <c r="W15" s="28" t="inlineStr">
         <is>
           <t>Data scientist, Talpiot. No systems/power/GPU evidence.</t>
         </is>
       </c>
-      <c r="X15" s="33" t="n"/>
+      <c r="X15" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] education: תלפיות · tags: Apex Newsletter,Signed To Apex,Fireside Chat,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="26" t="n">
@@ -11709,7 +12997,11 @@
           <t>Software Engineer / R&amp;D Team Lead</t>
         </is>
       </c>
-      <c r="I20" s="29" t="n"/>
+      <c r="I20" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J20" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -12157,14 +13449,22 @@
           <t>https://www.linkedin.com/in/zvi-wexlstein</t>
         </is>
       </c>
-      <c r="U27" s="29" t="n"/>
+      <c r="U27" s="29" t="inlineStr">
+        <is>
+          <t>zviwex@gmail.com</t>
+        </is>
+      </c>
       <c r="V27" s="29" t="n"/>
       <c r="W27" s="28" t="inlineStr">
         <is>
           <t>Software architect at Polar/IBM; Founder Track signal. Solid architect, no power/GPU record.</t>
         </is>
       </c>
-      <c r="X27" s="33" t="n"/>
+      <c r="X27" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] tags: Fireside Chat</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="26" t="n">
@@ -12197,7 +13497,11 @@
           <t>R&amp;D Group Lead</t>
         </is>
       </c>
-      <c r="I28" s="29" t="n"/>
+      <c r="I28" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J28" s="26" t="n"/>
       <c r="K28" s="32" t="inlineStr">
         <is>
@@ -12217,14 +13521,26 @@
           <t>https://www.linkedin.com/in/almog-zer-865897118</t>
         </is>
       </c>
-      <c r="U28" s="29" t="n"/>
-      <c r="V28" s="29" t="n"/>
+      <c r="U28" s="29" t="inlineStr">
+        <is>
+          <t>almogx3@gmail.com</t>
+        </is>
+      </c>
+      <c r="V28" s="29" t="inlineStr">
+        <is>
+          <t>+972507363131</t>
+        </is>
+      </c>
       <c r="W28" s="28" t="inlineStr">
         <is>
           <t>Group lead at stealth - domain unknown, availability low.</t>
         </is>
       </c>
-      <c r="X28" s="33" t="n"/>
+      <c r="X28" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: טו · met with: Can help Apex · warm intro via: Lutati · education: פסגות · tags: Fireside Chat,Signed To Apex,Apex Newsletter,Watchlist,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="26" t="n">
@@ -12257,7 +13573,11 @@
           <t>Architect</t>
         </is>
       </c>
-      <c r="I29" s="29" t="n"/>
+      <c r="I29" s="29" t="inlineStr">
+        <is>
+          <t>Rishon LeZion, Israel</t>
+        </is>
+      </c>
       <c r="J29" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -12281,14 +13601,26 @@
           <t>https://www.linkedin.com/in/aviel-zecharia-832a66131/</t>
         </is>
       </c>
-      <c r="U29" s="29" t="n"/>
-      <c r="V29" s="29" t="n"/>
+      <c r="U29" s="29" t="inlineStr">
+        <is>
+          <t>avielz1199@gmail.com</t>
+        </is>
+      </c>
+      <c r="V29" s="29" t="inlineStr">
+        <is>
+          <t>+972547260058</t>
+        </is>
+      </c>
       <c r="W29" s="28" t="inlineStr">
         <is>
           <t>Security architect at PAN. Strong engineer, security domain.</t>
         </is>
       </c>
-      <c r="X29" s="33" t="n"/>
+      <c r="X29" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 20 · education: אר"ם · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="26" t="n">
@@ -12321,7 +13653,11 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="I30" s="29" t="n"/>
+      <c r="I30" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J30" s="26" t="n"/>
       <c r="K30" s="32" t="inlineStr">
         <is>
@@ -12341,14 +13677,26 @@
           <t>https://www.linkedin.com/in/bar-matityahu</t>
         </is>
       </c>
-      <c r="U30" s="29" t="n"/>
-      <c r="V30" s="29" t="n"/>
+      <c r="U30" s="29" t="inlineStr">
+        <is>
+          <t>barmatit@gmail.com</t>
+        </is>
+      </c>
+      <c r="V30" s="29" t="inlineStr">
+        <is>
+          <t>+972525892000</t>
+        </is>
+      </c>
       <c r="W30" s="28" t="inlineStr">
         <is>
           <t>Stealth founder - unknowable and unavailable.</t>
         </is>
       </c>
-      <c r="X30" s="33" t="n"/>
+      <c r="X30" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: מחזור י - חשמל פיזיקה טכניון · education: פסגות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="26" t="n">
@@ -12381,7 +13729,11 @@
           <t>CEO &amp; Founder</t>
         </is>
       </c>
-      <c r="I31" s="29" t="n"/>
+      <c r="I31" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J31" s="26" t="inlineStr">
         <is>
           <t>health-bio</t>
@@ -12405,14 +13757,26 @@
           <t>http://linkedin.com/in/benny-rousso-27832b32b</t>
         </is>
       </c>
-      <c r="U31" s="29" t="n"/>
-      <c r="V31" s="29" t="n"/>
+      <c r="U31" s="29" t="inlineStr">
+        <is>
+          <t>rousso.benny@gmail.com</t>
+        </is>
+      </c>
+      <c r="V31" s="29" t="inlineStr">
+        <is>
+          <t>+972544345653</t>
+        </is>
+      </c>
       <c r="W31" s="28" t="inlineStr">
         <is>
           <t>Founder-CEO in medical imaging. Founder DNA, wrong domain, committed.</t>
         </is>
       </c>
-      <c r="X31" s="33" t="n"/>
+      <c r="X31" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 9 · education: תלפיות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="26" t="n">
@@ -12441,7 +13805,11 @@
           <t>OneStep</t>
         </is>
       </c>
-      <c r="I32" s="29" t="n"/>
+      <c r="I32" s="29" t="inlineStr">
+        <is>
+          <t>West Jerusalem, Jerusalem District, Israel</t>
+        </is>
+      </c>
       <c r="J32" s="26" t="n"/>
       <c r="K32" s="35" t="inlineStr">
         <is>
@@ -12461,14 +13829,26 @@
           <t>https://www.linkedin.com/in/benzionkossowsky</t>
         </is>
       </c>
-      <c r="U32" s="29" t="n"/>
-      <c r="V32" s="29" t="n"/>
+      <c r="U32" s="29" t="inlineStr">
+        <is>
+          <t>benzionkossowsky@gmail.com</t>
+        </is>
+      </c>
+      <c r="V32" s="29" t="inlineStr">
+        <is>
+          <t>+972543315821</t>
+        </is>
+      </c>
       <c r="W32" s="28" t="inlineStr">
         <is>
           <t>At OneStep (digital health/motion analysis). No domain evidence.</t>
         </is>
       </c>
-      <c r="X32" s="33" t="n"/>
+      <c r="X32" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 22 · education: אר״מ · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="26" t="n">
@@ -12501,7 +13881,11 @@
           <t>Senior SWE</t>
         </is>
       </c>
-      <c r="I33" s="29" t="n"/>
+      <c r="I33" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J33" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -12525,14 +13909,26 @@
           <t>https://www.linkedin.com/in/eyal-horowicz</t>
         </is>
       </c>
-      <c r="U33" s="29" t="n"/>
-      <c r="V33" s="29" t="n"/>
+      <c r="U33" s="29" t="inlineStr">
+        <is>
+          <t>eyalhoro6@gmail.com</t>
+        </is>
+      </c>
+      <c r="V33" s="29" t="inlineStr">
+        <is>
+          <t>+972506228892</t>
+        </is>
+      </c>
       <c r="W33" s="28" t="inlineStr">
         <is>
           <t>Senior engineer at Claroty (OT/ICS security) - adjacent to industrial control environments, but security-side, not performance/power.</t>
         </is>
       </c>
-      <c r="X33" s="33" t="n"/>
+      <c r="X33" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 36 · education: תלפיות · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="26" t="n">
@@ -12565,7 +13961,11 @@
           <t>CTO</t>
         </is>
       </c>
-      <c r="I34" s="29" t="n"/>
+      <c r="I34" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J34" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -12589,14 +13989,26 @@
           <t>https://www.linkedin.com/in/galwiernik</t>
         </is>
       </c>
-      <c r="U34" s="29" t="n"/>
-      <c r="V34" s="29" t="n"/>
+      <c r="U34" s="29" t="inlineStr">
+        <is>
+          <t>galwiernik@gmail.com</t>
+        </is>
+      </c>
+      <c r="V34" s="29" t="inlineStr">
+        <is>
+          <t>+972502338655</t>
+        </is>
+      </c>
       <c r="W34" s="28" t="inlineStr">
         <is>
           <t>Genuine HPC pedigree: co-author of an IPDPS 2024 paper on fast, stable matrix multiplication - performance engineering of the exact kernels GPUs burn watts on - plus AI-infra experience and TAU research excellence awards. Now CTO at Edwin, so likely unavailable; skills-wise the top available-market operator in the roster.</t>
         </is>
       </c>
-      <c r="X34" s="33" t="n"/>
+      <c r="X34" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ארזים ט׳ · met with: NA · education: ארזים · tags: Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Architect Cohort #2,Fireside Chat,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="26" t="n">
@@ -12629,7 +14041,11 @@
           <t>Director of Engineering</t>
         </is>
       </c>
-      <c r="I35" s="29" t="n"/>
+      <c r="I35" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -12653,14 +14069,26 @@
           <t>https://www.linkedin.com/in/gil-raytan/</t>
         </is>
       </c>
-      <c r="U35" s="29" t="n"/>
-      <c r="V35" s="29" t="n"/>
+      <c r="U35" s="29" t="inlineStr">
+        <is>
+          <t>gil.raytan@gmail.com</t>
+        </is>
+      </c>
+      <c r="V35" s="29" t="inlineStr">
+        <is>
+          <t>+972544322242</t>
+        </is>
+      </c>
       <c r="W35" s="28" t="inlineStr">
         <is>
           <t>Eng leadership over AI/ML at fintech scale. VP-Eng-later-stage profile, not founding GPU-systems fit.</t>
         </is>
       </c>
-      <c r="X35" s="33" t="n"/>
+      <c r="X35" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט · education: פסגות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="26" t="n">
@@ -12693,7 +14121,11 @@
           <t>Building</t>
         </is>
       </c>
-      <c r="I36" s="29" t="n"/>
+      <c r="I36" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J36" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -12717,8 +14149,16 @@
           <t>https://www.linkedin.com/in/yoshpe</t>
         </is>
       </c>
-      <c r="U36" s="29" t="n"/>
-      <c r="V36" s="29" t="n"/>
+      <c r="U36" s="29" t="inlineStr">
+        <is>
+          <t>yoshpe@gmail.com</t>
+        </is>
+      </c>
+      <c r="V36" s="29" t="inlineStr">
+        <is>
+          <t>+972508717313</t>
+        </is>
+      </c>
       <c r="W36" s="28" t="inlineStr">
         <is>
           <t>Proven founder-CTO now at Wiz. Elite cloud engineering environment; application/cloud layer rather than GPU/power systems.</t>
@@ -12757,7 +14197,11 @@
           <t>Co-Founder</t>
         </is>
       </c>
-      <c r="I37" s="29" t="n"/>
+      <c r="I37" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -12781,14 +14225,26 @@
           <t>https://www.linkedin.com/in/hilashmuel/</t>
         </is>
       </c>
-      <c r="U37" s="29" t="n"/>
-      <c r="V37" s="29" t="n"/>
+      <c r="U37" s="29" t="inlineStr">
+        <is>
+          <t>hila4321@gmail.com</t>
+        </is>
+      </c>
+      <c r="V37" s="29" t="inlineStr">
+        <is>
+          <t>+972508871171</t>
+        </is>
+      </c>
       <c r="W37" s="28" t="inlineStr">
         <is>
           <t>AI-product founder. Founder DNA, committed, different layer of the stack.</t>
         </is>
       </c>
-      <c r="X37" s="33" t="n"/>
+      <c r="X37" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: יב · met with: Raised · education: אר״מ · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="26" t="n">
@@ -12821,7 +14277,11 @@
           <t>Co-Founder &amp; CPO</t>
         </is>
       </c>
-      <c r="I38" s="29" t="n"/>
+      <c r="I38" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
           <t>product-gtm</t>
@@ -12845,14 +14305,26 @@
           <t>https://www.linkedin.com/in/iddangolomb/</t>
         </is>
       </c>
-      <c r="U38" s="29" t="n"/>
-      <c r="V38" s="29" t="n"/>
+      <c r="U38" s="29" t="inlineStr">
+        <is>
+          <t>igolomb@gmail.com</t>
+        </is>
+      </c>
+      <c r="V38" s="29" t="inlineStr">
+        <is>
+          <t>+972542421974</t>
+        </is>
+      </c>
       <c r="W38" s="28" t="inlineStr">
         <is>
           <t>Product co-founder. Founder DNA, committed, product-side.</t>
         </is>
       </c>
-      <c r="X38" s="33" t="n"/>
+      <c r="X38" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 25 · education: תלפיות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="26" t="n">
@@ -12885,7 +14357,11 @@
           <t>Algo Team Lead</t>
         </is>
       </c>
-      <c r="I39" s="29" t="n"/>
+      <c r="I39" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J39" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -12909,14 +14385,26 @@
           <t>https://www.linkedin.com/in/idokazma</t>
         </is>
       </c>
-      <c r="U39" s="29" t="n"/>
-      <c r="V39" s="29" t="n"/>
+      <c r="U39" s="29" t="inlineStr">
+        <is>
+          <t>idokazma@gmail.com</t>
+        </is>
+      </c>
+      <c r="V39" s="29" t="inlineStr">
+        <is>
+          <t>+972528584131</t>
+        </is>
+      </c>
       <c r="W39" s="28" t="inlineStr">
         <is>
           <t>Algorithms team lead. Relevant optimization skills, no systems/power record.</t>
         </is>
       </c>
-      <c r="X39" s="33" t="n"/>
+      <c r="X39" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 31 · education: תלפיות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="26" t="n">
@@ -12949,7 +14437,11 @@
           <t>ML &amp; DS Team Leader</t>
         </is>
       </c>
-      <c r="I40" s="29" t="n"/>
+      <c r="I40" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J40" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -12973,14 +14465,26 @@
           <t>https://www.linkedin.com/in/ilan-voronel/</t>
         </is>
       </c>
-      <c r="U40" s="29" t="n"/>
-      <c r="V40" s="29" t="n"/>
+      <c r="U40" s="29" t="inlineStr">
+        <is>
+          <t>ilan.voronel@gmail.com</t>
+        </is>
+      </c>
+      <c r="V40" s="29" t="inlineStr">
+        <is>
+          <t>+972547397052</t>
+        </is>
+      </c>
       <c r="W40" s="28" t="inlineStr">
         <is>
           <t>ML/DS team leadership. No systems/power record.</t>
         </is>
       </c>
-      <c r="X40" s="33" t="n"/>
+      <c r="X40" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 24 · education: תלפיות · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="26" t="n">
@@ -13013,7 +14517,11 @@
           <t>Co-Founder</t>
         </is>
       </c>
-      <c r="I41" s="29" t="n"/>
+      <c r="I41" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J41" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -13032,15 +14540,31 @@
       <c r="Q41" s="29" t="n"/>
       <c r="R41" s="33" t="n"/>
       <c r="S41" s="34" t="n"/>
-      <c r="T41" s="26" t="n"/>
-      <c r="U41" s="29" t="n"/>
-      <c r="V41" s="29" t="n"/>
+      <c r="T41" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonathangilat</t>
+        </is>
+      </c>
+      <c r="U41" s="29" t="inlineStr">
+        <is>
+          <t>jonathan@medida.ai</t>
+        </is>
+      </c>
+      <c r="V41" s="29" t="inlineStr">
+        <is>
+          <t>+972528198278</t>
+        </is>
+      </c>
       <c r="W41" s="28" t="inlineStr">
         <is>
           <t>Talpiot + 8200 co-founder. Committed to Medida; domain (health AI) different.</t>
         </is>
       </c>
-      <c r="X41" s="33" t="n"/>
+      <c r="X41" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 37 · met with: Keep in touch · education: תלפיות · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Architect Cohort #2,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="26" t="n">
@@ -13133,7 +14657,11 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I43" s="29" t="n"/>
+      <c r="I43" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -13157,14 +14685,26 @@
           <t>https://www.linkedin.com/in/liorlevtov</t>
         </is>
       </c>
-      <c r="U43" s="29" t="n"/>
-      <c r="V43" s="29" t="n"/>
+      <c r="U43" s="29" t="inlineStr">
+        <is>
+          <t>liorlevtov@gmail.com</t>
+        </is>
+      </c>
+      <c r="V43" s="29" t="inlineStr">
+        <is>
+          <t>+972542267010</t>
+        </is>
+      </c>
       <c r="W43" s="28" t="inlineStr">
         <is>
           <t>SWE at cloud backup startup. No domain evidence.</t>
         </is>
       </c>
-      <c r="X43" s="33" t="n"/>
+      <c r="X43" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ח · met with: Keep in touch · education: אר״מ · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Mega Connector,Avishag's Substack,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="26" t="n">
@@ -13197,7 +14737,11 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="I44" s="29" t="n"/>
+      <c r="I44" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J44" s="26" t="n"/>
       <c r="K44" s="32" t="inlineStr">
         <is>
@@ -13217,14 +14761,26 @@
           <t>https://www.linkedin.com/in/liran-markin/</t>
         </is>
       </c>
-      <c r="U44" s="29" t="n"/>
-      <c r="V44" s="29" t="n"/>
+      <c r="U44" s="29" t="inlineStr">
+        <is>
+          <t>liran.markin@gmail.com</t>
+        </is>
+      </c>
+      <c r="V44" s="29" t="inlineStr">
+        <is>
+          <t>+972544911254</t>
+        </is>
+      </c>
       <c r="W44" s="28" t="inlineStr">
         <is>
           <t>Founder-CEO (with Gal Wiernik as CTO). Founder DNA; committed to Edwin.</t>
         </is>
       </c>
-      <c r="X44" s="33" t="n"/>
+      <c r="X44" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: קורס י״ט · met with: NA · education: אר״מ · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="26" t="n">
@@ -13277,8 +14833,16 @@
           <t>https://www.linkedin.com/in/michael-komraz/</t>
         </is>
       </c>
-      <c r="U45" s="29" t="n"/>
-      <c r="V45" s="29" t="n"/>
+      <c r="U45" s="29" t="inlineStr">
+        <is>
+          <t>mikomraz@gmail.com</t>
+        </is>
+      </c>
+      <c r="V45" s="29" t="inlineStr">
+        <is>
+          <t>+972544319975</t>
+        </is>
+      </c>
       <c r="W45" s="28" t="inlineStr">
         <is>
           <t>Ex-Snyk CTO office, currently in founder mode. Strong generalist; committed to own thing.</t>
@@ -13341,8 +14905,16 @@
           <t>https://www.linkedin.com/in/michael-z-2355655a</t>
         </is>
       </c>
-      <c r="U46" s="29" t="n"/>
-      <c r="V46" s="29" t="n"/>
+      <c r="U46" s="29" t="inlineStr">
+        <is>
+          <t>giga123@gmail.com</t>
+        </is>
+      </c>
+      <c r="V46" s="29" t="inlineStr">
+        <is>
+          <t>+972527564010</t>
+        </is>
+      </c>
       <c r="W46" s="28" t="inlineStr">
         <is>
           <t>Ex-Amazon, now academic researcher. No power/GPU record.</t>
@@ -13381,7 +14953,11 @@
           <t>SW &amp; Algorithms</t>
         </is>
       </c>
-      <c r="I47" s="29" t="n"/>
+      <c r="I47" s="29" t="inlineStr">
+        <is>
+          <t>Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J47" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -13405,14 +14981,26 @@
           <t>https://www.linkedin.com/in/michal-ran</t>
         </is>
       </c>
-      <c r="U47" s="29" t="n"/>
-      <c r="V47" s="29" t="n"/>
+      <c r="U47" s="29" t="inlineStr">
+        <is>
+          <t>michalran95@gmail.com</t>
+        </is>
+      </c>
+      <c r="V47" s="29" t="inlineStr">
+        <is>
+          <t>+972544443440</t>
+        </is>
+      </c>
       <c r="W47" s="28" t="inlineStr">
         <is>
           <t>Algo engineer in bio/proteomics AI. No domain evidence.</t>
         </is>
       </c>
-      <c r="X47" s="33" t="n"/>
+      <c r="X47" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט״ו · education: פסגות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="26" t="n">
@@ -13445,7 +15033,11 @@
           <t>Founding Engineer</t>
         </is>
       </c>
-      <c r="I48" s="29" t="n"/>
+      <c r="I48" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J48" s="26" t="n"/>
       <c r="K48" s="32" t="inlineStr">
         <is>
@@ -13465,8 +15057,16 @@
           <t>https://www.linkedin.com/in/mor-shemesh-1bb04a155</t>
         </is>
       </c>
-      <c r="U48" s="29" t="n"/>
-      <c r="V48" s="29" t="n"/>
+      <c r="U48" s="29" t="inlineStr">
+        <is>
+          <t>mor.m.shemesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="V48" s="29" t="inlineStr">
+        <is>
+          <t>+972507711998</t>
+        </is>
+      </c>
       <c r="W48" s="28" t="inlineStr">
         <is>
           <t>Stealth founding engineer - unknowable, unavailable.</t>
@@ -13505,7 +15105,11 @@
           <t>Cloud &amp; Tech Alliance Mgr</t>
         </is>
       </c>
-      <c r="I49" s="29" t="n"/>
+      <c r="I49" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -13529,14 +15133,26 @@
           <t>https://www.linkedin.com/in/omer-onn-0b980961</t>
         </is>
       </c>
-      <c r="U49" s="29" t="n"/>
-      <c r="V49" s="29" t="n"/>
+      <c r="U49" s="29" t="inlineStr">
+        <is>
+          <t>omeronn@gmail.com</t>
+        </is>
+      </c>
+      <c r="V49" s="29" t="inlineStr">
+        <is>
+          <t>+972508112332</t>
+        </is>
+      </c>
       <c r="W49" s="28" t="inlineStr">
         <is>
           <t>Real systems depth from DriveNets (carrier-scale networking), but has pivoted to BD/alliances. Better fit for a partnerships role than founding engineering.</t>
         </is>
       </c>
-      <c r="X49" s="33" t="n"/>
+      <c r="X49" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ו · education: פסגות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="26" t="n">
@@ -13565,7 +15181,11 @@
           <t>Team Lead, Security Research</t>
         </is>
       </c>
-      <c r="I50" s="29" t="n"/>
+      <c r="I50" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J50" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -13589,14 +15209,26 @@
           <t>https://www.linkedin.com/in/omri-gotlib-223288260/</t>
         </is>
       </c>
-      <c r="U50" s="29" t="n"/>
-      <c r="V50" s="29" t="n"/>
+      <c r="U50" s="29" t="inlineStr">
+        <is>
+          <t>gotlib.omri@gmail.com</t>
+        </is>
+      </c>
+      <c r="V50" s="29" t="inlineStr">
+        <is>
+          <t>+972528225572</t>
+        </is>
+      </c>
       <c r="W50" s="28" t="inlineStr">
         <is>
           <t>Security research lead. Wrong domain.</t>
         </is>
       </c>
-      <c r="X50" s="33" t="n"/>
+      <c r="X50" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: כ · education: אר״מ · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="26" t="n">
@@ -13629,7 +15261,11 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="I51" s="29" t="n"/>
+      <c r="I51" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -13653,14 +15289,26 @@
           <t>https://www.linkedin.com/in/peleg-ben-hamo-a90034355</t>
         </is>
       </c>
-      <c r="U51" s="29" t="n"/>
-      <c r="V51" s="29" t="n"/>
+      <c r="U51" s="29" t="inlineStr">
+        <is>
+          <t>peleg87@gmail.com</t>
+        </is>
+      </c>
+      <c r="V51" s="29" t="inlineStr">
+        <is>
+          <t>+972524447878</t>
+        </is>
+      </c>
       <c r="W51" s="28" t="inlineStr">
         <is>
           <t>SWE at Cyera. No domain evidence.</t>
         </is>
       </c>
-      <c r="X51" s="33" t="n"/>
+      <c r="X51" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 36 · education: תלפיות · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="26" t="n">
@@ -13693,7 +15341,11 @@
           <t>Senior SWE</t>
         </is>
       </c>
-      <c r="I52" s="29" t="n"/>
+      <c r="I52" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -13717,14 +15369,26 @@
           <t>https://www.linkedin.com/in/ron-galay-0b451662</t>
         </is>
       </c>
-      <c r="U52" s="29" t="n"/>
-      <c r="V52" s="29" t="n"/>
+      <c r="U52" s="29" t="inlineStr">
+        <is>
+          <t>rongalay@gmail.com</t>
+        </is>
+      </c>
+      <c r="V52" s="29" t="inlineStr">
+        <is>
+          <t>+972503039885</t>
+        </is>
+      </c>
       <c r="W52" s="28" t="inlineStr">
         <is>
           <t>Senior SWE at Datadog - large-scale observability is mildly adjacent (telemetry pipelines), but no power/GPU record.</t>
         </is>
       </c>
-      <c r="X52" s="33" t="n"/>
+      <c r="X52" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט · education: פסגות · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="26" t="n">
@@ -13761,7 +15425,11 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="I53" s="29" t="n"/>
+      <c r="I53" s="29" t="inlineStr">
+        <is>
+          <t>Givatayim, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J53" s="26" t="n"/>
       <c r="K53" s="32" t="inlineStr">
         <is>
@@ -13781,14 +15449,26 @@
           <t>https://www.linkedin.com/in/roy-moshe-0727b115b</t>
         </is>
       </c>
-      <c r="U53" s="29" t="n"/>
-      <c r="V53" s="29" t="n"/>
+      <c r="U53" s="29" t="inlineStr">
+        <is>
+          <t>roymoshe23@gmail.com</t>
+        </is>
+      </c>
+      <c r="V53" s="29" t="inlineStr">
+        <is>
+          <t>+972546777815</t>
+        </is>
+      </c>
       <c r="W53" s="28" t="inlineStr">
         <is>
           <t>Stealth CEO, Founder Track. Unknowable and unavailable; track what he's building.</t>
         </is>
       </c>
-      <c r="X53" s="33" t="n"/>
+      <c r="X53" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט״ו · unit: Psagot · domains: Agentic AI Workflow · role tag: CEO · commitment: 2 - רמה בינונית · tags: Apex Inception May 2026</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="26" t="n">
@@ -13821,7 +15501,11 @@
           <t>Algorithm Developer</t>
         </is>
       </c>
-      <c r="I54" s="29" t="n"/>
+      <c r="I54" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J54" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -13840,15 +15524,31 @@
       <c r="Q54" s="29" t="n"/>
       <c r="R54" s="33" t="n"/>
       <c r="S54" s="34" t="n"/>
-      <c r="T54" s="26" t="n"/>
-      <c r="U54" s="29" t="n"/>
-      <c r="V54" s="29" t="n"/>
+      <c r="T54" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shachar-resisi</t>
+        </is>
+      </c>
+      <c r="U54" s="29" t="inlineStr">
+        <is>
+          <t>shachar.resisi@gmail.com</t>
+        </is>
+      </c>
+      <c r="V54" s="29" t="inlineStr">
+        <is>
+          <t>+972542566787</t>
+        </is>
+      </c>
       <c r="W54" s="28" t="inlineStr">
         <is>
           <t>Algorithms at an RF-imaging chip company - hardware-adjacent algo work.</t>
         </is>
       </c>
-      <c r="X54" s="33" t="n"/>
+      <c r="X54" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: א · education: אגוז (לא של גולני) · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="26" t="n">
@@ -13937,7 +15637,11 @@
           <t>Security Researcher (ICS/OT, firmware)</t>
         </is>
       </c>
-      <c r="I56" s="29" t="n"/>
+      <c r="I56" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J56" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -13961,14 +15665,26 @@
           <t>https://www.linkedin.com/in/sharonbrizinov/</t>
         </is>
       </c>
-      <c r="U56" s="29" t="n"/>
-      <c r="V56" s="29" t="n"/>
+      <c r="U56" s="29" t="inlineStr">
+        <is>
+          <t>sharon.brizinov@gmail.com</t>
+        </is>
+      </c>
+      <c r="V56" s="29" t="inlineStr">
+        <is>
+          <t>+972544702148</t>
+        </is>
+      </c>
       <c r="W56" s="28" t="inlineStr">
         <is>
           <t>Elite low-level/firmware vulnerability researcher in the ICS/OT world. Reverse-engineering and firmware depth transfer directly to a layer sitting near GPU firmware/drivers - but it's security, not performance/power, and no infra-scaling record.</t>
         </is>
       </c>
-      <c r="X56" s="33" t="n"/>
+      <c r="X56" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט · met with: Keep in touch · education: סילאן · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="26" t="n">
@@ -14012,15 +15728,31 @@
       <c r="Q57" s="29" t="n"/>
       <c r="R57" s="33" t="n"/>
       <c r="S57" s="34" t="n"/>
-      <c r="T57" s="26" t="n"/>
-      <c r="U57" s="29" t="n"/>
-      <c r="V57" s="29" t="n"/>
+      <c r="T57" s="26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/אין</t>
+        </is>
+      </c>
+      <c r="U57" s="29" t="inlineStr">
+        <is>
+          <t>tomergoren99@gmail.com</t>
+        </is>
+      </c>
+      <c r="V57" s="29" t="inlineStr">
+        <is>
+          <t>+972544744575</t>
+        </is>
+      </c>
       <c r="W57" s="28" t="inlineStr">
         <is>
           <t>In founder mode, domain unknown. Cannot assess.</t>
         </is>
       </c>
-      <c r="X57" s="33" t="n"/>
+      <c r="X57" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 39 · tags: Fireside Chat,Apex Newsletter</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="26" t="n">
@@ -14053,7 +15785,11 @@
           <t>Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="I58" s="29" t="n"/>
+      <c r="I58" s="29" t="inlineStr">
+        <is>
+          <t>Ramat Gan, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J58" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -14077,14 +15813,26 @@
           <t>https://www.linkedin.com/in/tzah-pahima-6b5b75178</t>
         </is>
       </c>
-      <c r="U58" s="29" t="n"/>
-      <c r="V58" s="29" t="n"/>
+      <c r="U58" s="29" t="inlineStr">
+        <is>
+          <t>tzahpahima123@gmail.com</t>
+        </is>
+      </c>
+      <c r="V58" s="29" t="inlineStr">
+        <is>
+          <t>+972538271198</t>
+        </is>
+      </c>
       <c r="W58" s="28" t="inlineStr">
         <is>
           <t>Cloud security researcher. Deep cloud internals knowledge, security-side.</t>
         </is>
       </c>
-      <c r="X58" s="33" t="n"/>
+      <c r="X58" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: ט׳ · education: אר״מ · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="26" t="n">
@@ -14113,7 +15861,11 @@
           <t>MSc Research Student, Weizmann</t>
         </is>
       </c>
-      <c r="I59" s="29" t="n"/>
+      <c r="I59" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Tel-Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J59" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -14137,14 +15889,26 @@
           <t>https://www.linkedin.com/in/yakov-kosoburd-8b8aa127a</t>
         </is>
       </c>
-      <c r="U59" s="29" t="n"/>
-      <c r="V59" s="29" t="n"/>
+      <c r="U59" s="29" t="inlineStr">
+        <is>
+          <t>yakov.kosoburd@gmail.com</t>
+        </is>
+      </c>
+      <c r="V59" s="29" t="inlineStr">
+        <is>
+          <t>+972529508555</t>
+        </is>
+      </c>
       <c r="W59" s="28" t="inlineStr">
         <is>
           <t>Graduate researcher. Insufficient production record.</t>
         </is>
       </c>
-      <c r="X59" s="33" t="n"/>
+      <c r="X59" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 38 · education: תלפיות · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="26" t="n">
@@ -14177,7 +15941,11 @@
           <t>Principal Researcher</t>
         </is>
       </c>
-      <c r="I60" s="29" t="n"/>
+      <c r="I60" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -14201,14 +15969,26 @@
           <t>https://www.linkedin.com/in/yurishapira</t>
         </is>
       </c>
-      <c r="U60" s="29" t="n"/>
-      <c r="V60" s="29" t="n"/>
+      <c r="U60" s="29" t="inlineStr">
+        <is>
+          <t>yurishapira@gmail.com</t>
+        </is>
+      </c>
+      <c r="V60" s="29" t="inlineStr">
+        <is>
+          <t>+972547225688</t>
+        </is>
+      </c>
       <c r="W60" s="28" t="inlineStr">
         <is>
           <t>Principal security researcher/architect. Deep technical, wrong domain.</t>
         </is>
       </c>
-      <c r="X60" s="33" t="n"/>
+      <c r="X60" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] military course: 2003 · education: אחראי מחשוב · tags: 25/2/2026 - Closing Event,Fireside Chat,Apex Newsletter,Signed To Apex,Apex Grad</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="26" t="n">
@@ -14249,8 +16029,16 @@
       <c r="R61" s="33" t="n"/>
       <c r="S61" s="34" t="n"/>
       <c r="T61" s="26" t="n"/>
-      <c r="U61" s="29" t="n"/>
-      <c r="V61" s="29" t="n"/>
+      <c r="U61" s="29" t="inlineStr">
+        <is>
+          <t>cohenadi02@gmail.com</t>
+        </is>
+      </c>
+      <c r="V61" s="29" t="inlineStr">
+        <is>
+          <t>+972543990302</t>
+        </is>
+      </c>
       <c r="W61" s="28" t="inlineStr">
         <is>
           <t>Name too common for reliable public disambiguation; no LinkedIn in roster.</t>
@@ -14316,7 +16104,11 @@
           <t>Embedded SW developer at a voice-AI/DSP startup, ex-Elbit, Technion computer engineering. Embedded/DSP is a relevant profile shape at junior level; no GPU/power record.</t>
         </is>
       </c>
-      <c r="X62" s="33" t="n"/>
+      <c r="X62" s="33" t="inlineStr">
+        <is>
+          <t>[dex import] tags: Architect Cohort #3,30/6/2026 - State of AI</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="26" t="n">
@@ -14345,7 +16137,11 @@
           <t>MSc</t>
         </is>
       </c>
-      <c r="I63" s="29" t="n"/>
+      <c r="I63" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J63" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -14369,8 +16165,16 @@
           <t>https://www.linkedin.com/in/adir-kobovich-004494233</t>
         </is>
       </c>
-      <c r="U63" s="29" t="n"/>
-      <c r="V63" s="29" t="n"/>
+      <c r="U63" s="29" t="inlineStr">
+        <is>
+          <t>adir.kob@gmail.com</t>
+        </is>
+      </c>
+      <c r="V63" s="29" t="inlineStr">
+        <is>
+          <t>+972546540789</t>
+        </is>
+      </c>
       <c r="W63" s="28" t="inlineStr">
         <is>
           <t>Coding-theory researcher (arXiv/IEEE publications) with visible bare-metal/embedded interest. Strong theory, junior, no production systems record yet.</t>
@@ -14409,7 +16213,11 @@
           <t>Likely: AI Security Solution Architect</t>
         </is>
       </c>
-      <c r="I64" s="29" t="n"/>
+      <c r="I64" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J64" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -14433,8 +16241,16 @@
           <t>https://www.linkedin.com/in/alon-wolf</t>
         </is>
       </c>
-      <c r="U64" s="29" t="n"/>
-      <c r="V64" s="29" t="n"/>
+      <c r="U64" s="29" t="inlineStr">
+        <is>
+          <t>alonwolfy@gmail.com</t>
+        </is>
+      </c>
+      <c r="V64" s="29" t="inlineStr">
+        <is>
+          <t>+972546611903</t>
+        </is>
+      </c>
       <c r="W64" s="28" t="inlineStr">
         <is>
           <t>Best identity match: Cyera AI security architect, previously AI research at Decart (a company famous for extreme GPU-efficiency engineering), Talpiot, HUJI BSc + TAU MSc. Decart exposure is a real signal for GPU-efficiency thinking. Identity needs verification (common name incl. a Technion robotics professor).</t>
@@ -14462,10 +16278,14 @@
       <c r="G65" s="26" t="n"/>
       <c r="H65" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I65" s="29" t="n"/>
+          <t>Cyber Security Leader</t>
+        </is>
+      </c>
+      <c r="I65" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J65" s="26" t="n"/>
       <c r="K65" s="35" t="inlineStr">
         <is>
@@ -14485,8 +16305,16 @@
           <t>https://www.linkedin.com/in/amirbalva</t>
         </is>
       </c>
-      <c r="U65" s="29" t="n"/>
-      <c r="V65" s="29" t="n"/>
+      <c r="U65" s="29" t="inlineStr">
+        <is>
+          <t>amirbalva@gmail.com</t>
+        </is>
+      </c>
+      <c r="V65" s="29" t="inlineStr">
+        <is>
+          <t>+972525591311</t>
+        </is>
+      </c>
       <c r="W65" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public technical record for this name.</t>
@@ -14511,13 +16339,21 @@
       </c>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="26" t="n"/>
-      <c r="G66" s="26" t="n"/>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>Franklin by QIAGEN</t>
+        </is>
+      </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I66" s="29" t="n"/>
+          <t>Data Scientist | Impact | Talpiot Alumnus</t>
+        </is>
+      </c>
+      <c r="I66" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J66" s="26" t="n"/>
       <c r="K66" s="35" t="inlineStr">
         <is>
@@ -14537,8 +16373,16 @@
           <t>https://www.linkedin.com/in/amitai-nevo</t>
         </is>
       </c>
-      <c r="U66" s="29" t="n"/>
-      <c r="V66" s="29" t="n"/>
+      <c r="U66" s="29" t="inlineStr">
+        <is>
+          <t>amitai.nevo2@gmail.com</t>
+        </is>
+      </c>
+      <c r="V66" s="29" t="inlineStr">
+        <is>
+          <t>+972522344098</t>
+        </is>
+      </c>
       <c r="W66" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public disambiguation for this name.</t>
@@ -14601,8 +16445,16 @@
           <t>https://linkedin.com/in/ariel-bachar</t>
         </is>
       </c>
-      <c r="U67" s="29" t="n"/>
-      <c r="V67" s="29" t="n"/>
+      <c r="U67" s="29" t="inlineStr">
+        <is>
+          <t>relrelbachar@gmail.com</t>
+        </is>
+      </c>
+      <c r="V67" s="29" t="inlineStr">
+        <is>
+          <t>+972545301526</t>
+        </is>
+      </c>
       <c r="W67" s="28" t="inlineStr">
         <is>
           <t>Senior SWE at Zafran (threat exposure mgmt), ex-military-intelligence security researcher. Solid cyber engineer, wrong domain.</t>
@@ -14649,8 +16501,16 @@
       <c r="R68" s="33" t="n"/>
       <c r="S68" s="34" t="n"/>
       <c r="T68" s="26" t="n"/>
-      <c r="U68" s="29" t="n"/>
-      <c r="V68" s="29" t="n"/>
+      <c r="U68" s="29" t="inlineStr">
+        <is>
+          <t>avichayr@gmail.com</t>
+        </is>
+      </c>
+      <c r="V68" s="29" t="inlineStr">
+        <is>
+          <t>+972526351833</t>
+        </is>
+      </c>
       <c r="W68" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public technical record for this name.</t>
@@ -14681,7 +16541,11 @@
           <t>Quantum Tech Projects Officer, MoD; ex-Rafael; HUJI/Weizmann quantum physics</t>
         </is>
       </c>
-      <c r="I69" s="29" t="n"/>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -14705,8 +16569,16 @@
           <t>https://il.linkedin.com/in/avraham-berrebi-0981b5266</t>
         </is>
       </c>
-      <c r="U69" s="29" t="n"/>
-      <c r="V69" s="29" t="n"/>
+      <c r="U69" s="29" t="inlineStr">
+        <is>
+          <t>avraham.berr@gmail.com</t>
+        </is>
+      </c>
+      <c r="V69" s="29" t="inlineStr">
+        <is>
+          <t>+972526207606</t>
+        </is>
+      </c>
       <c r="W69" s="28" t="inlineStr">
         <is>
           <t>Quantum-technology program leader at MoD, ex-Rafael researcher, PRL-published quantum physics (spin decoherence). Deep hard-tech + program leadership; no GPU/power-software fit.</t>
@@ -14745,7 +16617,11 @@
           <t>Co-Founder &amp; CTO</t>
         </is>
       </c>
-      <c r="I70" s="29" t="n"/>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>Ramat HaSharon, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J70" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -14769,8 +16645,16 @@
           <t>https://www.linkedin.com/in/benny-benjamin-g-93922b</t>
         </is>
       </c>
-      <c r="U70" s="29" t="n"/>
-      <c r="V70" s="29" t="n"/>
+      <c r="U70" s="29" t="inlineStr">
+        <is>
+          <t>benny.getz@gmail.com</t>
+        </is>
+      </c>
+      <c r="V70" s="29" t="inlineStr">
+        <is>
+          <t>+972545551000</t>
+        </is>
+      </c>
       <c r="W70" s="28" t="inlineStr">
         <is>
           <t>25 years of silicon/system architecture: Intel wireless chief-architect roles, Samsung IoT senior director, DSP/signal processing, Talpiot. Deep chip-and-systems architecture DNA - relevant to hardware-aware software - but currently CTO of his own health-AI startup and very senior.</t>
@@ -14795,13 +16679,21 @@
       </c>
       <c r="E71" s="26" t="n"/>
       <c r="F71" s="26" t="n"/>
-      <c r="G71" s="26" t="n"/>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
       <c r="H71" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="n"/>
+          <t>System Architecture Leader | From Ambiguity to Execution</t>
+        </is>
+      </c>
+      <c r="I71" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J71" s="26" t="n"/>
       <c r="K71" s="35" t="inlineStr">
         <is>
@@ -14821,8 +16713,16 @@
           <t>https://www.linkedin.com/in/shasha-david</t>
         </is>
       </c>
-      <c r="U71" s="29" t="n"/>
-      <c r="V71" s="29" t="n"/>
+      <c r="U71" s="29" t="inlineStr">
+        <is>
+          <t>davidroyshasha@gmail.com</t>
+        </is>
+      </c>
+      <c r="V71" s="29" t="inlineStr">
+        <is>
+          <t>+972544961009</t>
+        </is>
+      </c>
       <c r="W71" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public disambiguation for this name.</t>
@@ -14861,7 +16761,11 @@
           <t>Co-Founder &amp; CTO</t>
         </is>
       </c>
-      <c r="I72" s="29" t="n"/>
+      <c r="I72" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J72" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -14885,8 +16789,16 @@
           <t>https://www.linkedin.com/in/dolevelbaz/</t>
         </is>
       </c>
-      <c r="U72" s="29" t="n"/>
-      <c r="V72" s="29" t="n"/>
+      <c r="U72" s="29" t="inlineStr">
+        <is>
+          <t>dolevelb@gmail.com</t>
+        </is>
+      </c>
+      <c r="V72" s="29" t="inlineStr">
+        <is>
+          <t>+972525677675</t>
+        </is>
+      </c>
       <c r="W72" s="28" t="inlineStr">
         <is>
           <t>One of the strongest systems profiles in the roster: built DDoS-protection datapath for Azure's edge in DPDK + Rust as tech lead ('high performance at scale'), embedded Linux + x86 virtualization background, Israel-Defense-Prize-winning projects, Psagot. Exactly the kernel/datapath engineering Joulix needs - but he is co-founder/CTO of his own funded startup, so availability is ~0. Track closely.</t>
@@ -14921,7 +16833,11 @@
           <t>Principal Scientist</t>
         </is>
       </c>
-      <c r="I73" s="29" t="n"/>
+      <c r="I73" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J73" s="26" t="n"/>
       <c r="K73" s="36" t="inlineStr">
         <is>
@@ -14941,8 +16857,16 @@
           <t>https://www.linkedin.com/in/georgy-melamed-0315a71</t>
         </is>
       </c>
-      <c r="U73" s="29" t="n"/>
-      <c r="V73" s="29" t="n"/>
+      <c r="U73" s="29" t="inlineStr">
+        <is>
+          <t>gmelamed@gmail.com</t>
+        </is>
+      </c>
+      <c r="V73" s="29" t="inlineStr">
+        <is>
+          <t>+972523872832</t>
+        </is>
+      </c>
       <c r="W73" s="28" t="inlineStr">
         <is>
           <t>Principal applied scientist (machine vision), ex-Amazon, ex-PrimeSense. Strong applied AI; no power/GPU-systems record.</t>
@@ -14977,7 +16901,11 @@
           <t>Senior SWE / Security Researcher</t>
         </is>
       </c>
-      <c r="I74" s="29" t="n"/>
+      <c r="I74" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J74" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -15001,8 +16929,16 @@
           <t>https://www.linkedin.com/in/guy-goldenberg</t>
         </is>
       </c>
-      <c r="U74" s="29" t="n"/>
-      <c r="V74" s="29" t="n"/>
+      <c r="U74" s="29" t="inlineStr">
+        <is>
+          <t>guy.goldenberg@gmail.com</t>
+        </is>
+      </c>
+      <c r="V74" s="29" t="inlineStr">
+        <is>
+          <t>+972542172153</t>
+        </is>
+      </c>
       <c r="W74" s="28" t="inlineStr">
         <is>
           <t>Senior engineer on Wiz's ASM product line; published vulnerability research. Elite cyber engineering, wrong domain.</t>
@@ -15033,7 +16969,11 @@
         </is>
       </c>
       <c r="H75" s="28" t="n"/>
-      <c r="I75" s="29" t="n"/>
+      <c r="I75" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J75" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -15057,8 +16997,16 @@
           <t>https://www.linkedin.com/in/hillel-twersky</t>
         </is>
       </c>
-      <c r="U75" s="29" t="n"/>
-      <c r="V75" s="29" t="n"/>
+      <c r="U75" s="29" t="inlineStr">
+        <is>
+          <t>hilleltwersky@gmail.com</t>
+        </is>
+      </c>
+      <c r="V75" s="29" t="inlineStr">
+        <is>
+          <t>+972545258759</t>
+        </is>
+      </c>
       <c r="W75" s="28" t="inlineStr">
         <is>
           <t>At a funded AI-hiring startup; specific role and technical record not publicly verifiable against the criteria.</t>
@@ -15097,7 +17045,11 @@
           <t>PhD</t>
         </is>
       </c>
-      <c r="I76" s="29" t="n"/>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J76" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -15121,8 +17073,16 @@
           <t>https://il.linkedin.com/in/idan-lev-yehudi</t>
         </is>
       </c>
-      <c r="U76" s="29" t="n"/>
-      <c r="V76" s="29" t="n"/>
+      <c r="U76" s="29" t="inlineStr">
+        <is>
+          <t>idanly98@gmail.com</t>
+        </is>
+      </c>
+      <c r="V76" s="29" t="inlineStr">
+        <is>
+          <t>+972523059999</t>
+        </is>
+      </c>
       <c r="W76" s="28" t="inlineStr">
         <is>
           <t>Talpiot, ex-Google, publishes at AAAI/RA-L on real-time planning under uncertainty with formal guarantees, where computational cost of models is the core constraint - the intellectual core of Joulix's control loop (decide fast, under uncertainty, with guarantees). No GPU-systems production record; would need a systems counterpart. Best pure 'founding algorithms engineer' bet in cohort #3.</t>
@@ -15147,13 +17107,21 @@
       </c>
       <c r="E77" s="26" t="n"/>
       <c r="F77" s="26" t="n"/>
-      <c r="G77" s="26" t="n"/>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>Toga Networks-a Huawei Company</t>
+        </is>
+      </c>
       <c r="H77" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="n"/>
+          <t>AI Systems Engineer | GPU/NPU Performance, LLM Fine-Tuning, AI-Assisted Development</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J77" s="26" t="n"/>
       <c r="K77" s="35" t="inlineStr">
         <is>
@@ -15173,8 +17141,16 @@
           <t>https://www.linkedin.com/in/ibentsion</t>
         </is>
       </c>
-      <c r="U77" s="29" t="n"/>
-      <c r="V77" s="29" t="n"/>
+      <c r="U77" s="29" t="inlineStr">
+        <is>
+          <t>ibentsion@gmail.com</t>
+        </is>
+      </c>
+      <c r="V77" s="29" t="inlineStr">
+        <is>
+          <t>+972523322722</t>
+        </is>
+      </c>
       <c r="W77" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public disambiguation for this name.</t>
@@ -15202,10 +17178,14 @@
       <c r="G78" s="26" t="n"/>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Unknown (low-level/PL signal on GitHub)</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="n"/>
+          <t>Research Assistant at The Open University of Israel</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J78" s="26" t="n"/>
       <c r="K78" s="35" t="inlineStr">
         <is>
@@ -15225,8 +17205,16 @@
           <t>https://il.linkedin.com/in/ilan-godik-20a47464</t>
         </is>
       </c>
-      <c r="U78" s="29" t="n"/>
-      <c r="V78" s="29" t="n"/>
+      <c r="U78" s="29" t="inlineStr">
+        <is>
+          <t>ilan3580@gmail.com</t>
+        </is>
+      </c>
+      <c r="V78" s="29" t="inlineStr">
+        <is>
+          <t>+972503028929</t>
+        </is>
+      </c>
       <c r="W78" s="28" t="inlineStr">
         <is>
           <t>Public footprint shows serious functional-programming/type-theory/low-level inclination (active OSS, x86/Haskell/Scala work) - the profile shape of a great kernel engineer - but no verifiable GPU, power, or production-systems record against the criteria. Worth a screening call.</t>
@@ -15261,7 +17249,11 @@
           <t>Threat Detection Lead</t>
         </is>
       </c>
-      <c r="I79" s="29" t="n"/>
+      <c r="I79" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J79" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -15285,8 +17277,16 @@
           <t>https://www.linkedin.com/in/igilad/</t>
         </is>
       </c>
-      <c r="U79" s="29" t="n"/>
-      <c r="V79" s="29" t="n"/>
+      <c r="U79" s="29" t="inlineStr">
+        <is>
+          <t>itamar.gilad@wiz.io</t>
+        </is>
+      </c>
+      <c r="V79" s="29" t="inlineStr">
+        <is>
+          <t>+972504787314</t>
+        </is>
+      </c>
       <c r="W79" s="28" t="inlineStr">
         <is>
           <t>Threat-detection lead at Wiz, ex-Microsoft architecture &amp; security lead for large-scale data services. Elite security engineering; no power/GPU/performance record.</t>
@@ -15325,7 +17325,11 @@
           <t>VP R&amp;D</t>
         </is>
       </c>
-      <c r="I80" s="29" t="n"/>
+      <c r="I80" s="29" t="inlineStr">
+        <is>
+          <t>Center District, Israel</t>
+        </is>
+      </c>
       <c r="J80" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -15349,8 +17353,16 @@
           <t>https://www.linkedin.com/in/itay-gissis/</t>
         </is>
       </c>
-      <c r="U80" s="29" t="n"/>
-      <c r="V80" s="29" t="n"/>
+      <c r="U80" s="29" t="inlineStr">
+        <is>
+          <t>itaigiss@gmail.com</t>
+        </is>
+      </c>
+      <c r="V80" s="29" t="inlineStr">
+        <is>
+          <t>+972504039870</t>
+        </is>
+      </c>
       <c r="W80" s="28" t="inlineStr">
         <is>
           <t>VP R&amp;D at a fusion-energy startup pitching power for the data-hungry world; Technion PhD in pulsed power/plasma. Deep energy-domain physics + multidisciplinary R&amp;D leadership. Not GPU software; committed to nT-Tao. Excellent energy-domain advisor.</t>
@@ -15378,10 +17390,14 @@
       <c r="G81" s="26" t="n"/>
       <c r="H81" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I81" s="29" t="n"/>
+          <t>Tech Executive Bridging Deep-Tech and Software at Scale | Cyber, Data &amp; AI, RF | System Architecture &amp; Engineering Leadership  |  Project Execution |  TALPIOT |  8200  |  Unit 81</t>
+        </is>
+      </c>
+      <c r="I81" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J81" s="26" t="n"/>
       <c r="K81" s="35" t="inlineStr">
         <is>
@@ -15401,8 +17417,16 @@
           <t>https://www.linkedin.com/in/itzhak-bernstein-606808153</t>
         </is>
       </c>
-      <c r="U81" s="29" t="n"/>
-      <c r="V81" s="29" t="n"/>
+      <c r="U81" s="29" t="inlineStr">
+        <is>
+          <t>yitzhokt2@gmail.com</t>
+        </is>
+      </c>
+      <c r="V81" s="29" t="inlineStr">
+        <is>
+          <t>+972529280436</t>
+        </is>
+      </c>
       <c r="W81" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public technical record for this profile.</t>
@@ -15441,7 +17465,11 @@
           <t>PhD</t>
         </is>
       </c>
-      <c r="I82" s="29" t="n"/>
+      <c r="I82" s="29" t="inlineStr">
+        <is>
+          <t>Haifa, Haifa District, Israel</t>
+        </is>
+      </c>
       <c r="J82" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -15465,8 +17493,16 @@
           <t>https://www.linkedin.com/in/liad-ben-uri-58a034167</t>
         </is>
       </c>
-      <c r="U82" s="29" t="n"/>
-      <c r="V82" s="29" t="n"/>
+      <c r="U82" s="29" t="inlineStr">
+        <is>
+          <t>liadgo2@gmail.com</t>
+        </is>
+      </c>
+      <c r="V82" s="29" t="inlineStr">
+        <is>
+          <t>+972546326372</t>
+        </is>
+      </c>
       <c r="W82" s="28" t="inlineStr">
         <is>
           <t>Rare combination for Joulix: twice Israel Defense Prize for physics-based sensing + AI in complex sensor systems, then managed the Israeli Air Force's Energy Division (renewable energy, efficiency, IDF climate plan), Technion MSc in AI, Talpiot. Literal energy-management leadership + elite AI - the best conceptual match in cohort #3. Currently committed to a Weizmann PhD.</t>
@@ -15501,7 +17537,11 @@
           <t>Chief Platform Innovation Officer</t>
         </is>
       </c>
-      <c r="I83" s="29" t="n"/>
+      <c r="I83" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J83" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -15525,8 +17565,16 @@
           <t>https://www.linkedin.com/in/mark-popov-92759b77</t>
         </is>
       </c>
-      <c r="U83" s="29" t="n"/>
-      <c r="V83" s="29" t="n"/>
+      <c r="U83" s="29" t="inlineStr">
+        <is>
+          <t>mark.popov@gmail.com</t>
+        </is>
+      </c>
+      <c r="V83" s="29" t="inlineStr">
+        <is>
+          <t>+972544321050</t>
+        </is>
+      </c>
       <c r="W83" s="28" t="inlineStr">
         <is>
           <t>C-level platform/innovation leadership at an RF-imaging chip company - real hardware-platform depth at a semiconductor player. Senior and committed; no GPU/power-software record.</t>
@@ -15561,7 +17609,11 @@
           <t>Algorithms Team Lead</t>
         </is>
       </c>
-      <c r="I84" s="29" t="n"/>
+      <c r="I84" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J84" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -15585,8 +17637,16 @@
           <t>https://il.linkedin.com/in/matan-shoef-05a22a155</t>
         </is>
       </c>
-      <c r="U84" s="29" t="n"/>
-      <c r="V84" s="29" t="n"/>
+      <c r="U84" s="29" t="inlineStr">
+        <is>
+          <t>matan.shoef@gmail.com</t>
+        </is>
+      </c>
+      <c r="V84" s="29" t="inlineStr">
+        <is>
+          <t>+972545221060</t>
+        </is>
+      </c>
       <c r="W84" s="28" t="inlineStr">
         <is>
           <t>Algorithms team lead, ex-Samsung R&amp;D, Technion EE. Solid algo engineering; no domain evidence.</t>
@@ -15633,8 +17693,16 @@
       <c r="R85" s="33" t="n"/>
       <c r="S85" s="34" t="n"/>
       <c r="T85" s="26" t="n"/>
-      <c r="U85" s="29" t="n"/>
-      <c r="V85" s="29" t="n"/>
+      <c r="U85" s="29" t="inlineStr">
+        <is>
+          <t>mayak144@gmail.com</t>
+        </is>
+      </c>
+      <c r="V85" s="29" t="inlineStr">
+        <is>
+          <t>+972552242152</t>
+        </is>
+      </c>
       <c r="W85" s="28" t="inlineStr">
         <is>
           <t>No LinkedIn in roster; no reliable public record found.</t>
@@ -15681,8 +17749,16 @@
       <c r="R86" s="33" t="n"/>
       <c r="S86" s="34" t="n"/>
       <c r="T86" s="26" t="n"/>
-      <c r="U86" s="29" t="n"/>
-      <c r="V86" s="29" t="n"/>
+      <c r="U86" s="29" t="inlineStr">
+        <is>
+          <t>maya.naveh.40@gmail.com</t>
+        </is>
+      </c>
+      <c r="V86" s="29" t="inlineStr">
+        <is>
+          <t>+972504291882</t>
+        </is>
+      </c>
       <c r="W86" s="28" t="inlineStr">
         <is>
           <t>No LinkedIn in roster; web search returned no reliable disambiguation.</t>
@@ -15729,8 +17805,16 @@
       <c r="R87" s="33" t="n"/>
       <c r="S87" s="34" t="n"/>
       <c r="T87" s="26" t="n"/>
-      <c r="U87" s="29" t="n"/>
-      <c r="V87" s="29" t="n"/>
+      <c r="U87" s="29" t="inlineStr">
+        <is>
+          <t>meny1237@gmail.com</t>
+        </is>
+      </c>
+      <c r="V87" s="29" t="inlineStr">
+        <is>
+          <t>+972542338686</t>
+        </is>
+      </c>
       <c r="W87" s="28" t="inlineStr">
         <is>
           <t>No LinkedIn in roster; no reliable public record found.</t>
@@ -15761,7 +17845,11 @@
           <t>Stealth; reverse-engineering / binary-exploitation background</t>
         </is>
       </c>
-      <c r="I88" s="29" t="n"/>
+      <c r="I88" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J88" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -15785,8 +17873,16 @@
           <t>https://www.linkedin.com/in/nadav-claude-cohen-8533b2a2/</t>
         </is>
       </c>
-      <c r="U88" s="29" t="n"/>
-      <c r="V88" s="29" t="n"/>
+      <c r="U88" s="29" t="inlineStr">
+        <is>
+          <t>nadav.claude.cohen@gmail.com</t>
+        </is>
+      </c>
+      <c r="V88" s="29" t="inlineStr">
+        <is>
+          <t>+972543134989</t>
+        </is>
+      </c>
       <c r="W88" s="28" t="inlineStr">
         <is>
           <t>Personal blog demonstrates real low-level depth (ASLR/PIE exploitation, RE). Profile shape of a systems engineer; currently at stealth; no verifiable GPU/power record.</t>
@@ -15811,13 +17907,21 @@
       </c>
       <c r="E89" s="26" t="n"/>
       <c r="F89" s="26" t="n"/>
-      <c r="G89" s="26" t="n"/>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>Tel Aviv University</t>
+        </is>
+      </c>
       <c r="H89" s="28" t="inlineStr">
         <is>
-          <t>IDENTITY CHECK: possibly Prof. Nadav Cohen (TAU CS professor; Co-Founder/CTO, Imubit)</t>
-        </is>
-      </c>
-      <c r="I89" s="29" t="n"/>
+          <t>CTO at Imubit / Prof. of Computer Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="I89" s="29" t="inlineStr">
+        <is>
+          <t>Houston, Texas, United States of America</t>
+        </is>
+      </c>
       <c r="J89" s="26" t="inlineStr">
         <is>
           <t>research</t>
@@ -15841,7 +17945,11 @@
           <t>https://www.linkedin.com/in/dr-nadav-cohen-05575825a</t>
         </is>
       </c>
-      <c r="U89" s="29" t="n"/>
+      <c r="U89" s="29" t="inlineStr">
+        <is>
+          <t>nadav@deepinsight.co.il</t>
+        </is>
+      </c>
       <c r="V89" s="29" t="n"/>
       <c r="W89" s="28" t="inlineStr">
         <is>
@@ -15873,7 +17981,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I90" s="29" t="n"/>
+      <c r="I90" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J90" s="26" t="n"/>
       <c r="K90" s="35" t="inlineStr">
         <is>
@@ -15893,8 +18005,16 @@
           <t>https://www.linkedin.com/in/noga-keren</t>
         </is>
       </c>
-      <c r="U90" s="29" t="n"/>
-      <c r="V90" s="29" t="n"/>
+      <c r="U90" s="29" t="inlineStr">
+        <is>
+          <t>noga.keren@gmail.com</t>
+        </is>
+      </c>
+      <c r="V90" s="29" t="inlineStr">
+        <is>
+          <t>+972586110398</t>
+        </is>
+      </c>
       <c r="W90" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public disambiguation for this name.</t>
@@ -15925,7 +18045,11 @@
         </is>
       </c>
       <c r="H91" s="28" t="n"/>
-      <c r="I91" s="29" t="n"/>
+      <c r="I91" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J91" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -15949,8 +18073,16 @@
           <t>https://www.linkedin.com/in/noy-hadar-501870181</t>
         </is>
       </c>
-      <c r="U91" s="29" t="n"/>
-      <c r="V91" s="29" t="n"/>
+      <c r="U91" s="29" t="inlineStr">
+        <is>
+          <t>noyhadar95@gmail.com</t>
+        </is>
+      </c>
+      <c r="V91" s="29" t="inlineStr">
+        <is>
+          <t>+972544826333</t>
+        </is>
+      </c>
       <c r="W91" s="28" t="inlineStr">
         <is>
           <t>At Breeze Security (Dolev Elbaz's startup). No domain evidence.</t>
@@ -15985,7 +18117,11 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="I92" s="29" t="n"/>
+      <c r="I92" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J92" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -16009,8 +18145,16 @@
           <t>https://www.linkedin.com/in/orenfine2021/</t>
         </is>
       </c>
-      <c r="U92" s="29" t="n"/>
-      <c r="V92" s="29" t="n"/>
+      <c r="U92" s="29" t="inlineStr">
+        <is>
+          <t>orenfine@gmail.com</t>
+        </is>
+      </c>
+      <c r="V92" s="29" t="inlineStr">
+        <is>
+          <t>+972586392129</t>
+        </is>
+      </c>
       <c r="W92" s="28" t="inlineStr">
         <is>
           <t>Leads Israel-Innovation-Authority-funded research on ultrafast encrypted-traffic understanding powered by NVIDIA SmartNIC/DPU - genuinely close to modern GPU data-center infrastructure. Building his own stealth startup, so likely unavailable; strong advisor/partner candidate.</t>
@@ -16045,7 +18189,11 @@
           <t>Builder; AI harness engineering speaker; embedded hobbyist</t>
         </is>
       </c>
-      <c r="I93" s="29" t="n"/>
+      <c r="I93" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J93" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -16069,8 +18217,16 @@
           <t>https://www.linkedin.com/in/oztamir/</t>
         </is>
       </c>
-      <c r="U93" s="29" t="n"/>
-      <c r="V93" s="29" t="n"/>
+      <c r="U93" s="29" t="inlineStr">
+        <is>
+          <t>oz@tamir.fun</t>
+        </is>
+      </c>
+      <c r="V93" s="29" t="inlineStr">
+        <is>
+          <t>+972528645340</t>
+        </is>
+      </c>
       <c r="W93" s="28" t="inlineStr">
         <is>
           <t>Prolific builder-generalist: talks on AI 'harness engineering' (built a Claude-Code-style agent harness from scratch), OSS incl. x86 assembly and ESP32/embedded projects. High-energy 0-to-1 engineer for the agentic tooling around the product; not a GPU/power-systems specialist.</t>
@@ -16105,7 +18261,11 @@
           <t>Co-Founder &amp; CTO</t>
         </is>
       </c>
-      <c r="I94" s="29" t="n"/>
+      <c r="I94" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J94" s="26" t="n"/>
       <c r="K94" s="32" t="inlineStr">
         <is>
@@ -16125,8 +18285,16 @@
           <t>https://il.linkedin.com/in/shlomolahav</t>
         </is>
       </c>
-      <c r="U94" s="29" t="n"/>
-      <c r="V94" s="29" t="n"/>
+      <c r="U94" s="29" t="inlineStr">
+        <is>
+          <t>shlomo@lahavs.com</t>
+        </is>
+      </c>
+      <c r="V94" s="29" t="inlineStr">
+        <is>
+          <t>+972545330111</t>
+        </is>
+      </c>
       <c r="W94" s="28" t="inlineStr">
         <is>
           <t>Long-tenured data-science leader (built LivePerson's sentiment/emotion engines), now founding his own company. Senior ML leadership; committed; no power/GPU record.</t>
@@ -16157,7 +18325,11 @@
           <t>Intel Granulate</t>
         </is>
       </c>
-      <c r="I95" s="29" t="n"/>
+      <c r="I95" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J95" s="26" t="inlineStr">
         <is>
           <t>infra-systems</t>
@@ -16181,8 +18353,16 @@
           <t>https://www.linkedin.com/in/uri-chen/</t>
         </is>
       </c>
-      <c r="U95" s="29" t="n"/>
-      <c r="V95" s="29" t="n"/>
+      <c r="U95" s="29" t="inlineStr">
+        <is>
+          <t>uriariel10@gmail.com</t>
+        </is>
+      </c>
+      <c r="V95" s="29" t="inlineStr">
+        <is>
+          <t>+972549703632</t>
+        </is>
+      </c>
       <c r="W95" s="28" t="inlineStr">
         <is>
           <t>At Intel Granulate - autonomous, real-time, agent-based workload/runtime optimization in production, acquired by Intel. This is the closest commercial analog to Joulix's value proposition (continuous compute-efficiency optimization), on the CPU side. Highest-priority screening call in cohort #3. (Minor caveat: roster slug differs from the public profile found; verify same person.)</t>
@@ -16217,7 +18397,11 @@
           <t>Stealth; ex-Computer Vision Group Leader</t>
         </is>
       </c>
-      <c r="I96" s="29" t="n"/>
+      <c r="I96" s="29" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="J96" s="26" t="inlineStr">
         <is>
           <t>ai-ml</t>
@@ -16241,8 +18425,16 @@
           <t>https://www.linkedin.com/in/yaniv-shaked-201b6540/</t>
         </is>
       </c>
-      <c r="U96" s="29" t="n"/>
-      <c r="V96" s="29" t="n"/>
+      <c r="U96" s="29" t="inlineStr">
+        <is>
+          <t>yanivsh002@gmail.com</t>
+        </is>
+      </c>
+      <c r="V96" s="29" t="inlineStr">
+        <is>
+          <t>+972525621097</t>
+        </is>
+      </c>
       <c r="W96" s="28" t="inlineStr">
         <is>
           <t>Led Samsung Israel's computer-vision group; now at a stealth startup. Strong algo leadership; CV domain, availability unclear.</t>
@@ -16277,7 +18469,11 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I97" s="29" t="n"/>
+      <c r="I97" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J97" s="26" t="inlineStr">
         <is>
           <t>security</t>
@@ -16301,8 +18497,16 @@
           <t>https://il.linkedin.com/in/yoni-hornstein-082177156</t>
         </is>
       </c>
-      <c r="U97" s="29" t="n"/>
-      <c r="V97" s="29" t="n"/>
+      <c r="U97" s="29" t="inlineStr">
+        <is>
+          <t>yoni.horn@gmail.com</t>
+        </is>
+      </c>
+      <c r="V97" s="29" t="inlineStr">
+        <is>
+          <t>+972502758710</t>
+        </is>
+      </c>
       <c r="W97" s="28" t="inlineStr">
         <is>
           <t>SWE at Wiz. No domain evidence.</t>
@@ -16327,13 +18531,21 @@
       </c>
       <c r="E98" s="26" t="n"/>
       <c r="F98" s="26" t="n"/>
-      <c r="G98" s="26" t="n"/>
+      <c r="G98" s="26" t="inlineStr">
+        <is>
+          <t>Government of Israel</t>
+        </is>
+      </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I98" s="29" t="n"/>
+          <t>Head of R&amp;D Section | Talpiot</t>
+        </is>
+      </c>
+      <c r="I98" s="29" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+        </is>
+      </c>
       <c r="J98" s="26" t="n"/>
       <c r="K98" s="35" t="inlineStr">
         <is>
@@ -16353,8 +18565,16 @@
           <t>https://www.linkedin.com/in/yuvalgenossar</t>
         </is>
       </c>
-      <c r="U98" s="29" t="n"/>
-      <c r="V98" s="29" t="n"/>
+      <c r="U98" s="29" t="inlineStr">
+        <is>
+          <t>yuval.genossar@gmail.com</t>
+        </is>
+      </c>
+      <c r="V98" s="29" t="inlineStr">
+        <is>
+          <t>+972547260186</t>
+        </is>
+      </c>
       <c r="W98" s="28" t="inlineStr">
         <is>
           <t>Web search returned no reliable public disambiguation (results match a different academic).</t>

--- a/plan/2026-2027/APEX-Yearly-Plan.xlsx
+++ b/plan/2026-2027/APEX-Yearly-Plan.xlsx
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I4" s="28" t="inlineStr">
@@ -1697,8 +1697,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr"/>
-      <c r="K4" s="26" t="inlineStr"/>
+      <c r="J4" s="26" t="inlineStr">
+        <is>
+          <t>+972549441034</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
+        <is>
+          <t>ekepten@gmail.com</t>
+        </is>
+      </c>
       <c r="L4" s="29" t="n"/>
       <c r="M4" s="29" t="n"/>
     </row>
@@ -1791,7 +1799,7 @@
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr">
@@ -1799,8 +1807,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr"/>
-      <c r="K6" s="26" t="inlineStr"/>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>+972503485015</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>eyalkraft@gmail.com</t>
+        </is>
+      </c>
       <c r="L6" s="29" t="n"/>
       <c r="M6" s="29" t="n"/>
     </row>
@@ -1893,7 +1909,7 @@
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I8" s="28" t="inlineStr">
@@ -1901,8 +1917,16 @@
           <t>What can they give — office hours, referrals into Miggo, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr"/>
-      <c r="K8" s="26" t="inlineStr"/>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>+972543140162</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>gaigutherz@gmail.com</t>
+        </is>
+      </c>
       <c r="L8" s="29" t="n"/>
       <c r="M8" s="29" t="n"/>
     </row>
@@ -1953,7 +1977,11 @@
           <t>+972524056440</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr"/>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>danielohayon444@gmail.com</t>
+        </is>
+      </c>
       <c r="L9" s="29" t="n"/>
       <c r="M9" s="29" t="n"/>
     </row>
@@ -1991,7 +2019,7 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I10" s="28" t="inlineStr">
@@ -1999,8 +2027,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr"/>
-      <c r="K10" s="26" t="inlineStr"/>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
+          <t>+972528759227</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>inbal.beracha@gmail.com</t>
+        </is>
+      </c>
       <c r="L10" s="29" t="n"/>
       <c r="M10" s="29" t="n"/>
     </row>
@@ -2038,7 +2074,7 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">
@@ -2046,8 +2082,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr"/>
-      <c r="K11" s="26" t="inlineStr"/>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>+972543183227</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>madest@gmail.com</t>
+        </is>
+      </c>
       <c r="L11" s="29" t="n"/>
       <c r="M11" s="29" t="n"/>
     </row>
@@ -2195,7 +2239,7 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I14" s="28" t="inlineStr">
@@ -2203,8 +2247,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr"/>
-      <c r="K14" s="26" t="inlineStr"/>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>+972527495040</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>nadavzemach@gmail.com</t>
+        </is>
+      </c>
       <c r="L14" s="29" t="n"/>
       <c r="M14" s="29" t="n"/>
     </row>
@@ -2242,7 +2294,7 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I15" s="28" t="inlineStr">
@@ -2250,8 +2302,16 @@
           <t>What can they give — office hours, referrals into Hopper Security, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr"/>
-      <c r="K15" s="26" t="inlineStr"/>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>+972524546876</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>noyduany@gmail.com</t>
+        </is>
+      </c>
       <c r="L15" s="29" t="n"/>
       <c r="M15" s="29" t="n"/>
     </row>
@@ -2289,7 +2349,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I16" s="28" t="inlineStr">
@@ -2297,8 +2357,16 @@
           <t>Stay current — what are they working on in product-gtm now, and what would help?</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr"/>
-      <c r="K16" s="26" t="inlineStr"/>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>+972544558495</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>dror.ben@gmail.com</t>
+        </is>
+      </c>
       <c r="L16" s="29" t="n"/>
       <c r="M16" s="29" t="n"/>
     </row>
@@ -2336,7 +2404,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I17" s="28" t="inlineStr">
@@ -2344,8 +2412,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr"/>
-      <c r="K17" s="26" t="inlineStr"/>
+      <c r="J17" s="26" t="inlineStr">
+        <is>
+          <t>+972504445453</t>
+        </is>
+      </c>
+      <c r="K17" s="26" t="inlineStr">
+        <is>
+          <t>uri@urishaked.com</t>
+        </is>
+      </c>
       <c r="L17" s="29" t="n"/>
       <c r="M17" s="29" t="n"/>
     </row>
@@ -2383,7 +2459,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I18" s="28" t="inlineStr">
@@ -2391,7 +2467,11 @@
           <t>Transition point — what are they building or moving toward, what is the blocker, and who should they meet?</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr"/>
+      <c r="J18" s="26" t="inlineStr">
+        <is>
+          <t>+972524774655</t>
+        </is>
+      </c>
       <c r="K18" s="26" t="inlineStr">
         <is>
           <t>zviwex@gmail.com</t>
@@ -2434,7 +2514,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I19" s="28" t="inlineStr">
@@ -2442,8 +2522,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr"/>
-      <c r="K19" s="26" t="inlineStr"/>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>+972546618606</t>
+        </is>
+      </c>
+      <c r="K19" s="26" t="inlineStr">
+        <is>
+          <t>amosy3@gmail.com</t>
+        </is>
+      </c>
       <c r="L19" s="29" t="n"/>
       <c r="M19" s="29" t="n"/>
     </row>
@@ -2481,7 +2569,7 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I20" s="28" t="inlineStr">
@@ -2489,8 +2577,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr"/>
-      <c r="K20" s="26" t="inlineStr"/>
+      <c r="J20" s="26" t="inlineStr">
+        <is>
+          <t>+972526699700</t>
+        </is>
+      </c>
+      <c r="K20" s="26" t="inlineStr">
+        <is>
+          <t>omerhay95@gmail.com</t>
+        </is>
+      </c>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
     </row>
@@ -2528,7 +2624,7 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
@@ -2536,8 +2632,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr"/>
-      <c r="K21" s="26" t="inlineStr"/>
+      <c r="J21" s="26" t="inlineStr">
+        <is>
+          <t>+972544976983</t>
+        </is>
+      </c>
+      <c r="K21" s="26" t="inlineStr">
+        <is>
+          <t>rami@anatifamily.com</t>
+        </is>
+      </c>
       <c r="L21" s="29" t="n"/>
       <c r="M21" s="29" t="n"/>
     </row>
@@ -2685,7 +2789,7 @@
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I24" s="28" t="inlineStr">
@@ -2693,8 +2797,16 @@
           <t>What can they give — office hours, referrals into Ministry of Defense, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr"/>
-      <c r="K24" s="26" t="inlineStr"/>
+      <c r="J24" s="26" t="inlineStr">
+        <is>
+          <t>+972585550675</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
+        <is>
+          <t>roee.yaron.40@gmail.com</t>
+        </is>
+      </c>
       <c r="L24" s="29" t="n"/>
       <c r="M24" s="29" t="n"/>
     </row>
@@ -2732,7 +2844,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I25" s="28" t="inlineStr">
@@ -2740,8 +2852,16 @@
           <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
         </is>
       </c>
-      <c r="J25" s="26" t="inlineStr"/>
-      <c r="K25" s="26" t="inlineStr"/>
+      <c r="J25" s="26" t="inlineStr">
+        <is>
+          <t>+972544343258</t>
+        </is>
+      </c>
+      <c r="K25" s="26" t="inlineStr">
+        <is>
+          <t>njyaron@gmail.com</t>
+        </is>
+      </c>
       <c r="L25" s="29" t="n"/>
       <c r="M25" s="29" t="n"/>
     </row>
@@ -2889,7 +3009,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I28" s="28" t="inlineStr">
@@ -2897,8 +3017,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J28" s="26" t="inlineStr"/>
-      <c r="K28" s="26" t="inlineStr"/>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>+972544661198</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>turronen@gmail.com</t>
+        </is>
+      </c>
       <c r="L28" s="29" t="n"/>
       <c r="M28" s="29" t="n"/>
     </row>
@@ -2936,7 +3064,7 @@
       </c>
       <c r="H29" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I29" s="28" t="inlineStr">
@@ -2944,8 +3072,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J29" s="26" t="inlineStr"/>
-      <c r="K29" s="26" t="inlineStr"/>
+      <c r="J29" s="26" t="inlineStr">
+        <is>
+          <t>+972546729998</t>
+        </is>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>shachar64@gmail.com</t>
+        </is>
+      </c>
       <c r="L29" s="29" t="n"/>
       <c r="M29" s="29" t="n"/>
     </row>
@@ -3093,7 +3229,7 @@
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I32" s="28" t="inlineStr">
@@ -3101,8 +3237,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J32" s="26" t="inlineStr"/>
-      <c r="K32" s="26" t="inlineStr"/>
+      <c r="J32" s="26" t="inlineStr">
+        <is>
+          <t>+972528039532</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>shaielro@gmail.com</t>
+        </is>
+      </c>
       <c r="L32" s="29" t="n"/>
       <c r="M32" s="29" t="n"/>
     </row>
@@ -3470,7 +3614,7 @@
       </c>
       <c r="H39" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I39" s="28" t="inlineStr">
@@ -3478,8 +3622,16 @@
           <t>Stay current — still at Cyera? What are they working on in security, and what would help?</t>
         </is>
       </c>
-      <c r="J39" s="26" t="inlineStr"/>
-      <c r="K39" s="26" t="inlineStr"/>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>+972546793903</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>kfirshoar@gmail.com</t>
+        </is>
+      </c>
       <c r="L39" s="29" t="n"/>
       <c r="M39" s="29" t="n"/>
     </row>
@@ -4292,7 +4444,7 @@
       </c>
       <c r="I54" s="28" t="inlineStr">
         <is>
-          <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
+          <t>Tell Dolev whether Apex wants the Ron Zaidman / Israel Sofer intros, and whether the F2 or Apple-lecturer offers are relevant</t>
         </is>
       </c>
       <c r="J54" s="26" t="inlineStr">
@@ -4507,7 +4659,7 @@
       </c>
       <c r="H58" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -4515,8 +4667,16 @@
           <t>What can they give — office hours, referrals into TAU, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J58" s="26" t="inlineStr"/>
-      <c r="K58" s="26" t="inlineStr"/>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>+972547530590</t>
+        </is>
+      </c>
+      <c r="K58" s="26" t="inlineStr">
+        <is>
+          <t>shaked@yehezkel.net</t>
+        </is>
+      </c>
       <c r="L58" s="29" t="n"/>
       <c r="M58" s="29" t="n"/>
     </row>
@@ -5159,7 +5319,7 @@
       </c>
       <c r="H70" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -5167,8 +5327,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J70" s="26" t="inlineStr"/>
-      <c r="K70" s="26" t="inlineStr"/>
+      <c r="J70" s="26" t="inlineStr">
+        <is>
+          <t>+972503485015</t>
+        </is>
+      </c>
+      <c r="K70" s="26" t="inlineStr">
+        <is>
+          <t>eyalkraft@gmail.com</t>
+        </is>
+      </c>
       <c r="L70" s="29" t="n"/>
       <c r="M70" s="29" t="n"/>
     </row>
@@ -5206,7 +5374,7 @@
       </c>
       <c r="H71" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I71" s="28" t="inlineStr">
@@ -5214,8 +5382,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J71" s="26" t="inlineStr"/>
-      <c r="K71" s="26" t="inlineStr"/>
+      <c r="J71" s="26" t="inlineStr">
+        <is>
+          <t>+972528759227</t>
+        </is>
+      </c>
+      <c r="K71" s="26" t="inlineStr">
+        <is>
+          <t>inbal.beracha@gmail.com</t>
+        </is>
+      </c>
       <c r="L71" s="29" t="n"/>
       <c r="M71" s="29" t="n"/>
     </row>
@@ -5363,7 +5539,7 @@
       </c>
       <c r="H74" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I74" s="28" t="inlineStr">
@@ -5371,8 +5547,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J74" s="26" t="inlineStr"/>
-      <c r="K74" s="26" t="inlineStr"/>
+      <c r="J74" s="26" t="inlineStr">
+        <is>
+          <t>+972543183227</t>
+        </is>
+      </c>
+      <c r="K74" s="26" t="inlineStr">
+        <is>
+          <t>madest@gmail.com</t>
+        </is>
+      </c>
       <c r="L74" s="29" t="n"/>
       <c r="M74" s="29" t="n"/>
     </row>
@@ -5465,7 +5649,7 @@
       </c>
       <c r="H76" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -5473,8 +5657,16 @@
           <t>Stay current — still at Kardome (voice AI)? What are they working on in ai-ml, and what would help?</t>
         </is>
       </c>
-      <c r="J76" s="26" t="inlineStr"/>
-      <c r="K76" s="26" t="inlineStr"/>
+      <c r="J76" s="26" t="inlineStr">
+        <is>
+          <t>+972523617199</t>
+        </is>
+      </c>
+      <c r="K76" s="26" t="inlineStr">
+        <is>
+          <t>adi.tzhori@gmail.com</t>
+        </is>
+      </c>
       <c r="L76" s="29" t="n"/>
       <c r="M76" s="29" t="n"/>
     </row>
@@ -5567,7 +5759,7 @@
       </c>
       <c r="H78" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -5575,8 +5767,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J78" s="26" t="inlineStr"/>
-      <c r="K78" s="26" t="inlineStr"/>
+      <c r="J78" s="26" t="inlineStr">
+        <is>
+          <t>+972504445453</t>
+        </is>
+      </c>
+      <c r="K78" s="26" t="inlineStr">
+        <is>
+          <t>uri@urishaked.com</t>
+        </is>
+      </c>
       <c r="L78" s="29" t="n"/>
       <c r="M78" s="29" t="n"/>
     </row>
@@ -5724,7 +5924,7 @@
       </c>
       <c r="H81" s="26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I81" s="28" t="inlineStr">
@@ -5732,7 +5932,11 @@
           <t>Transition point — what are they building or moving toward, what is the blocker, and who should they meet?</t>
         </is>
       </c>
-      <c r="J81" s="26" t="inlineStr"/>
+      <c r="J81" s="26" t="inlineStr">
+        <is>
+          <t>+972524774655</t>
+        </is>
+      </c>
       <c r="K81" s="26" t="inlineStr">
         <is>
           <t>zviwex@gmail.com</t>
@@ -6495,7 +6699,7 @@
       </c>
       <c r="I95" s="28" t="inlineStr">
         <is>
-          <t>What can they give — office hours, referrals into OpenEyes, mentoring? And what do they need from us right now?</t>
+          <t>Confirm the Pearl connection landed, and what the consultation covered</t>
         </is>
       </c>
       <c r="J95" s="26" t="inlineStr">
@@ -6545,7 +6749,7 @@
       </c>
       <c r="H96" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I96" s="28" t="inlineStr">
@@ -6553,8 +6757,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J96" s="26" t="inlineStr"/>
-      <c r="K96" s="26" t="inlineStr"/>
+      <c r="J96" s="26" t="inlineStr">
+        <is>
+          <t>+972549441034</t>
+        </is>
+      </c>
+      <c r="K96" s="26" t="inlineStr">
+        <is>
+          <t>ekepten@gmail.com</t>
+        </is>
+      </c>
       <c r="L96" s="29" t="n"/>
       <c r="M96" s="29" t="n"/>
     </row>
@@ -6707,7 +6919,7 @@
       </c>
       <c r="I99" s="28" t="inlineStr">
         <is>
-          <t>Roll-up — no verified role on file. What are they doing now, where are they heading, and what do they need?</t>
+          <t>Stay current — what are they working on now, and what would help?</t>
         </is>
       </c>
       <c r="J99" s="26" t="inlineStr">
@@ -6812,7 +7024,7 @@
       </c>
       <c r="H101" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I101" s="28" t="inlineStr">
@@ -6820,8 +7032,16 @@
           <t>What can they give — office hours, referrals into Miggo, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J101" s="26" t="inlineStr"/>
-      <c r="K101" s="26" t="inlineStr"/>
+      <c r="J101" s="26" t="inlineStr">
+        <is>
+          <t>+972543140162</t>
+        </is>
+      </c>
+      <c r="K101" s="26" t="inlineStr">
+        <is>
+          <t>gaigutherz@gmail.com</t>
+        </is>
+      </c>
       <c r="L101" s="29" t="n"/>
       <c r="M101" s="29" t="n"/>
     </row>
@@ -7024,7 +7244,7 @@
       </c>
       <c r="H105" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I105" s="28" t="inlineStr">
@@ -7032,8 +7252,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J105" s="26" t="inlineStr"/>
-      <c r="K105" s="26" t="inlineStr"/>
+      <c r="J105" s="26" t="inlineStr">
+        <is>
+          <t>+972527495040</t>
+        </is>
+      </c>
+      <c r="K105" s="26" t="inlineStr">
+        <is>
+          <t>nadavzemach@gmail.com</t>
+        </is>
+      </c>
       <c r="L105" s="29" t="n"/>
       <c r="M105" s="29" t="n"/>
     </row>
@@ -7131,7 +7359,7 @@
       </c>
       <c r="I107" s="28" t="inlineStr">
         <is>
-          <t>Stay current — still at Stealth? What are they working on, and what would help?</t>
+          <t>Confirm the 3.9 call with David Shasha happened and log the outcome</t>
         </is>
       </c>
       <c r="J107" s="26" t="inlineStr">
@@ -7181,7 +7409,7 @@
       </c>
       <c r="H108" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I108" s="28" t="inlineStr">
@@ -7189,8 +7417,16 @@
           <t>What can they give — office hours, referrals into Hopper Security, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J108" s="26" t="inlineStr"/>
-      <c r="K108" s="26" t="inlineStr"/>
+      <c r="J108" s="26" t="inlineStr">
+        <is>
+          <t>+972524546876</t>
+        </is>
+      </c>
+      <c r="K108" s="26" t="inlineStr">
+        <is>
+          <t>noyduany@gmail.com</t>
+        </is>
+      </c>
       <c r="L108" s="29" t="n"/>
       <c r="M108" s="29" t="n"/>
     </row>
@@ -7338,7 +7574,7 @@
       </c>
       <c r="H111" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I111" s="28" t="inlineStr">
@@ -7346,8 +7582,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J111" s="26" t="inlineStr"/>
-      <c r="K111" s="26" t="inlineStr"/>
+      <c r="J111" s="26" t="inlineStr">
+        <is>
+          <t>+972546618606</t>
+        </is>
+      </c>
+      <c r="K111" s="26" t="inlineStr">
+        <is>
+          <t>amosy3@gmail.com</t>
+        </is>
+      </c>
       <c r="L111" s="29" t="n"/>
       <c r="M111" s="29" t="n"/>
     </row>
@@ -7385,7 +7629,7 @@
       </c>
       <c r="H112" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -7393,8 +7637,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J112" s="26" t="inlineStr"/>
-      <c r="K112" s="26" t="inlineStr"/>
+      <c r="J112" s="26" t="inlineStr">
+        <is>
+          <t>+972526699700</t>
+        </is>
+      </c>
+      <c r="K112" s="26" t="inlineStr">
+        <is>
+          <t>omerhay95@gmail.com</t>
+        </is>
+      </c>
       <c r="L112" s="29" t="n"/>
       <c r="M112" s="29" t="n"/>
     </row>
@@ -7542,7 +7794,7 @@
       </c>
       <c r="H115" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I115" s="28" t="inlineStr">
@@ -7550,8 +7802,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J115" s="26" t="inlineStr"/>
-      <c r="K115" s="26" t="inlineStr"/>
+      <c r="J115" s="26" t="inlineStr">
+        <is>
+          <t>+972544976983</t>
+        </is>
+      </c>
+      <c r="K115" s="26" t="inlineStr">
+        <is>
+          <t>rami@anatifamily.com</t>
+        </is>
+      </c>
       <c r="L115" s="29" t="n"/>
       <c r="M115" s="29" t="n"/>
     </row>
@@ -7649,7 +7909,7 @@
       </c>
       <c r="I117" s="28" t="inlineStr">
         <is>
-          <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
+          <t>Tell Dolev whether Apex wants the Ron Zaidman / Israel Sofer intros, and whether the F2 or Apple-lecturer offers are relevant</t>
         </is>
       </c>
       <c r="J117" s="26" t="inlineStr">
@@ -7754,7 +8014,7 @@
       </c>
       <c r="H119" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I119" s="28" t="inlineStr">
@@ -7762,8 +8022,16 @@
           <t>What can they give — office hours, referrals into Ministry of Defense, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J119" s="26" t="inlineStr"/>
-      <c r="K119" s="26" t="inlineStr"/>
+      <c r="J119" s="26" t="inlineStr">
+        <is>
+          <t>+972585550675</t>
+        </is>
+      </c>
+      <c r="K119" s="26" t="inlineStr">
+        <is>
+          <t>roee.yaron.40@gmail.com</t>
+        </is>
+      </c>
       <c r="L119" s="29" t="n"/>
       <c r="M119" s="29" t="n"/>
     </row>
@@ -7966,7 +8234,7 @@
       </c>
       <c r="H123" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I123" s="28" t="inlineStr">
@@ -7974,8 +8242,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J123" s="26" t="inlineStr"/>
-      <c r="K123" s="26" t="inlineStr"/>
+      <c r="J123" s="26" t="inlineStr">
+        <is>
+          <t>+972544661198</t>
+        </is>
+      </c>
+      <c r="K123" s="26" t="inlineStr">
+        <is>
+          <t>turronen@gmail.com</t>
+        </is>
+      </c>
       <c r="L123" s="29" t="n"/>
       <c r="M123" s="29" t="n"/>
     </row>
@@ -8013,7 +8289,7 @@
       </c>
       <c r="H124" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I124" s="28" t="inlineStr">
@@ -8021,8 +8297,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J124" s="26" t="inlineStr"/>
-      <c r="K124" s="26" t="inlineStr"/>
+      <c r="J124" s="26" t="inlineStr">
+        <is>
+          <t>+972546729998</t>
+        </is>
+      </c>
+      <c r="K124" s="26" t="inlineStr">
+        <is>
+          <t>shachar64@gmail.com</t>
+        </is>
+      </c>
       <c r="L124" s="29" t="n"/>
       <c r="M124" s="29" t="n"/>
     </row>
@@ -8170,7 +8454,7 @@
       </c>
       <c r="H127" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I127" s="28" t="inlineStr">
@@ -8178,8 +8462,16 @@
           <t>What can they give — office hours, referrals, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J127" s="26" t="inlineStr"/>
-      <c r="K127" s="26" t="inlineStr"/>
+      <c r="J127" s="26" t="inlineStr">
+        <is>
+          <t>+972528039532</t>
+        </is>
+      </c>
+      <c r="K127" s="26" t="inlineStr">
+        <is>
+          <t>shaielro@gmail.com</t>
+        </is>
+      </c>
       <c r="L127" s="29" t="n"/>
       <c r="M127" s="29" t="n"/>
     </row>
@@ -8547,7 +8839,7 @@
       </c>
       <c r="H134" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I134" s="28" t="inlineStr">
@@ -8555,8 +8847,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J134" s="26" t="inlineStr"/>
-      <c r="K134" s="26" t="inlineStr"/>
+      <c r="J134" s="26" t="inlineStr">
+        <is>
+          <t>+972503485015</t>
+        </is>
+      </c>
+      <c r="K134" s="26" t="inlineStr">
+        <is>
+          <t>eyalkraft@gmail.com</t>
+        </is>
+      </c>
       <c r="L134" s="29" t="n"/>
       <c r="M134" s="29" t="n"/>
     </row>
@@ -8594,7 +8894,7 @@
       </c>
       <c r="H135" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I135" s="28" t="inlineStr">
@@ -8602,8 +8902,16 @@
           <t>Founding track — building this year? What is the blocker, is co-founder the gap, and who should they meet?</t>
         </is>
       </c>
-      <c r="J135" s="26" t="inlineStr"/>
-      <c r="K135" s="26" t="inlineStr"/>
+      <c r="J135" s="26" t="inlineStr">
+        <is>
+          <t>+972528759227</t>
+        </is>
+      </c>
+      <c r="K135" s="26" t="inlineStr">
+        <is>
+          <t>inbal.beracha@gmail.com</t>
+        </is>
+      </c>
       <c r="L135" s="29" t="n"/>
       <c r="M135" s="29" t="n"/>
     </row>
@@ -8751,7 +9059,7 @@
       </c>
       <c r="H138" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I138" s="28" t="inlineStr">
@@ -8759,8 +9067,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J138" s="26" t="inlineStr"/>
-      <c r="K138" s="26" t="inlineStr"/>
+      <c r="J138" s="26" t="inlineStr">
+        <is>
+          <t>+972543183227</t>
+        </is>
+      </c>
+      <c r="K138" s="26" t="inlineStr">
+        <is>
+          <t>madest@gmail.com</t>
+        </is>
+      </c>
       <c r="L138" s="29" t="n"/>
       <c r="M138" s="29" t="n"/>
     </row>
@@ -8963,7 +9279,7 @@
       </c>
       <c r="H142" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I142" s="28" t="inlineStr">
@@ -8971,8 +9287,16 @@
           <t>Node candidate. What can they open for our alumni, and would they give office hours?</t>
         </is>
       </c>
-      <c r="J142" s="26" t="inlineStr"/>
-      <c r="K142" s="26" t="inlineStr"/>
+      <c r="J142" s="26" t="inlineStr">
+        <is>
+          <t>+972504445453</t>
+        </is>
+      </c>
+      <c r="K142" s="26" t="inlineStr">
+        <is>
+          <t>uri@urishaked.com</t>
+        </is>
+      </c>
       <c r="L142" s="29" t="n"/>
       <c r="M142" s="29" t="n"/>
     </row>
@@ -9120,7 +9444,7 @@
       </c>
       <c r="H145" s="26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I145" s="28" t="inlineStr">
@@ -9128,7 +9452,11 @@
           <t>Transition point — what are they building or moving toward, what is the blocker, and who should they meet?</t>
         </is>
       </c>
-      <c r="J145" s="26" t="inlineStr"/>
+      <c r="J145" s="26" t="inlineStr">
+        <is>
+          <t>+972524774655</t>
+        </is>
+      </c>
       <c r="K145" s="26" t="inlineStr">
         <is>
           <t>zviwex@gmail.com</t>
@@ -9446,7 +9774,7 @@
       </c>
       <c r="H151" s="26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I151" s="28" t="inlineStr">
@@ -9454,8 +9782,16 @@
           <t>What can they give — office hours, referrals into TAU, mentoring? And what do they need from us right now?</t>
         </is>
       </c>
-      <c r="J151" s="26" t="inlineStr"/>
-      <c r="K151" s="26" t="inlineStr"/>
+      <c r="J151" s="26" t="inlineStr">
+        <is>
+          <t>+972547530590</t>
+        </is>
+      </c>
+      <c r="K151" s="26" t="inlineStr">
+        <is>
+          <t>shaked@yehezkel.net</t>
+        </is>
+      </c>
       <c r="L151" s="29" t="n"/>
       <c r="M151" s="29" t="n"/>
     </row>
@@ -9493,18 +9829,22 @@
       </c>
       <c r="H152" s="26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="I152" s="28" t="inlineStr">
         <is>
-          <t>Stay current — still at Tel Aviv University? What are they working on in research, and what would help?</t>
-        </is>
-      </c>
-      <c r="J152" s="26" t="inlineStr"/>
+          <t>Shape a concrete Deep Insight collaboration proposal and get back to him</t>
+        </is>
+      </c>
+      <c r="J152" s="26" t="inlineStr">
+        <is>
+          <t>+972506298628</t>
+        </is>
+      </c>
       <c r="K152" s="26" t="inlineStr">
         <is>
-          <t>nadav@deepinsight.co.il</t>
+          <t>nadavc@gmail.com</t>
         </is>
       </c>
       <c r="L152" s="29" t="n"/>
@@ -10979,7 +11319,7 @@
       </c>
       <c r="I179" s="28" t="inlineStr">
         <is>
-          <t>Node candidate — founded Breeze Security. What can they open for our alumni, and would they give office hours?</t>
+          <t>Tell Dolev whether Apex wants the Ron Zaidman / Israel Sofer intros, and whether the F2 or Apple-lecturer offers are relevant</t>
         </is>
       </c>
       <c r="J179" s="26" t="inlineStr">
@@ -11584,7 +11924,7 @@
       </c>
       <c r="I190" s="28" t="inlineStr">
         <is>
-          <t>What can they give — office hours, referrals into OpenEyes, mentoring? And what do they need from us right now?</t>
+          <t>Confirm the Pearl connection landed, and what the consultation covered</t>
         </is>
       </c>
       <c r="J190" s="26" t="inlineStr">
@@ -11783,7 +12123,11 @@
           <t>Assaf Monsa</t>
         </is>
       </c>
-      <c r="C2" s="29" t="n"/>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>אסף מונסה</t>
+        </is>
+      </c>
       <c r="D2" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -11927,7 +12271,11 @@
           <t>Daniel Ohayon</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n"/>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>דניאל אוחיון</t>
+        </is>
+      </c>
       <c r="D4" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -11973,7 +12321,11 @@
           <t>https://www.linkedin.com/in/daniel-ohayon-45b68513a</t>
         </is>
       </c>
-      <c r="U4" s="29" t="n"/>
+      <c r="U4" s="29" t="inlineStr">
+        <is>
+          <t>danielohayon444@gmail.com</t>
+        </is>
+      </c>
       <c r="V4" s="29" t="inlineStr">
         <is>
           <t>+972524056440</t>
@@ -11995,7 +12347,11 @@
           <t>Danny Grander</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n"/>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>דני גרנדר</t>
+        </is>
+      </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12075,7 +12431,11 @@
           <t>Dror Ben Eliezer</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>דרור בן אליעזר</t>
+        </is>
+      </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12117,8 +12477,16 @@
           <t>https://www.linkedin.com/in/dror-ben-eliezer-b084406/</t>
         </is>
       </c>
-      <c r="U6" s="29" t="n"/>
-      <c r="V6" s="29" t="n"/>
+      <c r="U6" s="29" t="inlineStr">
+        <is>
+          <t>dror.ben@gmail.com</t>
+        </is>
+      </c>
+      <c r="V6" s="29" t="inlineStr">
+        <is>
+          <t>+972544558495</t>
+        </is>
+      </c>
       <c r="W6" s="28" t="inlineStr">
         <is>
           <t>Consulting profile, no evidence of hands-on systems/infra work relevant to the criteria.</t>
@@ -12135,7 +12503,11 @@
           <t>Eldad Kepten</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>אלדד קפטן</t>
+        </is>
+      </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12177,8 +12549,16 @@
           <t>https://www.linkedin.com/in/eldad-kepten-441ba124/</t>
         </is>
       </c>
-      <c r="U7" s="29" t="n"/>
-      <c r="V7" s="29" t="n"/>
+      <c r="U7" s="29" t="inlineStr">
+        <is>
+          <t>ekepten@gmail.com</t>
+        </is>
+      </c>
+      <c r="V7" s="29" t="inlineStr">
+        <is>
+          <t>+972549441034</t>
+        </is>
+      </c>
       <c r="W7" s="28" t="inlineStr">
         <is>
           <t>Senior data scientist bridging research to product. Relevant analytical horsepower, no systems/power/GPU evidence.</t>
@@ -12195,7 +12575,11 @@
           <t>Eran Hertzmann</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>ערן הרצמן</t>
+        </is>
+      </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12271,7 +12655,11 @@
           <t>Eran Hirsch</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n"/>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>ערן הירש</t>
+        </is>
+      </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12347,7 +12735,11 @@
           <t>Eyal Kraft</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n"/>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>אייל קרפט</t>
+        </is>
+      </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12389,8 +12781,16 @@
           <t>https://www.linkedin.com/in/eyalkraft</t>
         </is>
       </c>
-      <c r="U10" s="29" t="n"/>
-      <c r="V10" s="29" t="n"/>
+      <c r="U10" s="29" t="inlineStr">
+        <is>
+          <t>eyalkraft@gmail.com</t>
+        </is>
+      </c>
+      <c r="V10" s="29" t="inlineStr">
+        <is>
+          <t>+972503485015</t>
+        </is>
+      </c>
       <c r="W10" s="28" t="inlineStr">
         <is>
           <t>CTO of a stealth company - cannot assess technical fit without knowing the domain, and availability is presumptively zero. Track, don't pitch.</t>
@@ -12407,7 +12807,11 @@
           <t>Gai Gutherz</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n"/>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>גיא גוטהרץ</t>
+        </is>
+      </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12453,8 +12857,16 @@
           <t>https://www.linkedin.com/in/gai-gutherz</t>
         </is>
       </c>
-      <c r="U11" s="29" t="n"/>
-      <c r="V11" s="29" t="n"/>
+      <c r="U11" s="29" t="inlineStr">
+        <is>
+          <t>gaigutherz@gmail.com</t>
+        </is>
+      </c>
+      <c r="V11" s="29" t="inlineStr">
+        <is>
+          <t>+972543140162</t>
+        </is>
+      </c>
       <c r="W11" s="28" t="inlineStr">
         <is>
           <t>Technical product leadership in appsec. No systems/power/GPU record.</t>
@@ -12471,7 +12883,11 @@
           <t>Inbal Beracha</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n"/>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>ענבל ברכה</t>
+        </is>
+      </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12513,8 +12929,16 @@
           <t>https://www.linkedin.com/in/inbal-beracha-a668ab182/</t>
         </is>
       </c>
-      <c r="U12" s="29" t="n"/>
-      <c r="V12" s="29" t="n"/>
+      <c r="U12" s="29" t="inlineStr">
+        <is>
+          <t>inbal.beracha@gmail.com</t>
+        </is>
+      </c>
+      <c r="V12" s="29" t="inlineStr">
+        <is>
+          <t>+972528759227</t>
+        </is>
+      </c>
       <c r="W12" s="28" t="inlineStr">
         <is>
           <t>Founding engineer at stealth - domain unknown, availability presumptively zero.</t>
@@ -12531,7 +12955,11 @@
           <t>Meir Adest</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n"/>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>מאיר אדסט</t>
+        </is>
+      </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12573,8 +13001,16 @@
           <t>https://www.linkedin.com/in/meiradest/</t>
         </is>
       </c>
-      <c r="U13" s="29" t="n"/>
-      <c r="V13" s="29" t="n"/>
+      <c r="U13" s="29" t="inlineStr">
+        <is>
+          <t>madest@gmail.com</t>
+        </is>
+      </c>
+      <c r="V13" s="29" t="inlineStr">
+        <is>
+          <t>+972543183227</t>
+        </is>
+      </c>
       <c r="W13" s="28" t="inlineStr">
         <is>
           <t>Co-founded SolarEdge - the defining company in power-optimization electronics (per-panel DC optimization, i.e. 'maximize output per installed watt'), scaled to a global public company. Exact business logic of Joulix in a different asset class. Won't join as operator; exceptional as founding chairman / technical advisor / seed investor.</t>
@@ -12591,7 +13027,11 @@
           <t>Michael Kellner</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>מיכאל קלנר</t>
+        </is>
+      </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12663,7 +13103,11 @@
           <t>Michal Shilo</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>מיכל שילה</t>
+        </is>
+      </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12739,7 +13183,11 @@
           <t>Nadav Zemach</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>נדב צמח</t>
+        </is>
+      </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12781,8 +13229,16 @@
           <t>https://www.linkedin.com/in/nadav-zemach-477a42365/</t>
         </is>
       </c>
-      <c r="U16" s="29" t="n"/>
-      <c r="V16" s="29" t="n"/>
+      <c r="U16" s="29" t="inlineStr">
+        <is>
+          <t>nadavzemach@gmail.com</t>
+        </is>
+      </c>
+      <c r="V16" s="29" t="inlineStr">
+        <is>
+          <t>+972527495040</t>
+        </is>
+      </c>
       <c r="W16" s="28" t="inlineStr">
         <is>
           <t>Government finance advisor - not a technical fit for a founding team. Separately valuable for sovereign-AI / regulatory / grant angles.</t>
@@ -12799,7 +13255,11 @@
           <t>Nir Yaron</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>ניר ירון</t>
+        </is>
+      </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12837,8 +13297,16 @@
           <t>https://www.linkedin.com/in/nir-yaron-886051241</t>
         </is>
       </c>
-      <c r="U17" s="29" t="n"/>
-      <c r="V17" s="29" t="n"/>
+      <c r="U17" s="29" t="inlineStr">
+        <is>
+          <t>njyaron@gmail.com</t>
+        </is>
+      </c>
+      <c r="V17" s="29" t="inlineStr">
+        <is>
+          <t>+972544343258</t>
+        </is>
+      </c>
       <c r="W17" s="28" t="inlineStr">
         <is>
           <t>No role data in roster/alumni page and no reliable public technical record found.</t>
@@ -12855,7 +13323,11 @@
           <t>Noy Duany</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n"/>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>נוי דואני</t>
+        </is>
+      </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12901,8 +13373,16 @@
           <t>https://www.linkedin.com/in/noyduany/</t>
         </is>
       </c>
-      <c r="U18" s="29" t="n"/>
-      <c r="V18" s="29" t="n"/>
+      <c r="U18" s="29" t="inlineStr">
+        <is>
+          <t>noyduany@gmail.com</t>
+        </is>
+      </c>
+      <c r="V18" s="29" t="inlineStr">
+        <is>
+          <t>+972524546876</t>
+        </is>
+      </c>
       <c r="W18" s="28" t="inlineStr">
         <is>
           <t>Cyber R&amp;D team lead. Solid engineer-leader, wrong domain.</t>
@@ -12919,7 +13399,11 @@
           <t>Ohad Amosy</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n"/>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>אוהד עמוסי</t>
+        </is>
+      </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -12961,8 +13445,16 @@
           <t>https://il.linkedin.com/in/ohad-amosy</t>
         </is>
       </c>
-      <c r="U19" s="29" t="n"/>
-      <c r="V19" s="29" t="n"/>
+      <c r="U19" s="29" t="inlineStr">
+        <is>
+          <t>amosy3@gmail.com</t>
+        </is>
+      </c>
+      <c r="V19" s="29" t="inlineStr">
+        <is>
+          <t>+972546618606</t>
+        </is>
+      </c>
       <c r="W19" s="28" t="inlineStr">
         <is>
           <t>Published ML researcher (WACV, EMNLP; federated learning, hypernetworks) incl. a neural-network-driven QAOA optimization paper and co-authorship with NVIDIA Research-affiliated lab. Strong optimization/ML brain for the control-policy side; no GPU systems or power production record.</t>
@@ -12979,7 +13471,11 @@
           <t>Omer Hay</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n"/>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>עומר חי</t>
+        </is>
+      </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13025,8 +13521,16 @@
           <t>https://www.linkedin.com/in/hay-omer</t>
         </is>
       </c>
-      <c r="U20" s="29" t="n"/>
-      <c r="V20" s="29" t="n"/>
+      <c r="U20" s="29" t="inlineStr">
+        <is>
+          <t>omerhay95@gmail.com</t>
+        </is>
+      </c>
+      <c r="V20" s="29" t="inlineStr">
+        <is>
+          <t>+972526699700</t>
+        </is>
+      </c>
       <c r="W20" s="28" t="inlineStr">
         <is>
           <t>Generalist SWE/team lead. No domain evidence.</t>
@@ -13043,7 +13547,11 @@
           <t>Rami Anati</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n"/>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>רמי ענתי</t>
+        </is>
+      </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13085,8 +13593,16 @@
           <t>https://www.linkedin.com/in/ramianati</t>
         </is>
       </c>
-      <c r="U21" s="29" t="n"/>
-      <c r="V21" s="29" t="n"/>
+      <c r="U21" s="29" t="inlineStr">
+        <is>
+          <t>rami@anatifamily.com</t>
+        </is>
+      </c>
+      <c r="V21" s="29" t="inlineStr">
+        <is>
+          <t>+972544976983</t>
+        </is>
+      </c>
       <c r="W21" s="28" t="inlineStr">
         <is>
           <t>Backend team lead/PM. No domain evidence.</t>
@@ -13103,7 +13619,11 @@
           <t>Roee Yaron</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n"/>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>רועי ירון</t>
+        </is>
+      </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13145,8 +13665,16 @@
       <c r="R22" s="33" t="n"/>
       <c r="S22" s="34" t="n"/>
       <c r="T22" s="26" t="n"/>
-      <c r="U22" s="29" t="n"/>
-      <c r="V22" s="29" t="n"/>
+      <c r="U22" s="29" t="inlineStr">
+        <is>
+          <t>roee.yaron.40@gmail.com</t>
+        </is>
+      </c>
+      <c r="V22" s="29" t="inlineStr">
+        <is>
+          <t>+972585550675</t>
+        </is>
+      </c>
       <c r="W22" s="28" t="inlineStr">
         <is>
           <t>Defense physicist, Talpiot. Hard-science depth, no software-infrastructure record.</t>
@@ -13163,7 +13691,11 @@
           <t>Ronen Tur</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n"/>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>רונן טור</t>
+        </is>
+      </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13205,8 +13737,16 @@
           <t>https://www.linkedin.com/in/ronen-tur-641a0a18/</t>
         </is>
       </c>
-      <c r="U23" s="29" t="n"/>
-      <c r="V23" s="29" t="n"/>
+      <c r="U23" s="29" t="inlineStr">
+        <is>
+          <t>turronen@gmail.com</t>
+        </is>
+      </c>
+      <c r="V23" s="29" t="inlineStr">
+        <is>
+          <t>+972544661198</t>
+        </is>
+      </c>
       <c r="W23" s="28" t="inlineStr">
         <is>
           <t>Senior algorithms/DL leadership - relevant to the optimization brain of a power-control loop, but no public GPU/power specifics.</t>
@@ -13223,7 +13763,11 @@
           <t>Shachar Cohen</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n"/>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>שחר כהן</t>
+        </is>
+      </c>
       <c r="D24" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13265,8 +13809,16 @@
           <t>https://www.linkedin.com/in/shachar-cohen-480b86205</t>
         </is>
       </c>
-      <c r="U24" s="29" t="n"/>
-      <c r="V24" s="29" t="n"/>
+      <c r="U24" s="29" t="inlineStr">
+        <is>
+          <t>shachar64@gmail.com</t>
+        </is>
+      </c>
+      <c r="V24" s="29" t="inlineStr">
+        <is>
+          <t>+972546729998</t>
+        </is>
+      </c>
       <c r="W24" s="28" t="inlineStr">
         <is>
           <t>SW R&amp;D engineer/manager, Talpiot. No domain evidence.</t>
@@ -13283,7 +13835,11 @@
           <t>Shai Elroy</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n"/>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>שי אלרואי</t>
+        </is>
+      </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13325,8 +13881,16 @@
           <t>https://www.linkedin.com/in/shai-elroy</t>
         </is>
       </c>
-      <c r="U25" s="29" t="n"/>
-      <c r="V25" s="29" t="n"/>
+      <c r="U25" s="29" t="inlineStr">
+        <is>
+          <t>shaielro@gmail.com</t>
+        </is>
+      </c>
+      <c r="V25" s="29" t="inlineStr">
+        <is>
+          <t>+972528039532</t>
+        </is>
+      </c>
       <c r="W25" s="28" t="inlineStr">
         <is>
           <t>Cyber R&amp;D team lead. Wrong domain.</t>
@@ -13343,7 +13907,11 @@
           <t>Uri Shaked</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n"/>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>אורי שקד</t>
+        </is>
+      </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13385,8 +13953,16 @@
           <t>https://www.linkedin.com/in/urishaked/</t>
         </is>
       </c>
-      <c r="U26" s="29" t="n"/>
-      <c r="V26" s="29" t="n"/>
+      <c r="U26" s="29" t="inlineStr">
+        <is>
+          <t>uri@urishaked.com</t>
+        </is>
+      </c>
+      <c r="V26" s="29" t="inlineStr">
+        <is>
+          <t>+972504445453</t>
+        </is>
+      </c>
       <c r="W26" s="28" t="inlineStr">
         <is>
           <t>Built Wokwi (embedded/silicon simulation) and active in open silicon (TinyTapeout) - rare HW/SW boundary depth, exactly the instinct a firmware-adjacent power layer needs. No GPU DVFS/data-center record; committed to his own products. Best used as technical advisor.</t>
@@ -13403,7 +13979,11 @@
           <t>Zvi Wexlstein</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n"/>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>צבי וקסלשטיין</t>
+        </is>
+      </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
           <t>#1</t>
@@ -13454,7 +14034,11 @@
           <t>zviwex@gmail.com</t>
         </is>
       </c>
-      <c r="V27" s="29" t="n"/>
+      <c r="V27" s="29" t="inlineStr">
+        <is>
+          <t>+972524774655</t>
+        </is>
+      </c>
       <c r="W27" s="28" t="inlineStr">
         <is>
           <t>Software architect at Polar/IBM; Founder Track signal. Solid architect, no power/GPU record.</t>
@@ -13475,7 +14059,11 @@
           <t>Almog Zer</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n"/>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>אלמוג זר</t>
+        </is>
+      </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13551,7 +14139,11 @@
           <t>Aviel Zecharia</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n"/>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>אביאל זכריה</t>
+        </is>
+      </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13631,7 +14223,11 @@
           <t>Bar Matityahu</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n"/>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>בר מתתיהו</t>
+        </is>
+      </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13707,7 +14303,11 @@
           <t>Benny Rousso</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n"/>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>בני רוסו</t>
+        </is>
+      </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13787,7 +14387,11 @@
           <t>Benzion Kossowsky</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n"/>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>בן ציון קוסובסקי</t>
+        </is>
+      </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13859,7 +14463,11 @@
           <t>Eyal Horowicz</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n"/>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>אייל הורוביץ</t>
+        </is>
+      </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -13939,7 +14547,11 @@
           <t>Gal Wiernik</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n"/>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>גל ורניק</t>
+        </is>
+      </c>
       <c r="D34" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14019,7 +14631,11 @@
           <t>Gil Raytan</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n"/>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>גיל רייטן</t>
+        </is>
+      </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14099,7 +14715,11 @@
           <t>Guy Yoshpe</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n"/>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>גיא ישפה</t>
+        </is>
+      </c>
       <c r="D36" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14175,7 +14795,11 @@
           <t>Hila Shmuel</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n"/>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>הילה שמואל</t>
+        </is>
+      </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14255,7 +14879,11 @@
           <t>Iddan Golomb</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n"/>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>עידן גולומב</t>
+        </is>
+      </c>
       <c r="D38" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14335,7 +14963,11 @@
           <t>Ido Kazma</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n"/>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>עידו קזמה</t>
+        </is>
+      </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14415,7 +15047,11 @@
           <t>Ilan Voronel</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n"/>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>אילן וורונל</t>
+        </is>
+      </c>
       <c r="D40" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14495,7 +15131,11 @@
           <t>Jonathan Gilat</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n"/>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>יונתן גילת</t>
+        </is>
+      </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14575,7 +15215,11 @@
           <t>Kfir Shoar</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n"/>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>כפיר שואר</t>
+        </is>
+      </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14617,8 +15261,16 @@
       <c r="R42" s="33" t="n"/>
       <c r="S42" s="34" t="n"/>
       <c r="T42" s="26" t="n"/>
-      <c r="U42" s="29" t="n"/>
-      <c r="V42" s="29" t="n"/>
+      <c r="U42" s="29" t="inlineStr">
+        <is>
+          <t>kfirshoar@gmail.com</t>
+        </is>
+      </c>
+      <c r="V42" s="29" t="inlineStr">
+        <is>
+          <t>+972546793903</t>
+        </is>
+      </c>
       <c r="W42" s="28" t="inlineStr">
         <is>
           <t>SWE at Cyera. No domain evidence.</t>
@@ -14635,7 +15287,11 @@
           <t>Lior Lev Tov</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n"/>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>ליאור לב טוב</t>
+        </is>
+      </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14715,7 +15371,11 @@
           <t>Liran Markin</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n"/>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>לירן מרקין</t>
+        </is>
+      </c>
       <c r="D44" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14778,7 +15438,7 @@
       </c>
       <c r="X44" s="33" t="inlineStr">
         <is>
-          <t>[dex import] military course: קורס י״ט · met with: NA · education: אר״מ · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad</t>
+          <t>[dex import] military course: קורס י״ט · met with: NA · education: אר״מ · tags: Fireside Chat,Apex Newsletter,Signed To Apex,25/2/2026 - Closing Event,Apex Grad · [2026-09-01] חובר לגישה ל-GB300 בפרינסטון (יחד עם גל וינר ואור וילדר, לא ברוסטר) [[NADAV: תאריך? ולוודא שהאיות 'Liran Markin' תואם למי שדיברת איתו]] (call, date not given)</t>
         </is>
       </c>
     </row>
@@ -14791,7 +15451,11 @@
           <t>Michael Komraz</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n"/>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>מיכאל קומרז</t>
+        </is>
+      </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14859,7 +15523,11 @@
           <t>Michael Zuzovski</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n"/>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>מיכאל זוזובסקי</t>
+        </is>
+      </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -14931,7 +15599,11 @@
           <t>Michal Ran Shchory</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n"/>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>מיכל רן שחורי</t>
+        </is>
+      </c>
       <c r="D47" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15011,7 +15683,11 @@
           <t>Mor Shemesh</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n"/>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>מור שמש</t>
+        </is>
+      </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15083,7 +15759,11 @@
           <t>Omer Onn</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n"/>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>עומר און</t>
+        </is>
+      </c>
       <c r="D49" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15163,7 +15843,11 @@
           <t>Omri Gotlib</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n"/>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>עומרי גוטליב</t>
+        </is>
+      </c>
       <c r="D50" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15239,7 +15923,11 @@
           <t>Peleg Ben Hamo</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n"/>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>פלג בן חמו</t>
+        </is>
+      </c>
       <c r="D51" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15319,7 +16007,11 @@
           <t>Ron Galay</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n"/>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>רון גאלאי</t>
+        </is>
+      </c>
       <c r="D52" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15399,7 +16091,11 @@
           <t>Roy Moshe</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n"/>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>רועי משה</t>
+        </is>
+      </c>
       <c r="D53" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15479,7 +16175,11 @@
           <t>Shachar Resisi</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n"/>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>שחר רסיסי</t>
+        </is>
+      </c>
       <c r="D54" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15559,7 +16259,11 @@
           <t>Shaked Yehezkel</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n"/>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>שקד יחזקאל</t>
+        </is>
+      </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15601,8 +16305,16 @@
       <c r="R55" s="33" t="n"/>
       <c r="S55" s="34" t="n"/>
       <c r="T55" s="26" t="n"/>
-      <c r="U55" s="29" t="n"/>
-      <c r="V55" s="29" t="n"/>
+      <c r="U55" s="29" t="inlineStr">
+        <is>
+          <t>shaked@yehezkel.net</t>
+        </is>
+      </c>
+      <c r="V55" s="29" t="inlineStr">
+        <is>
+          <t>+972547530590</t>
+        </is>
+      </c>
       <c r="W55" s="28" t="inlineStr">
         <is>
           <t>Academic researcher. Insufficient record.</t>
@@ -15619,7 +16331,11 @@
           <t>Sharon Brizinov</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n"/>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>שרון בריזינוב</t>
+        </is>
+      </c>
       <c r="D56" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15695,7 +16411,11 @@
           <t>Tomer Goren</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n"/>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>תומר גורן</t>
+        </is>
+      </c>
       <c r="D57" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15763,7 +16483,11 @@
           <t>Tzah Pahima</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n"/>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>צח פחימה</t>
+        </is>
+      </c>
       <c r="D58" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15843,7 +16567,11 @@
           <t>Yakov Kosoburd</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n"/>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>יעקב קוסובורד</t>
+        </is>
+      </c>
       <c r="D59" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15919,7 +16647,11 @@
           <t>Yuri Shapira</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n"/>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>יורי שפירא</t>
+        </is>
+      </c>
       <c r="D60" s="26" t="inlineStr">
         <is>
           <t>#2</t>
@@ -15999,7 +16731,11 @@
           <t>Adi Cohen</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n"/>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>עדי כהן</t>
+        </is>
+      </c>
       <c r="D61" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16055,7 +16791,11 @@
           <t>Adi Tzhori Moshe</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n"/>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>עדי צחורי משה</t>
+        </is>
+      </c>
       <c r="D62" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16097,8 +16837,16 @@
           <t>https://www.linkedin.com/in/adi-tzhori</t>
         </is>
       </c>
-      <c r="U62" s="29" t="n"/>
-      <c r="V62" s="29" t="n"/>
+      <c r="U62" s="29" t="inlineStr">
+        <is>
+          <t>adi.tzhori@gmail.com</t>
+        </is>
+      </c>
+      <c r="V62" s="29" t="inlineStr">
+        <is>
+          <t>+972523617199</t>
+        </is>
+      </c>
       <c r="W62" s="28" t="inlineStr">
         <is>
           <t>Embedded SW developer at a voice-AI/DSP startup, ex-Elbit, Technion computer engineering. Embedded/DSP is a relevant profile shape at junior level; no GPU/power record.</t>
@@ -16119,7 +16867,11 @@
           <t>Adir Kobovich</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n"/>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>אדיר קובוביץ</t>
+        </is>
+      </c>
       <c r="D63" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16191,7 +16943,11 @@
           <t>Alon Wolf</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n"/>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>אלון וולף</t>
+        </is>
+      </c>
       <c r="D64" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16267,7 +17023,11 @@
           <t>Amir Balva</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n"/>
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>אמיר בלוא</t>
+        </is>
+      </c>
       <c r="D65" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16331,7 +17091,11 @@
           <t>Amitai Nevo</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n"/>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>אמיתי נבו</t>
+        </is>
+      </c>
       <c r="D66" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16399,7 +17163,11 @@
           <t>Ariel Bachar</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n"/>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>אריאל בכר</t>
+        </is>
+      </c>
       <c r="D67" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16471,7 +17239,11 @@
           <t>Avichay Radovsky</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n"/>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>אביחי רדובסקי</t>
+        </is>
+      </c>
       <c r="D68" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16482,7 +17254,7 @@
       <c r="G68" s="26" t="n"/>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="I68" s="29" t="n"/>
@@ -16495,7 +17267,11 @@
       <c r="L68" s="29" t="n"/>
       <c r="M68" s="33" t="n"/>
       <c r="N68" s="33" t="n"/>
-      <c r="O68" s="33" t="n"/>
+      <c r="O68" s="33" t="inlineStr">
+        <is>
+          <t>Offered to connect Nadav to Jackie Levi (National AI Program/מטה הבינה המלאכותית הלאומי) re: frontier labs</t>
+        </is>
+      </c>
       <c r="P68" s="34" t="n"/>
       <c r="Q68" s="29" t="n"/>
       <c r="R68" s="33" t="n"/>
@@ -16516,7 +17292,11 @@
           <t>Web search returned no reliable public technical record for this name.</t>
         </is>
       </c>
-      <c r="X68" s="33" t="n"/>
+      <c r="X68" s="33" t="inlineStr">
+        <is>
+          <t>[2026-09-01] תפקיד עודכן מ-'Unknown' ל-Architect; הציע לחבר לז'קי לוי (מטה הבינה הלאומי, frontier labs) (told directly by Nadav)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="26" t="n">
@@ -16527,7 +17307,11 @@
           <t>Avraham Berrebi</t>
         </is>
       </c>
-      <c r="C69" s="29" t="n"/>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>אברהם ברבי</t>
+        </is>
+      </c>
       <c r="D69" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16595,7 +17379,11 @@
           <t>Benny Getz</t>
         </is>
       </c>
-      <c r="C70" s="29" t="n"/>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>בני גץ</t>
+        </is>
+      </c>
       <c r="D70" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16671,7 +17459,11 @@
           <t>David Shasha</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n"/>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>דוד שאשא</t>
+        </is>
+      </c>
       <c r="D71" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16706,7 +17498,11 @@
       <c r="O71" s="33" t="n"/>
       <c r="P71" s="34" t="n"/>
       <c r="Q71" s="29" t="n"/>
-      <c r="R71" s="33" t="n"/>
+      <c r="R71" s="33" t="inlineStr">
+        <is>
+          <t>Confirm the 3.9 call with David Shasha happened and log the outcome</t>
+        </is>
+      </c>
       <c r="S71" s="34" t="n"/>
       <c r="T71" s="26" t="inlineStr">
         <is>
@@ -16728,7 +17524,11 @@
           <t>Web search returned no reliable public disambiguation for this name.</t>
         </is>
       </c>
-      <c r="X71" s="33" t="n"/>
+      <c r="X71" s="33" t="inlineStr">
+        <is>
+          <t>[2026-09-01] שיחה מתוכננת ל-3.9 (יום חמישי) על שותפות טווח ארוך [[NADAV: שעה? תוצאה?]] (told directly by Nadav)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="26" t="n">
@@ -16739,7 +17539,11 @@
           <t>Dolev Elbaz</t>
         </is>
       </c>
-      <c r="C72" s="29" t="n"/>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>דולב אלבז</t>
+        </is>
+      </c>
       <c r="D72" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16779,10 +17583,26 @@
       <c r="L72" s="29" t="n"/>
       <c r="M72" s="33" t="n"/>
       <c r="N72" s="33" t="n"/>
-      <c r="O72" s="33" t="n"/>
-      <c r="P72" s="34" t="n"/>
-      <c r="Q72" s="29" t="n"/>
-      <c r="R72" s="33" t="n"/>
+      <c r="O72" s="33" t="inlineStr">
+        <is>
+          <t>Referrals: Ron Zaidman (cohort-mate, VP R&amp;D x2, ex-Microsoft, indie 'Dopamine' agents project) and Israel Sofer (later cohort, רמ״ד ב-81, ~1yr to discharge) as contributor/mentor candidates · F2 (his investor, AI application-layer focus) if Apex wants investor intros · friend w/ PhD in vision at Apple, for a guest lecture</t>
+        </is>
+      </c>
+      <c r="P72" s="34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Q72" s="29" t="inlineStr">
+        <is>
+          <t>whatsapp 16.8</t>
+        </is>
+      </c>
+      <c r="R72" s="33" t="inlineStr">
+        <is>
+          <t>Tell Dolev whether Apex wants the Ron Zaidman / Israel Sofer intros, and whether the F2 or Apple-lecturer offers are relevant</t>
+        </is>
+      </c>
       <c r="S72" s="34" t="n"/>
       <c r="T72" s="26" t="inlineStr">
         <is>
@@ -16804,7 +17624,11 @@
           <t>One of the strongest systems profiles in the roster: built DDoS-protection datapath for Azure's edge in DPDK + Rust as tech lead ('high performance at scale'), embedded Linux + x86 virtualization background, Israel-Defense-Prize-winning projects, Psagot. Exactly the kernel/datapath engineering Joulix needs - but he is co-founder/CTO of his own funded startup, so availability is ~0. Track closely.</t>
         </is>
       </c>
-      <c r="X72" s="33" t="n"/>
+      <c r="X72" s="33" t="inlineStr">
+        <is>
+          <t>[2026-09-01] וואצאפ 16.8 — פירוט מלא של 4 ההצעות שלו (שני קולגות, F2, מרצה) (whatsapp, relayed by Dolev)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="26" t="n">
@@ -16815,7 +17639,11 @@
           <t>Georgy Melamed</t>
         </is>
       </c>
-      <c r="C73" s="29" t="n"/>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>גאורגי מלמד</t>
+        </is>
+      </c>
       <c r="D73" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16883,7 +17711,11 @@
           <t>Guy Goldenberg</t>
         </is>
       </c>
-      <c r="C74" s="29" t="n"/>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>גיא גולדנברג</t>
+        </is>
+      </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -16955,7 +17787,11 @@
           <t>Hillel Twersky</t>
         </is>
       </c>
-      <c r="C75" s="29" t="n"/>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>הלל טברסקי</t>
+        </is>
+      </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17023,7 +17859,11 @@
           <t>Idan Lev-Yehudi</t>
         </is>
       </c>
-      <c r="C76" s="29" t="n"/>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>עידן לב יהודי</t>
+        </is>
+      </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17099,7 +17939,11 @@
           <t>Ido Ben Tsion</t>
         </is>
       </c>
-      <c r="C77" s="29" t="n"/>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>עידו בן ציון</t>
+        </is>
+      </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17167,7 +18011,11 @@
           <t>Ilan Godik</t>
         </is>
       </c>
-      <c r="C78" s="29" t="n"/>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>אילן גודיק</t>
+        </is>
+      </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17231,7 +18079,11 @@
           <t>Itamar Gilad</t>
         </is>
       </c>
-      <c r="C79" s="29" t="n"/>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>איתמר גלעד</t>
+        </is>
+      </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17303,7 +18155,11 @@
           <t>Itay Gissis</t>
         </is>
       </c>
-      <c r="C80" s="29" t="n"/>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>איתי גיסיס</t>
+        </is>
+      </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17379,7 +18235,11 @@
           <t>Itzhak Bernstein</t>
         </is>
       </c>
-      <c r="C81" s="29" t="n"/>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>יצחק ברנשטיין</t>
+        </is>
+      </c>
       <c r="D81" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17443,7 +18303,11 @@
           <t>Liad Ben Uri</t>
         </is>
       </c>
-      <c r="C82" s="29" t="n"/>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>ליעד בן אורי</t>
+        </is>
+      </c>
       <c r="D82" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17519,7 +18383,11 @@
           <t>Mark Popov</t>
         </is>
       </c>
-      <c r="C83" s="29" t="n"/>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>מארק פופוב</t>
+        </is>
+      </c>
       <c r="D83" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17591,7 +18459,11 @@
           <t>Matan Shoef</t>
         </is>
       </c>
-      <c r="C84" s="29" t="n"/>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>מתן שואף</t>
+        </is>
+      </c>
       <c r="D84" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17629,8 +18501,16 @@
       <c r="N84" s="33" t="n"/>
       <c r="O84" s="33" t="n"/>
       <c r="P84" s="34" t="n"/>
-      <c r="Q84" s="29" t="n"/>
-      <c r="R84" s="33" t="n"/>
+      <c r="Q84" s="29" t="inlineStr">
+        <is>
+          <t>call [[NADAV: date?]]</t>
+        </is>
+      </c>
+      <c r="R84" s="33" t="inlineStr">
+        <is>
+          <t>Confirm the Pearl connection landed, and what the consultation covered</t>
+        </is>
+      </c>
       <c r="S84" s="34" t="n"/>
       <c r="T84" s="26" t="inlineStr">
         <is>
@@ -17652,7 +18532,11 @@
           <t>Algorithms team lead, ex-Samsung R&amp;D, Technion EE. Solid algo engineering; no domain evidence.</t>
         </is>
       </c>
-      <c r="X84" s="33" t="n"/>
+      <c r="X84" s="33" t="inlineStr">
+        <is>
+          <t>[2026-09-01] שיחה איתי — הצעתי חיבור ל-Pearl והתייעצות [[NADAV: מה זה Pearl — אדם/חברה, ומה היה נושא ההתייעצות?]] (call, date not given)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="26" t="n">
@@ -17663,7 +18547,11 @@
           <t>Maya Kleinstein</t>
         </is>
       </c>
-      <c r="C85" s="29" t="n"/>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>מאיה קלינשטיין</t>
+        </is>
+      </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17719,7 +18607,11 @@
           <t>Maya Naveh</t>
         </is>
       </c>
-      <c r="C86" s="29" t="n"/>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>מאיה נוה</t>
+        </is>
+      </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17775,7 +18667,11 @@
           <t>Menachem Menasherov</t>
         </is>
       </c>
-      <c r="C87" s="29" t="n"/>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>מנחם מנשרוב</t>
+        </is>
+      </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17831,7 +18727,11 @@
           <t>Nadav Claude Cohen</t>
         </is>
       </c>
-      <c r="C88" s="29" t="n"/>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>נדב קלוד כהן</t>
+        </is>
+      </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17899,7 +18799,11 @@
           <t>Nadav Cohen</t>
         </is>
       </c>
-      <c r="C89" s="29" t="n"/>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>נדב כהן</t>
+        </is>
+      </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -17937,8 +18841,16 @@
       <c r="N89" s="33" t="n"/>
       <c r="O89" s="33" t="n"/>
       <c r="P89" s="34" t="n"/>
-      <c r="Q89" s="29" t="n"/>
-      <c r="R89" s="33" t="n"/>
+      <c r="Q89" s="29" t="inlineStr">
+        <is>
+          <t>call [[NADAV: date?]]</t>
+        </is>
+      </c>
+      <c r="R89" s="33" t="inlineStr">
+        <is>
+          <t>Shape a concrete Deep Insight collaboration proposal and get back to him</t>
+        </is>
+      </c>
       <c r="S89" s="34" t="n"/>
       <c r="T89" s="26" t="inlineStr">
         <is>
@@ -17947,16 +18859,24 @@
       </c>
       <c r="U89" s="29" t="inlineStr">
         <is>
-          <t>nadav@deepinsight.co.il</t>
-        </is>
-      </c>
-      <c r="V89" s="29" t="n"/>
+          <t>nadavc@gmail.com</t>
+        </is>
+      </c>
+      <c r="V89" s="29" t="inlineStr">
+        <is>
+          <t>+972506298628</t>
+        </is>
+      </c>
       <c r="W89" s="28" t="inlineStr">
         <is>
           <t>If this is the Dr. Nadav Cohen of TAU/Imubit - whose company does deep-learning-based real-time control of large industrial facilities, optimizing them for profit and sustainability - it is conceptually the closest match in the entire roster: an RL control layer over physical infrastructure, monetized at scale (his Google Scholar even lists 'Physical AI' and RL). But the roster's LinkedIn slug does not match his known profiles and, if it is him, he is fully committed (professor + CTO). Verify identity before any outreach; would score ~92 on skills.</t>
         </is>
       </c>
-      <c r="X89" s="33" t="n"/>
+      <c r="X89" s="33" t="inlineStr">
+        <is>
+          <t>[2026-09-01] שיחה איתי — הציע שיתוף פעולה עם הקרן Deep Insight שהוא עובד בה. מאמת את source_note הקודם — nadav@deepinsight.co.il תואם. (call, date not given) · [apex sheet] also reachable at nadav@deepinsight.co.il</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="26" t="n">
@@ -17967,7 +18887,11 @@
           <t>Noga Keren</t>
         </is>
       </c>
-      <c r="C90" s="29" t="n"/>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>נגה קרן</t>
+        </is>
+      </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18031,7 +18955,11 @@
           <t>Noy Hadar</t>
         </is>
       </c>
-      <c r="C91" s="29" t="n"/>
+      <c r="C91" s="29" t="inlineStr">
+        <is>
+          <t>נוי הדר</t>
+        </is>
+      </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18099,7 +19027,11 @@
           <t>Oren Fine</t>
         </is>
       </c>
-      <c r="C92" s="29" t="n"/>
+      <c r="C92" s="29" t="inlineStr">
+        <is>
+          <t>אורן פיין</t>
+        </is>
+      </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18171,7 +19103,11 @@
           <t>Oz Tamir</t>
         </is>
       </c>
-      <c r="C93" s="29" t="n"/>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>עוז תמיר</t>
+        </is>
+      </c>
       <c r="D93" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18243,7 +19179,11 @@
           <t>Shlomo Lahav</t>
         </is>
       </c>
-      <c r="C94" s="29" t="n"/>
+      <c r="C94" s="29" t="inlineStr">
+        <is>
+          <t>שלמה להב</t>
+        </is>
+      </c>
       <c r="D94" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18311,7 +19251,11 @@
           <t>Uri Ariel Chen</t>
         </is>
       </c>
-      <c r="C95" s="29" t="n"/>
+      <c r="C95" s="29" t="inlineStr">
+        <is>
+          <t>אורי אריאל חן</t>
+        </is>
+      </c>
       <c r="D95" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18379,7 +19323,11 @@
           <t>Yaniv Shaked</t>
         </is>
       </c>
-      <c r="C96" s="29" t="n"/>
+      <c r="C96" s="29" t="inlineStr">
+        <is>
+          <t>יניב שקד</t>
+        </is>
+      </c>
       <c r="D96" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18451,7 +19399,11 @@
           <t>Yoni Hornstein</t>
         </is>
       </c>
-      <c r="C97" s="29" t="n"/>
+      <c r="C97" s="29" t="inlineStr">
+        <is>
+          <t>יוני הורנשטיין</t>
+        </is>
+      </c>
       <c r="D97" s="26" t="inlineStr">
         <is>
           <t>#3</t>
@@ -18523,7 +19475,11 @@
           <t>Yuval Genossar</t>
         </is>
       </c>
-      <c r="C98" s="29" t="n"/>
+      <c r="C98" s="29" t="inlineStr">
+        <is>
+          <t>יובל גנוסר</t>
+        </is>
+      </c>
       <c r="D98" s="26" t="inlineStr">
         <is>
           <t>#3</t>
